--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBDC1B8-4BB0-4853-AF27-18A6135165AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AF3F2A-3852-4AA1-9532-7427AE90128F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="3310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3603" uniqueCount="3322">
   <si>
     <t>C-VI096</t>
   </si>
@@ -9966,6 +9966,42 @@
   </si>
   <si>
     <t>Sure Stay | Pool</t>
+  </si>
+  <si>
+    <t>C-UN150</t>
+  </si>
+  <si>
+    <t>University of Pittsburgh       |Pool</t>
+  </si>
+  <si>
+    <t>University of Pittsburgh       |Spa</t>
+  </si>
+  <si>
+    <t>University of Pgh Rec</t>
+  </si>
+  <si>
+    <t>C-CE110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center for Fitness and Health </t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>Center for Fitness amd Health |Lap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center for Fitness amd Health |Therapy </t>
+  </si>
+  <si>
+    <t>Center for Fitness amd Health |Spa</t>
   </si>
 </sst>
 </file>
@@ -10042,7 +10078,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -10071,6 +10107,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10374,7 +10411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1412"/>
+  <dimension ref="A1:P1416"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -24031,7 +24068,7 @@
       </c>
       <c r="C1408" s="6"/>
     </row>
-    <row r="1409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1409" s="2" t="s">
         <v>3301</v>
       </c>
@@ -24042,7 +24079,7 @@
         <v>3304</v>
       </c>
     </row>
-    <row r="1410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1410" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1410" s="2" t="s">
         <v>3302</v>
       </c>
@@ -24053,7 +24090,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="1411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
         <v>3306</v>
       </c>
@@ -24061,12 +24098,62 @@
         <v>3308</v>
       </c>
     </row>
-    <row r="1412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
         <v>3307</v>
       </c>
       <c r="B1412" t="s">
         <v>3309</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1413" s="2" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B1413" s="2">
+        <v>503</v>
+      </c>
+      <c r="C1413" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1414" s="2" t="s">
+        <v>3313</v>
+      </c>
+      <c r="B1414" s="2" t="s">
+        <v>3311</v>
+      </c>
+      <c r="C1414" s="2" t="s">
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1415" s="14" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B1415" s="11" t="s">
+        <v>3316</v>
+      </c>
+      <c r="C1415" s="11" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1415" s="11" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1416" s="14" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>3319</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>3321</v>
       </c>
     </row>
   </sheetData>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AF3F2A-3852-4AA1-9532-7427AE90128F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C921937-DFD2-485B-9E66-9B75490927AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="75" windowWidth="22920" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DavidSheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3603" uniqueCount="3322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="3324">
   <si>
     <t>C-VI096</t>
   </si>
@@ -10002,6 +10002,12 @@
   </si>
   <si>
     <t>Center for Fitness amd Health |Spa</t>
+  </si>
+  <si>
+    <t>Seven Springs Resort|Indoor Splash Pad</t>
+  </si>
+  <si>
+    <t>498</t>
   </si>
 </sst>
 </file>
@@ -10078,7 +10084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -10107,7 +10113,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20391,7 +20396,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="2" t="s">
         <v>2381</v>
       </c>
@@ -20416,8 +20421,11 @@
       <c r="H1041" s="2" t="s">
         <v>2388</v>
       </c>
-    </row>
-    <row r="1042" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I1041" s="13" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
         <v>2389</v>
       </c>
@@ -20442,8 +20450,11 @@
       <c r="H1042" s="2" t="s">
         <v>2396</v>
       </c>
-    </row>
-    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1042" s="2" t="s">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>2397</v>
       </c>
@@ -20451,7 +20462,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>2399</v>
       </c>
@@ -20459,7 +20470,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>2401</v>
       </c>
@@ -20470,7 +20481,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>2404</v>
       </c>
@@ -20481,7 +20492,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>202</v>
       </c>
@@ -20492,7 +20503,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>2409</v>
       </c>
@@ -20503,7 +20514,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
         <v>202</v>
       </c>
@@ -20511,7 +20522,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
         <v>2413</v>
       </c>
@@ -20519,7 +20530,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>2415</v>
       </c>
@@ -20530,7 +20541,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>2418</v>
       </c>
@@ -20541,7 +20552,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="1053" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
         <v>2421</v>
       </c>
@@ -20552,7 +20563,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="1054" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
         <v>2424</v>
       </c>
@@ -20563,7 +20574,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>2427</v>
       </c>
@@ -20580,7 +20591,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>2432</v>
       </c>
@@ -24129,7 +24140,7 @@
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1415" s="14" t="s">
+      <c r="A1415" t="s">
         <v>3314</v>
       </c>
       <c r="B1415" s="11" t="s">
@@ -24143,7 +24154,7 @@
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1416" s="14" t="s">
+      <c r="A1416" t="s">
         <v>3315</v>
       </c>
       <c r="B1416" t="s">

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AF3F2A-3852-4AA1-9532-7427AE90128F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA55F9F-01C3-467E-933A-28DBF323D99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="18000" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DavidSheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3603" uniqueCount="3322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="3328">
   <si>
     <t>C-VI096</t>
   </si>
@@ -10002,6 +10002,24 @@
   </si>
   <si>
     <t>Center for Fitness amd Health |Spa</t>
+  </si>
+  <si>
+    <t>C-NA100</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>National Aviary</t>
+  </si>
+  <si>
+    <t>Aviari|</t>
   </si>
 </sst>
 </file>
@@ -10078,7 +10096,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -10107,7 +10125,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10411,7 +10428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1416"/>
+  <dimension ref="A1:P1418"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -24129,7 +24146,7 @@
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1415" s="14" t="s">
+      <c r="A1415" t="s">
         <v>3314</v>
       </c>
       <c r="B1415" s="11" t="s">
@@ -24143,7 +24160,7 @@
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1416" s="14" t="s">
+      <c r="A1416" t="s">
         <v>3315</v>
       </c>
       <c r="B1416" t="s">
@@ -24154,6 +24171,34 @@
       </c>
       <c r="D1416" t="s">
         <v>3321</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1417" t="s">
+        <v>3322</v>
+      </c>
+      <c r="B1417" s="11" t="s">
+        <v>3323</v>
+      </c>
+      <c r="C1417" s="11" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D1417" s="11" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1418" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>3327</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>3327</v>
       </c>
     </row>
   </sheetData>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97DCAFF-D9F2-44BC-B4FB-CB93EFEE7536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15A755A-4A56-4FDB-8435-B37784A1DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="3388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3674" uniqueCount="3393">
   <si>
     <t>C-VI096</t>
   </si>
@@ -9062,12 +9062,6 @@
     <t>2578</t>
   </si>
   <si>
-    <t xml:space="preserve">White Oaks Farms  </t>
-  </si>
-  <si>
-    <t>White Oaks Farms  |Pool</t>
-  </si>
-  <si>
     <t>C-WH130</t>
   </si>
   <si>
@@ -10007,9 +10001,6 @@
     <t>Nevilleside|Pool</t>
   </si>
   <si>
-    <t>Aviary|</t>
-  </si>
-  <si>
     <t>C-HA105</t>
   </si>
   <si>
@@ -10200,6 +10191,30 @@
   </si>
   <si>
     <t>Pace Analytical|Therapy 1</t>
+  </si>
+  <si>
+    <t>T-PA100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Oak Farms  </t>
+  </si>
+  <si>
+    <t>White Oak Farms  |Pool</t>
+  </si>
+  <si>
+    <t>Aviary|Penguin</t>
+  </si>
+  <si>
+    <t>Aviary|TF Waterfall</t>
+  </si>
+  <si>
+    <t>Aviary|TF Pond</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>Aviary|Wetlands</t>
   </si>
 </sst>
 </file>
@@ -10276,7 +10291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -10299,6 +10314,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10625,18 +10641,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3222</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3224</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3223</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3225</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10827,7 +10843,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>46</v>
@@ -10871,7 +10887,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>57</v>
@@ -10941,7 +10957,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>73</v>
@@ -11043,7 +11059,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>95</v>
@@ -11073,7 +11089,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="B48" t="s">
         <v>101</v>
@@ -11303,7 +11319,7 @@
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>158</v>
@@ -11341,7 +11357,7 @@
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>167</v>
@@ -11649,7 +11665,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B111" t="s">
         <v>244</v>
@@ -11737,7 +11753,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B119" t="s">
         <v>266</v>
@@ -11967,10 +11983,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="B144" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12013,7 +12029,7 @@
     </row>
     <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>326</v>
@@ -12271,7 +12287,7 @@
     </row>
     <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>393</v>
@@ -12533,7 +12549,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B199" t="s">
         <v>460</v>
@@ -12863,7 +12879,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="B235" t="s">
         <v>533</v>
@@ -12895,7 +12911,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B239" t="s">
         <v>540</v>
@@ -12933,7 +12949,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="B243" t="s">
         <v>572</v>
@@ -12971,7 +12987,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="B247" t="s">
         <v>552</v>
@@ -13057,7 +13073,7 @@
     </row>
     <row r="257" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>580</v>
@@ -13068,7 +13084,7 @@
         <v>577</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -13084,7 +13100,7 @@
         <v>581</v>
       </c>
       <c r="B260" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="261" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13117,7 +13133,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="B263" t="s">
         <v>585</v>
@@ -13451,10 +13467,10 @@
     </row>
     <row r="298" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -13695,7 +13711,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="B327" t="s">
         <v>721</v>
@@ -14151,7 +14167,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="B375" t="s">
         <v>831</v>
@@ -14189,7 +14205,7 @@
         <v>839</v>
       </c>
       <c r="C379" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -14291,7 +14307,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B391" t="s">
         <v>855</v>
@@ -14377,7 +14393,7 @@
     </row>
     <row r="401" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>879</v>
@@ -14433,15 +14449,15 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
       <c r="B408" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="409" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>891</v>
@@ -14581,7 +14597,7 @@
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>919</v>
@@ -15068,7 +15084,7 @@
         <v>1041</v>
       </c>
       <c r="B475" s="10" t="s">
-        <v>3362</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -15177,7 +15193,7 @@
     </row>
     <row r="489" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>1069</v>
@@ -15249,7 +15265,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B495" t="s">
         <v>1082</v>
@@ -15987,7 +16003,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B579" t="s">
         <v>1258</v>
@@ -16243,7 +16259,7 @@
     </row>
     <row r="605" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>1306</v>
@@ -16607,7 +16623,7 @@
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>1392</v>
@@ -16829,7 +16845,7 @@
     </row>
     <row r="673" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>1447</v>
@@ -17043,7 +17059,7 @@
     </row>
     <row r="693" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>1497</v>
@@ -17147,7 +17163,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="B703" t="s">
         <v>1524</v>
@@ -17547,7 +17563,7 @@
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>1623</v>
@@ -17691,7 +17707,7 @@
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="B756" t="s">
         <v>1651</v>
@@ -17815,7 +17831,7 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B767" t="s">
         <v>1685</v>
@@ -17977,7 +17993,7 @@
     </row>
     <row r="785" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>1725</v>
@@ -18033,7 +18049,7 @@
     </row>
     <row r="789" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>1734</v>
@@ -18109,7 +18125,7 @@
     </row>
     <row r="797" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="B797" s="2" t="s">
         <v>1758</v>
@@ -18403,7 +18419,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B827" t="s">
         <v>1833</v>
@@ -18585,10 +18601,10 @@
     </row>
     <row r="846" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
@@ -18617,10 +18633,10 @@
     </row>
     <row r="850" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.25">
@@ -18911,7 +18927,7 @@
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B883" t="s">
         <v>1949</v>
@@ -18949,7 +18965,7 @@
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B887" t="s">
         <v>1958</v>
@@ -18971,7 +18987,7 @@
     </row>
     <row r="889" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>1963</v>
@@ -19065,7 +19081,7 @@
     </row>
     <row r="897" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>1988</v>
@@ -19247,7 +19263,7 @@
     </row>
     <row r="913" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>2031</v>
@@ -19403,7 +19419,7 @@
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B931" t="s">
         <v>2068</v>
@@ -19475,7 +19491,7 @@
     </row>
     <row r="937" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>2087</v>
@@ -19823,7 +19839,7 @@
     </row>
     <row r="973" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B973" s="2" t="s">
         <v>2175</v>
@@ -20121,7 +20137,7 @@
     </row>
     <row r="1005" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1005" s="2" t="s">
         <v>2244</v>
@@ -20423,7 +20439,7 @@
     </row>
     <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1027" t="s">
         <v>2326</v>
@@ -20445,7 +20461,7 @@
     </row>
     <row r="1029" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B1029" s="2" t="s">
         <v>2331</v>
@@ -20514,7 +20530,7 @@
         <v>2348</v>
       </c>
       <c r="B1035" s="10" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
       <c r="C1035" s="10"/>
     </row>
@@ -20608,7 +20624,7 @@
         <v>2374</v>
       </c>
       <c r="I1041" s="11" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="1042" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20634,7 +20650,7 @@
         <v>2381</v>
       </c>
       <c r="H1042" s="2" t="s">
-        <v>3361</v>
+        <v>3358</v>
       </c>
       <c r="I1042" s="2" t="s">
         <v>2382</v>
@@ -20796,7 +20812,7 @@
     </row>
     <row r="1057" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1057" s="2" t="s">
         <v>2423</v>
@@ -21418,7 +21434,7 @@
     </row>
     <row r="1125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1125" s="2" t="s">
         <v>2576</v>
@@ -22146,7 +22162,7 @@
     </row>
     <row r="1201" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1201" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B1201" s="2" t="s">
         <v>2741</v>
@@ -22484,7 +22500,7 @@
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>3363</v>
+        <v>3360</v>
       </c>
       <c r="B1232" t="s">
         <v>2837</v>
@@ -22664,7 +22680,7 @@
     </row>
     <row r="1253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1253" s="2" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="B1253" s="2" t="s">
         <v>2880</v>
@@ -22960,7 +22976,7 @@
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="B1287" t="s">
         <v>2944</v>
@@ -23026,7 +23042,7 @@
     </row>
     <row r="1293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1293" s="2" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1293" s="2" t="s">
         <v>2961</v>
@@ -23064,7 +23080,7 @@
     </row>
     <row r="1297" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1297" s="2" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B1297" s="2" t="s">
         <v>2973</v>
@@ -23124,7 +23140,7 @@
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1303" t="s">
         <v>2987</v>
@@ -23186,43 +23202,43 @@
     </row>
     <row r="1310" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1310" s="2" t="s">
-        <v>3008</v>
+        <v>3386</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>3009</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C1311" t="s">
         <v>3010</v>
       </c>
-      <c r="B1311" t="s">
+      <c r="D1311" t="s">
         <v>3011</v>
-      </c>
-      <c r="C1311" t="s">
-        <v>3012</v>
-      </c>
-      <c r="D1311" t="s">
-        <v>3013</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1312" t="s">
         <v>3014</v>
       </c>
-      <c r="B1312" t="s">
+      <c r="D1312" t="s">
         <v>3015</v>
-      </c>
-      <c r="C1312" t="s">
-        <v>3016</v>
-      </c>
-      <c r="D1312" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="1313" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="2" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="B1313" s="2" t="s">
         <v>2989</v>
@@ -23236,7 +23252,7 @@
     </row>
     <row r="1314" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="2" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="B1314" s="2" t="s">
         <v>2995</v>
@@ -23250,12 +23266,12 @@
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="1317" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23263,371 +23279,371 @@
         <v>8</v>
       </c>
       <c r="B1317" s="2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C1317" s="2" t="s">
+        <v>3021</v>
+      </c>
+      <c r="D1317" s="2" t="s">
         <v>3022</v>
-      </c>
-      <c r="C1317" s="2" t="s">
-        <v>3023</v>
-      </c>
-      <c r="D1317" s="2" t="s">
-        <v>3024</v>
       </c>
     </row>
     <row r="1318" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1318" s="2" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="B1318" s="2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C1318" s="2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D1318" s="2" t="s">
         <v>3025</v>
-      </c>
-      <c r="C1318" s="2" t="s">
-        <v>3026</v>
-      </c>
-      <c r="D1318" s="2" t="s">
-        <v>3027</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>3027</v>
+      </c>
+      <c r="C1319" t="s">
         <v>3028</v>
       </c>
-      <c r="B1319" t="s">
+      <c r="D1319" t="s">
         <v>3029</v>
-      </c>
-      <c r="C1319" t="s">
-        <v>3030</v>
-      </c>
-      <c r="D1319" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C1320" t="s">
         <v>3032</v>
       </c>
-      <c r="B1320" t="s">
+      <c r="D1320" t="s">
         <v>3033</v>
-      </c>
-      <c r="C1320" t="s">
-        <v>3034</v>
-      </c>
-      <c r="D1320" t="s">
-        <v>3035</v>
       </c>
     </row>
     <row r="1321" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1321" s="2" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="1322" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1322" s="2" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="B1323" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="B1324" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="1325" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1325" s="2" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="B1325" s="2" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C1325" s="2" t="s">
+        <v>3040</v>
+      </c>
+      <c r="D1325" s="2" t="s">
         <v>3041</v>
-      </c>
-      <c r="C1325" s="2" t="s">
-        <v>3042</v>
-      </c>
-      <c r="D1325" s="2" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="1326" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1326" s="2" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="B1326" s="2" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C1326" s="2" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D1326" s="2" t="s">
         <v>3046</v>
-      </c>
-      <c r="C1326" s="2" t="s">
-        <v>3047</v>
-      </c>
-      <c r="D1326" s="2" t="s">
-        <v>3048</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="B1327" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="B1328" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1329" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1329" s="2" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B1329" s="2" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C1329" s="2" t="s">
         <v>3055</v>
       </c>
-      <c r="B1329" s="2" t="s">
+      <c r="D1329" s="2" t="s">
         <v>3056</v>
-      </c>
-      <c r="C1329" s="2" t="s">
-        <v>3057</v>
-      </c>
-      <c r="D1329" s="2" t="s">
-        <v>3058</v>
       </c>
     </row>
     <row r="1330" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1330" s="2" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B1330" s="2" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C1330" s="2" t="s">
         <v>3059</v>
       </c>
-      <c r="B1330" s="2" t="s">
-        <v>3060</v>
-      </c>
-      <c r="C1330" s="2" t="s">
-        <v>3061</v>
-      </c>
       <c r="D1330" s="2" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="B1331" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="B1332" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="1333" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1333" s="2" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1333" s="2" t="s">
+        <v>3067</v>
+      </c>
+      <c r="C1333" s="2" t="s">
         <v>3068</v>
       </c>
-      <c r="B1333" s="2" t="s">
+      <c r="D1333" s="2" t="s">
         <v>3069</v>
-      </c>
-      <c r="C1333" s="2" t="s">
-        <v>3070</v>
-      </c>
-      <c r="D1333" s="2" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="1334" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1334" s="2" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B1334" s="2" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C1334" s="2" t="s">
         <v>3072</v>
       </c>
-      <c r="B1334" s="2" t="s">
+      <c r="D1334" s="2" t="s">
         <v>3073</v>
-      </c>
-      <c r="C1334" s="2" t="s">
-        <v>3074</v>
-      </c>
-      <c r="D1334" s="2" t="s">
-        <v>3075</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>3075</v>
+      </c>
+      <c r="C1335" t="s">
         <v>3076</v>
-      </c>
-      <c r="B1335" t="s">
-        <v>3077</v>
-      </c>
-      <c r="C1335" t="s">
-        <v>3078</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C1336" t="s">
         <v>3079</v>
-      </c>
-      <c r="B1336" t="s">
-        <v>3080</v>
-      </c>
-      <c r="C1336" t="s">
-        <v>3081</v>
       </c>
     </row>
     <row r="1337" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1337" s="2" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="B1337" s="2" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1338" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1338" s="2" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1339" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="B1339" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="1340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="B1340" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="1341" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1341" s="2" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B1341" s="2" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C1341" s="2" t="s">
         <v>3088</v>
-      </c>
-      <c r="B1341" s="2" t="s">
-        <v>3089</v>
-      </c>
-      <c r="C1341" s="2" t="s">
-        <v>3090</v>
       </c>
     </row>
     <row r="1342" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1342" s="2" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B1342" s="2" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C1342" s="2" t="s">
         <v>3091</v>
-      </c>
-      <c r="B1342" s="2" t="s">
-        <v>3092</v>
-      </c>
-      <c r="C1342" s="2" t="s">
-        <v>3093</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="B1343" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="1344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="B1344" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1345" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1345" s="2" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="1346" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1346" s="2" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="B1346" s="2" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1347" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C1347" t="s">
         <v>3100</v>
-      </c>
-      <c r="B1347" t="s">
-        <v>3101</v>
-      </c>
-      <c r="C1347" t="s">
-        <v>3102</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1348" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1348" t="s">
         <v>3104</v>
-      </c>
-      <c r="B1348" t="s">
-        <v>3105</v>
-      </c>
-      <c r="C1348" t="s">
-        <v>3106</v>
       </c>
     </row>
     <row r="1349" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1349" s="2" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1350" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1350" s="2" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1351" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C1351" t="s">
         <v>3110</v>
       </c>
-      <c r="B1351" t="s">
+      <c r="D1351" t="s">
         <v>3111</v>
-      </c>
-      <c r="C1351" t="s">
-        <v>3112</v>
-      </c>
-      <c r="D1351" t="s">
-        <v>3113</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1352" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1352" t="s">
         <v>3114</v>
       </c>
-      <c r="B1352" t="s">
+      <c r="D1352" t="s">
         <v>3115</v>
-      </c>
-      <c r="C1352" t="s">
-        <v>3116</v>
-      </c>
-      <c r="D1352" t="s">
-        <v>3117</v>
       </c>
     </row>
     <row r="1353" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23635,343 +23651,343 @@
         <v>8</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="C1353" s="2" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="1354" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1354" s="2" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B1354" s="2" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1354" s="2" t="s">
         <v>3120</v>
-      </c>
-      <c r="B1354" s="2" t="s">
-        <v>3121</v>
-      </c>
-      <c r="C1354" s="2" t="s">
-        <v>3122</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1355" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="B1355" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1356" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="B1356" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="1357" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1357" s="2" t="s">
+        <v>3125</v>
+      </c>
+      <c r="B1357" s="2" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C1357" s="2" t="s">
         <v>3127</v>
-      </c>
-      <c r="B1357" s="2" t="s">
-        <v>3128</v>
-      </c>
-      <c r="C1357" s="2" t="s">
-        <v>3129</v>
       </c>
     </row>
     <row r="1358" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="2" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1358" s="2" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1358" s="2" t="s">
         <v>3130</v>
-      </c>
-      <c r="B1358" s="2" t="s">
-        <v>3131</v>
-      </c>
-      <c r="C1358" s="2" t="s">
-        <v>3132</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1359" t="s">
         <v>3133</v>
       </c>
-      <c r="B1359" t="s">
+      <c r="D1359" t="s">
         <v>3134</v>
-      </c>
-      <c r="C1359" t="s">
-        <v>3135</v>
-      </c>
-      <c r="D1359" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1360" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1360" t="s">
         <v>3137</v>
       </c>
-      <c r="B1360" t="s">
+      <c r="D1360" t="s">
         <v>3138</v>
-      </c>
-      <c r="C1360" t="s">
-        <v>3139</v>
-      </c>
-      <c r="D1360" t="s">
-        <v>3140</v>
       </c>
     </row>
     <row r="1361" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1361" s="2" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B1361" s="2" t="s">
+        <v>3140</v>
+      </c>
+      <c r="C1361" s="2" t="s">
         <v>3141</v>
       </c>
-      <c r="B1361" s="2" t="s">
+      <c r="D1361" s="2" t="s">
         <v>3142</v>
       </c>
-      <c r="C1361" s="2" t="s">
+      <c r="E1361" s="2" t="s">
         <v>3143</v>
       </c>
-      <c r="D1361" s="2" t="s">
+      <c r="F1361" s="2" t="s">
         <v>3144</v>
       </c>
-      <c r="E1361" s="2" t="s">
+      <c r="G1361" s="2" t="s">
         <v>3145</v>
-      </c>
-      <c r="F1361" s="2" t="s">
-        <v>3146</v>
-      </c>
-      <c r="G1361" s="2" t="s">
-        <v>3147</v>
       </c>
     </row>
     <row r="1362" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1362" s="2" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B1362" s="2" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1362" s="2" t="s">
         <v>3148</v>
       </c>
-      <c r="B1362" s="2" t="s">
+      <c r="D1362" s="2" t="s">
         <v>3149</v>
       </c>
-      <c r="C1362" s="2" t="s">
+      <c r="E1362" s="2" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F1362" s="2" t="s">
         <v>3150</v>
       </c>
-      <c r="D1362" s="2" t="s">
+      <c r="G1362" s="2" t="s">
         <v>3151</v>
-      </c>
-      <c r="E1362" s="2" t="s">
-        <v>3149</v>
-      </c>
-      <c r="F1362" s="2" t="s">
-        <v>3152</v>
-      </c>
-      <c r="G1362" s="2" t="s">
-        <v>3153</v>
       </c>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1363" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1363" t="s">
         <v>3154</v>
       </c>
-      <c r="B1363" t="s">
+      <c r="D1363" t="s">
         <v>3155</v>
       </c>
-      <c r="C1363" t="s">
+      <c r="E1363" t="s">
         <v>3156</v>
-      </c>
-      <c r="D1363" t="s">
-        <v>3157</v>
-      </c>
-      <c r="E1363" t="s">
-        <v>3158</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1364" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>3158</v>
+      </c>
+      <c r="C1364" t="s">
         <v>3159</v>
       </c>
-      <c r="B1364" t="s">
+      <c r="D1364" t="s">
         <v>3160</v>
       </c>
-      <c r="C1364" t="s">
+      <c r="E1364" t="s">
         <v>3161</v>
-      </c>
-      <c r="D1364" t="s">
-        <v>3162</v>
-      </c>
-      <c r="E1364" t="s">
-        <v>3163</v>
       </c>
     </row>
     <row r="1365" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1365" s="2" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="B1365" s="2" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="1366" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1366" s="2" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1367" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>3167</v>
+      </c>
+      <c r="C1367" t="s">
         <v>3168</v>
       </c>
-      <c r="B1367" t="s">
+      <c r="D1367" t="s">
         <v>3169</v>
       </c>
-      <c r="C1367" t="s">
+      <c r="E1367" t="s">
         <v>3170</v>
-      </c>
-      <c r="D1367" t="s">
-        <v>3171</v>
-      </c>
-      <c r="E1367" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1368" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C1368" t="s">
         <v>3173</v>
       </c>
-      <c r="B1368" t="s">
+      <c r="D1368" t="s">
         <v>3174</v>
       </c>
-      <c r="C1368" t="s">
+      <c r="E1368" t="s">
         <v>3175</v>
-      </c>
-      <c r="D1368" t="s">
-        <v>3176</v>
-      </c>
-      <c r="E1368" t="s">
-        <v>3177</v>
       </c>
     </row>
     <row r="1369" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1369" s="2" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B1369" s="2" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="1370" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="2" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1371" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B1371" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1372" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="B1372" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="1373" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1373" s="2" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="C1373" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="1374" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1374" s="2" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="B1374" s="2" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="C1374" s="2" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1375" t="s">
+        <v>3190</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>3191</v>
+      </c>
+      <c r="C1375" t="s">
         <v>3192</v>
-      </c>
-      <c r="B1375" t="s">
-        <v>3193</v>
-      </c>
-      <c r="C1375" t="s">
-        <v>3194</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1376" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>3194</v>
+      </c>
+      <c r="C1376" t="s">
         <v>3195</v>
-      </c>
-      <c r="B1376" t="s">
-        <v>3196</v>
-      </c>
-      <c r="C1376" t="s">
-        <v>3197</v>
       </c>
     </row>
     <row r="1377" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1377" s="2" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B1377" s="2" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C1377" s="2" t="s">
         <v>3198</v>
       </c>
-      <c r="B1377" s="2" t="s">
+      <c r="D1377" s="2" t="s">
         <v>3199</v>
-      </c>
-      <c r="C1377" s="2" t="s">
-        <v>3200</v>
-      </c>
-      <c r="D1377" s="2" t="s">
-        <v>3201</v>
       </c>
     </row>
     <row r="1378" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1378" s="2" t="s">
+        <v>3202</v>
+      </c>
+      <c r="B1378" s="2" t="s">
+        <v>3203</v>
+      </c>
+      <c r="C1378" s="2" t="s">
         <v>3204</v>
       </c>
-      <c r="B1378" s="2" t="s">
+      <c r="D1378" s="2" t="s">
         <v>3205</v>
-      </c>
-      <c r="C1378" s="2" t="s">
-        <v>3206</v>
-      </c>
-      <c r="D1378" s="2" t="s">
-        <v>3207</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1379" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="B1379" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="C1379" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1380" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="B1380" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="C1380" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="1381" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -23979,165 +23995,165 @@
         <v>8</v>
       </c>
       <c r="B1381" s="8" t="s">
-        <v>3336</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="1382" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1382" s="4" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="B1382" s="4" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1383" s="6" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="B1383" s="9" t="s">
-        <v>3337</v>
+        <v>3334</v>
       </c>
       <c r="C1383" s="9" t="s">
-        <v>3338</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C1384" t="s">
         <v>3238</v>
-      </c>
-      <c r="B1384" t="s">
-        <v>3239</v>
-      </c>
-      <c r="C1384" t="s">
-        <v>3240</v>
       </c>
     </row>
     <row r="1385" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1385" s="4" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="B1385" s="8" t="s">
-        <v>3339</v>
+        <v>3336</v>
       </c>
       <c r="C1385" s="8" t="s">
-        <v>3340</v>
+        <v>3337</v>
       </c>
       <c r="D1385" s="8" t="s">
-        <v>3341</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="1386" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1386" s="4" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B1386" s="4" t="s">
+        <v>3241</v>
+      </c>
+      <c r="C1386" s="4" t="s">
         <v>3242</v>
       </c>
-      <c r="B1386" s="4" t="s">
+      <c r="D1386" s="4" t="s">
         <v>3243</v>
-      </c>
-      <c r="C1386" s="4" t="s">
-        <v>3244</v>
-      </c>
-      <c r="D1386" s="4" t="s">
-        <v>3245</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1387" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="B1387" s="9" t="s">
-        <v>3342</v>
+        <v>3339</v>
       </c>
       <c r="C1387" s="9" t="s">
-        <v>3343</v>
+        <v>3340</v>
       </c>
       <c r="D1387" s="9" t="s">
-        <v>3344</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1388" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C1388" t="s">
         <v>3247</v>
       </c>
-      <c r="B1388" t="s">
+      <c r="D1388" t="s">
         <v>3248</v>
-      </c>
-      <c r="C1388" t="s">
-        <v>3249</v>
-      </c>
-      <c r="D1388" t="s">
-        <v>3250</v>
       </c>
     </row>
     <row r="1389" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1389" s="4" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="B1389" s="8" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="C1389" s="8" t="s">
-        <v>3346</v>
+        <v>3343</v>
       </c>
       <c r="D1389" s="8" t="s">
-        <v>3347</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="1390" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1390" s="4" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B1390" s="4" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C1390" s="4" t="s">
         <v>3252</v>
       </c>
-      <c r="B1390" s="4" t="s">
+      <c r="D1390" s="4" t="s">
         <v>3253</v>
-      </c>
-      <c r="C1390" s="4" t="s">
-        <v>3254</v>
-      </c>
-      <c r="D1390" s="4" t="s">
-        <v>3255</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1391" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B1391" s="9" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1392" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="B1392" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="1393" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1393" s="4" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="B1393" s="8" t="s">
-        <v>3349</v>
+        <v>3346</v>
       </c>
       <c r="C1393" s="8" t="s">
-        <v>3350</v>
+        <v>3347</v>
       </c>
       <c r="D1393" s="8" t="s">
-        <v>3351</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="1394" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1394" s="4" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B1394" s="4" t="s">
+        <v>3258</v>
+      </c>
+      <c r="C1394" s="4" t="s">
         <v>3259</v>
       </c>
-      <c r="B1394" s="4" t="s">
+      <c r="D1394" s="4" t="s">
         <v>3260</v>
-      </c>
-      <c r="C1394" s="4" t="s">
-        <v>3261</v>
-      </c>
-      <c r="D1394" s="4" t="s">
-        <v>3262</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.25">
@@ -24145,31 +24161,31 @@
         <v>202</v>
       </c>
       <c r="B1395" s="9" t="s">
-        <v>3352</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="B1396" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="1397" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1397" s="4" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="B1397" s="8" t="s">
-        <v>3353</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="1398" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1398" s="4" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B1398" s="4" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.25">
@@ -24177,28 +24193,28 @@
         <v>202</v>
       </c>
       <c r="B1399" s="9" t="s">
-        <v>3354</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="B1400" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="1401" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1401" s="4" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="B1401" s="8" t="s">
-        <v>3355</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="1402" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1402" s="7" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
       <c r="B1402" s="4" t="s">
         <v>551</v>
@@ -24206,79 +24222,79 @@
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="B1403" s="9" t="s">
-        <v>3356</v>
+        <v>3353</v>
       </c>
       <c r="C1403" s="9" t="s">
-        <v>3357</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C1404" t="s">
         <v>3274</v>
-      </c>
-      <c r="B1404" t="s">
-        <v>3275</v>
-      </c>
-      <c r="C1404" t="s">
-        <v>3276</v>
       </c>
     </row>
     <row r="1405" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1405" s="4" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="B1405" s="8" t="s">
-        <v>3332</v>
+        <v>3329</v>
       </c>
       <c r="C1405" s="8" t="s">
-        <v>3333</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="1406" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1406" s="4" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B1406" s="4" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="C1406" s="4" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
       <c r="B1407" s="10" t="s">
-        <v>3280</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
-        <v>3281</v>
+        <v>3279</v>
       </c>
       <c r="B1408" s="5" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="C1408" s="5"/>
     </row>
-    <row r="1409" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1409" s="4" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B1409" s="8" t="s">
         <v>3285</v>
       </c>
-      <c r="B1409" s="8" t="s">
-        <v>3287</v>
-      </c>
       <c r="C1409" s="8" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="1410" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1410" s="4" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B1410" s="4" t="s">
         <v>1124</v>
@@ -24287,221 +24303,230 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="1411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1411" s="10" t="s">
         <v>3290</v>
       </c>
-      <c r="B1411" s="10" t="s">
+    </row>
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1412" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1413" s="4" t="s">
         <v>3292</v>
       </c>
-    </row>
-    <row r="1412" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1412" t="s">
-        <v>3291</v>
-      </c>
-      <c r="B1412" t="s">
+      <c r="B1413" s="8" t="s">
+        <v>3332</v>
+      </c>
+      <c r="C1413" s="8" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1414" s="4" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B1414" s="4" t="s">
         <v>3293</v>
       </c>
-    </row>
-    <row r="1413" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1413" s="4" t="s">
+      <c r="C1414" s="4" t="s">
         <v>3294</v>
       </c>
-      <c r="B1413" s="8" t="s">
-        <v>3335</v>
-      </c>
-      <c r="C1413" s="8" t="s">
-        <v>3334</v>
-      </c>
-    </row>
-    <row r="1414" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1414" s="4" t="s">
+    </row>
+    <row r="1415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1415" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B1415" s="10" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C1415" s="10" t="s">
+        <v>3299</v>
+      </c>
+      <c r="D1415" s="10" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1416" t="s">
         <v>3297</v>
       </c>
-      <c r="B1414" s="4" t="s">
-        <v>3295</v>
-      </c>
-      <c r="C1414" s="4" t="s">
-        <v>3296</v>
-      </c>
-    </row>
-    <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1415" t="s">
-        <v>3298</v>
-      </c>
-      <c r="B1415" s="10" t="s">
-        <v>3300</v>
-      </c>
-      <c r="C1415" s="10" t="s">
+      <c r="B1416" t="s">
         <v>3301</v>
       </c>
-      <c r="D1415" s="10" t="s">
+      <c r="C1416" t="s">
         <v>3302</v>
       </c>
-    </row>
-    <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1416" t="s">
-        <v>3299</v>
-      </c>
-      <c r="B1416" t="s">
+      <c r="D1416" t="s">
         <v>3303</v>
       </c>
-      <c r="C1416" t="s">
+    </row>
+    <row r="1417" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1417" s="4" t="s">
         <v>3304</v>
       </c>
-      <c r="D1416" t="s">
+      <c r="B1417" s="8" t="s">
         <v>3305</v>
       </c>
-    </row>
-    <row r="1417" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1417" s="4" t="s">
+      <c r="C1417" s="8" t="s">
         <v>3306</v>
       </c>
-      <c r="B1417" s="8" t="s">
+      <c r="D1417" s="4" t="s">
         <v>3307</v>
       </c>
-      <c r="C1417" s="8" t="s">
+      <c r="E1417" s="12" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1418" s="4" t="s">
         <v>3308</v>
       </c>
-      <c r="D1417" s="4" t="s">
-        <v>3309</v>
-      </c>
-    </row>
-    <row r="1418" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1418" s="4" t="s">
-        <v>3310</v>
-      </c>
       <c r="B1418" s="4" t="s">
+        <v>3388</v>
+      </c>
+      <c r="C1418" s="4" t="s">
+        <v>3389</v>
+      </c>
+      <c r="D1418" s="4" t="s">
+        <v>3390</v>
+      </c>
+      <c r="E1418" s="4" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1419" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B1419" s="10" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1420" t="s">
+        <v>3322</v>
+      </c>
+      <c r="B1420" t="s">
         <v>3323</v>
       </c>
-      <c r="C1418" s="4" t="s">
-        <v>3323</v>
-      </c>
-      <c r="D1418" s="4" t="s">
-        <v>3323</v>
-      </c>
-    </row>
-    <row r="1419" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1419" t="s">
-        <v>3324</v>
-      </c>
-      <c r="B1419" s="10" t="s">
+    </row>
+    <row r="1421" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1421" s="4" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B1421" s="8" t="s">
+        <v>3373</v>
+      </c>
+      <c r="C1421" s="8"/>
+    </row>
+    <row r="1422" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1422" s="4" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B1422" s="4" t="s">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1423" t="s">
+        <v>3361</v>
+      </c>
+      <c r="B1423" s="10" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C1423" s="10" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1424" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>3374</v>
+      </c>
+      <c r="C1424" t="s">
         <v>3375</v>
-      </c>
-    </row>
-    <row r="1420" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1420" t="s">
-        <v>3325</v>
-      </c>
-      <c r="B1420" t="s">
-        <v>3326</v>
-      </c>
-    </row>
-    <row r="1421" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1421" s="4" t="s">
-        <v>3328</v>
-      </c>
-      <c r="B1421" s="8" t="s">
-        <v>3376</v>
-      </c>
-      <c r="C1421" s="8"/>
-    </row>
-    <row r="1422" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1422" s="4" t="s">
-        <v>3329</v>
-      </c>
-      <c r="B1422" s="4" t="s">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="1423" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1423" t="s">
-        <v>3364</v>
-      </c>
-      <c r="B1423" s="10" t="s">
-        <v>3379</v>
-      </c>
-      <c r="C1423" s="10" t="s">
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="1424" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1424" t="s">
-        <v>3365</v>
-      </c>
-      <c r="B1424" t="s">
-        <v>3377</v>
-      </c>
-      <c r="C1424" t="s">
-        <v>3378</v>
       </c>
     </row>
     <row r="1425" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1425" s="4" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="B1425" s="8"/>
       <c r="C1425" s="8"/>
     </row>
     <row r="1426" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1426" s="4" t="s">
-        <v>3369</v>
+        <v>3366</v>
       </c>
       <c r="B1426" s="4" t="s">
-        <v>3371</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="1427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>3372</v>
+        <v>3369</v>
       </c>
       <c r="B1427" s="10" t="s">
-        <v>3381</v>
+        <v>3378</v>
       </c>
     </row>
     <row r="1428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
-        <v>3373</v>
+        <v>3370</v>
       </c>
       <c r="B1428" t="s">
-        <v>3374</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="1429" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1429" s="4" t="s">
+        <v>3385</v>
+      </c>
       <c r="B1429" s="8" t="s">
-        <v>3327</v>
+        <v>3324</v>
       </c>
       <c r="C1429" s="8" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="D1429" s="4" t="s">
-        <v>3366</v>
+        <v>3363</v>
       </c>
       <c r="E1429" s="4" t="s">
+        <v>3364</v>
+      </c>
+      <c r="F1429" s="4" t="s">
         <v>3367</v>
-      </c>
-      <c r="F1429" s="4" t="s">
-        <v>3370</v>
       </c>
     </row>
     <row r="1430" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1430" s="4" t="s">
+        <v>3379</v>
+      </c>
+      <c r="B1430" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="C1430" s="4" t="s">
         <v>3382</v>
       </c>
-      <c r="B1430" s="4" t="s">
+      <c r="D1430" s="4" t="s">
+        <v>3384</v>
+      </c>
+      <c r="E1430" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="F1430" s="4" t="s">
         <v>3383</v>
-      </c>
-      <c r="C1430" s="4" t="s">
-        <v>3385</v>
-      </c>
-      <c r="D1430" s="4" t="s">
-        <v>3387</v>
-      </c>
-      <c r="E1430" s="4" t="s">
-        <v>3384</v>
-      </c>
-      <c r="F1430" s="4" t="s">
-        <v>3386</v>
       </c>
     </row>
   </sheetData>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92EAA29-7BB7-4FDB-A550-0D2005925CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF82B62E-F036-4E4B-9C75-AB50CC46F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DavidSheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="3436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="3444">
   <si>
     <t>2706</t>
   </si>
@@ -10344,6 +10344,30 @@
   </si>
   <si>
     <t>Manorview Apartments</t>
+  </si>
+  <si>
+    <t>C-AM115</t>
+  </si>
+  <si>
+    <t>Amherst Village</t>
+  </si>
+  <si>
+    <t>Amherst Village|Pool</t>
+  </si>
+  <si>
+    <t>2811</t>
+  </si>
+  <si>
+    <t>C-LE100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy </t>
+  </si>
+  <si>
+    <t>Legacy | Pool</t>
+  </si>
+  <si>
+    <t>2812</t>
   </si>
 </sst>
 </file>
@@ -10747,7 +10771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1454"/>
+  <dimension ref="A1:P1458"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -24878,6 +24902,38 @@
         <v>3429</v>
       </c>
     </row>
+    <row r="1455" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1455" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B1455" s="12" t="s">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1456" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="B1456" s="4" t="s">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1457" s="10" t="s">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>3442</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF82B62E-F036-4E4B-9C75-AB50CC46F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC297FFD-2BA1-47DE-B3C6-D72E5476F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="3444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="3456">
   <si>
     <t>2706</t>
   </si>
@@ -6050,9 +6050,6 @@
     <t>Park Place Rec</t>
   </si>
   <si>
-    <t>Park Place Rec|Pool</t>
-  </si>
-  <si>
     <t>C-PA170</t>
   </si>
   <si>
@@ -6803,9 +6800,6 @@
     <t>Rodgers-McFeely |Pool</t>
   </si>
   <si>
-    <t>Rodgers-McFeely  |Baby Pool</t>
-  </si>
-  <si>
     <t>Rose Garden|Pool</t>
   </si>
   <si>
@@ -10199,9 +10193,6 @@
     <t>Nox Apts|Pool</t>
   </si>
   <si>
-    <t>T-AL100</t>
-  </si>
-  <si>
     <t>Murray Chase</t>
   </si>
   <si>
@@ -10262,15 +10253,9 @@
     <t>Hamilton Park | Splash Pad</t>
   </si>
   <si>
-    <t>C-BR235</t>
-  </si>
-  <si>
     <t>C-GR275</t>
   </si>
   <si>
-    <t>C-GR100</t>
-  </si>
-  <si>
     <t>C-HU150</t>
   </si>
   <si>
@@ -10368,6 +10353,57 @@
   </si>
   <si>
     <t>2812</t>
+  </si>
+  <si>
+    <t>T-PA110</t>
+  </si>
+  <si>
+    <t>C-WA251</t>
+  </si>
+  <si>
+    <t>Landing HOA</t>
+  </si>
+  <si>
+    <t>Landing HOA|Pool</t>
+  </si>
+  <si>
+    <t>C-LA130</t>
+  </si>
+  <si>
+    <t>Best Western Garden Inn      |Outdoor Pool</t>
+  </si>
+  <si>
+    <t>2778</t>
+  </si>
+  <si>
+    <t>Rodgers-McFeely  |Spray Pad</t>
+  </si>
+  <si>
+    <t>2813</t>
+  </si>
+  <si>
+    <t>2814</t>
+  </si>
+  <si>
+    <t>Park Place Rec|Pool 1</t>
+  </si>
+  <si>
+    <t>Park Place Rec|Pool 2</t>
+  </si>
+  <si>
+    <t>Park Place Rec|Baby Pool</t>
+  </si>
+  <si>
+    <t>C-WI000</t>
+  </si>
+  <si>
+    <t>Ken Anderson</t>
+  </si>
+  <si>
+    <t>Ken Anderson|SPA</t>
+  </si>
+  <si>
+    <t>5000</t>
   </si>
 </sst>
 </file>
@@ -10405,7 +10441,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10430,6 +10466,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -10444,7 +10486,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -10468,6 +10510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10771,7 +10814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1458"/>
+  <dimension ref="A1:P1462"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -10794,18 +10837,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3181</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3183</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3182</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3184</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10904,7 +10947,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>3392</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10996,7 +11039,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>44</v>
@@ -11040,7 +11083,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>55</v>
@@ -11110,7 +11153,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>71</v>
@@ -11212,7 +11255,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>93</v>
@@ -11242,7 +11285,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -11472,7 +11515,7 @@
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>155</v>
@@ -11510,7 +11553,7 @@
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>164</v>
@@ -11731,6 +11774,9 @@
       <c r="B101" s="2" t="s">
         <v>218</v>
       </c>
+      <c r="C101" s="11" t="s">
+        <v>3445</v>
+      </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
@@ -11739,6 +11785,9 @@
       <c r="B102" s="2" t="s">
         <v>220</v>
       </c>
+      <c r="C102" s="2" t="s">
+        <v>3444</v>
+      </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
@@ -11818,7 +11867,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B111" t="s">
         <v>241</v>
@@ -11906,7 +11955,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B119" t="s">
         <v>262</v>
@@ -11928,7 +11977,7 @@
     </row>
     <row r="121" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>3430</v>
+        <v>3425</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>267</v>
@@ -12058,7 +12107,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3408</v>
+        <v>3439</v>
       </c>
       <c r="B135" t="s">
         <v>295</v>
@@ -12136,10 +12185,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
       <c r="B144" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12182,7 +12231,7 @@
     </row>
     <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>322</v>
@@ -12440,7 +12489,7 @@
     </row>
     <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>389</v>
@@ -12702,7 +12751,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B199" t="s">
         <v>456</v>
@@ -13064,7 +13113,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B239" t="s">
         <v>536</v>
@@ -13102,7 +13151,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="B243" t="s">
         <v>568</v>
@@ -13140,7 +13189,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="B247" t="s">
         <v>548</v>
@@ -13226,7 +13275,7 @@
     </row>
     <row r="257" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>576</v>
@@ -13237,7 +13286,7 @@
         <v>573</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -13253,7 +13302,7 @@
         <v>577</v>
       </c>
       <c r="B260" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="261" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13286,7 +13335,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="B263" t="s">
         <v>581</v>
@@ -13580,7 +13629,7 @@
     </row>
     <row r="293" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>199</v>
+        <v>7</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>653</v>
@@ -13620,10 +13669,10 @@
     </row>
     <row r="298" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -13856,7 +13905,7 @@
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>3351</v>
+        <v>3349</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>715</v>
@@ -13864,7 +13913,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B327" t="s">
         <v>716</v>
@@ -14320,7 +14369,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B375" t="s">
         <v>825</v>
@@ -14358,7 +14407,7 @@
         <v>833</v>
       </c>
       <c r="C379" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -14460,7 +14509,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="B391" t="s">
         <v>849</v>
@@ -14546,7 +14595,7 @@
     </row>
     <row r="401" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>873</v>
@@ -14602,15 +14651,15 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
       <c r="B408" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="409" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>885</v>
@@ -14750,7 +14799,7 @@
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>913</v>
@@ -15237,7 +15286,7 @@
         <v>1034</v>
       </c>
       <c r="B475" s="10" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -15266,7 +15315,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>3410</v>
+        <v>3439</v>
       </c>
       <c r="B479" t="s">
         <v>1041</v>
@@ -15346,7 +15395,7 @@
     </row>
     <row r="489" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>1062</v>
@@ -15418,7 +15467,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B495" t="s">
         <v>1075</v>
@@ -15440,7 +15489,7 @@
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>1080</v>
@@ -16156,7 +16205,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B579" t="s">
         <v>1251</v>
@@ -16412,7 +16461,7 @@
     </row>
     <row r="605" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>1299</v>
@@ -16776,7 +16825,7 @@
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>1384</v>
@@ -16922,7 +16971,7 @@
     </row>
     <row r="665" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>3411</v>
+        <v>3406</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>1419</v>
@@ -16998,7 +17047,7 @@
     </row>
     <row r="673" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>1439</v>
@@ -17212,7 +17261,7 @@
     </row>
     <row r="693" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>1489</v>
@@ -17245,13 +17294,13 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>3432</v>
+        <v>3427</v>
       </c>
       <c r="B696" t="s">
-        <v>3433</v>
+        <v>3428</v>
       </c>
       <c r="C696" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="697" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17316,7 +17365,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="B703" t="s">
         <v>1513</v>
@@ -17716,7 +17765,7 @@
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>1612</v>
@@ -17860,7 +17909,7 @@
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="B756" t="s">
         <v>1640</v>
@@ -17984,7 +18033,7 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B767" t="s">
         <v>1674</v>
@@ -18036,7 +18085,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>3435</v>
+        <v>3430</v>
       </c>
       <c r="B772" t="s">
         <v>1686</v>
@@ -18146,7 +18195,7 @@
     </row>
     <row r="785" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>1713</v>
@@ -18168,7 +18217,7 @@
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>3412</v>
+        <v>3407</v>
       </c>
       <c r="B787" t="s">
         <v>1718</v>
@@ -18202,7 +18251,7 @@
     </row>
     <row r="789" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>1722</v>
@@ -18354,7 +18403,7 @@
     </row>
     <row r="805" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
-        <v>3387</v>
+        <v>199</v>
       </c>
       <c r="B805" s="2" t="s">
         <v>1765</v>
@@ -18451,13 +18500,13 @@
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B816" t="s">
+        <v>3351</v>
+      </c>
+      <c r="C816" t="s">
         <v>3352</v>
-      </c>
-      <c r="B816" t="s">
-        <v>3353</v>
-      </c>
-      <c r="C816" t="s">
-        <v>3354</v>
       </c>
     </row>
     <row r="817" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18572,7 +18621,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B827" t="s">
         <v>1818</v>
@@ -18754,15 +18803,15 @@
     </row>
     <row r="846" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>3413</v>
+        <v>3408</v>
       </c>
       <c r="B847" t="s">
         <v>1864</v>
@@ -18786,10 +18835,10 @@
     </row>
     <row r="850" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>3281</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.25">
@@ -19080,7 +19129,7 @@
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B883" t="s">
         <v>1934</v>
@@ -19118,7 +19167,7 @@
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B887" t="s">
         <v>1943</v>
@@ -19140,7 +19189,7 @@
     </row>
     <row r="889" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>1948</v>
@@ -19234,7 +19283,7 @@
     </row>
     <row r="897" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>1973</v>
@@ -19361,41 +19410,53 @@
       <c r="B907" t="s">
         <v>2002</v>
       </c>
+      <c r="C907" s="10" t="s">
+        <v>3447</v>
+      </c>
+      <c r="D907" s="10" t="s">
+        <v>3448</v>
+      </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>2003</v>
       </c>
       <c r="B908" t="s">
-        <v>2004</v>
+        <v>3449</v>
+      </c>
+      <c r="C908" t="s">
+        <v>3450</v>
+      </c>
+      <c r="D908" t="s">
+        <v>3451</v>
       </c>
     </row>
     <row r="909" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B909" s="2" t="s">
         <v>2005</v>
       </c>
-      <c r="B909" s="2" t="s">
+      <c r="C909" s="2" t="s">
         <v>2006</v>
       </c>
-      <c r="C909" s="2" t="s">
+      <c r="D909" s="2" t="s">
         <v>2007</v>
-      </c>
-      <c r="D909" s="2" t="s">
-        <v>2008</v>
       </c>
     </row>
     <row r="910" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B910" s="2" t="s">
         <v>2009</v>
       </c>
-      <c r="B910" s="2" t="s">
+      <c r="C910" s="2" t="s">
         <v>2010</v>
       </c>
-      <c r="C910" s="2" t="s">
+      <c r="D910" s="2" t="s">
         <v>2011</v>
-      </c>
-      <c r="D910" s="2" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -19403,31 +19464,31 @@
         <v>7</v>
       </c>
       <c r="B911" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B912" t="s">
         <v>2014</v>
-      </c>
-      <c r="B912" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="913" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="B913" s="2" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="914" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B914" s="2" t="s">
         <v>2017</v>
-      </c>
-      <c r="B914" s="2" t="s">
-        <v>2018</v>
       </c>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.25">
@@ -19435,123 +19496,123 @@
         <v>7</v>
       </c>
       <c r="B915" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="916" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B916" t="s">
         <v>2020</v>
-      </c>
-      <c r="B916" t="s">
-        <v>2021</v>
       </c>
     </row>
     <row r="917" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B917" s="2" t="s">
         <v>2022</v>
-      </c>
-      <c r="B917" s="2" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="918" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B918" s="2" t="s">
         <v>2024</v>
-      </c>
-      <c r="B918" s="2" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="919" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B919" t="s">
         <v>2026</v>
-      </c>
-      <c r="B919" t="s">
-        <v>2027</v>
       </c>
     </row>
     <row r="920" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B920" t="s">
         <v>2028</v>
-      </c>
-      <c r="B920" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="921" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B921" s="2" t="s">
         <v>2030</v>
-      </c>
-      <c r="B921" s="2" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="922" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B922" s="2" t="s">
         <v>2032</v>
-      </c>
-      <c r="B922" s="2" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B923" t="s">
         <v>2034</v>
-      </c>
-      <c r="B923" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="924" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B924" t="s">
         <v>2036</v>
-      </c>
-      <c r="B924" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="925" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B925" s="2" t="s">
         <v>2038</v>
-      </c>
-      <c r="B925" s="2" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="926" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B926" s="2" t="s">
         <v>2040</v>
-      </c>
-      <c r="B926" s="2" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B927" t="s">
         <v>2042</v>
       </c>
-      <c r="B927" t="s">
+      <c r="C927" t="s">
         <v>2043</v>
       </c>
-      <c r="C927" t="s">
+      <c r="D927" t="s">
         <v>2044</v>
-      </c>
-      <c r="D927" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="928" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B928" t="s">
         <v>2046</v>
       </c>
-      <c r="B928" t="s">
+      <c r="C928" t="s">
         <v>2047</v>
       </c>
-      <c r="C928" t="s">
+      <c r="D928" t="s">
         <v>2048</v>
-      </c>
-      <c r="D928" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="929" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19559,229 +19620,229 @@
         <v>7</v>
       </c>
       <c r="B929" s="2" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="930" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B930" s="2" t="s">
         <v>2051</v>
-      </c>
-      <c r="B930" s="2" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B931" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C931" t="s">
         <v>2053</v>
-      </c>
-      <c r="C931" t="s">
-        <v>2054</v>
       </c>
     </row>
     <row r="932" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B932" t="s">
         <v>2055</v>
       </c>
-      <c r="B932" t="s">
+      <c r="C932" t="s">
         <v>2056</v>
-      </c>
-      <c r="C932" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="933" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B933" s="2" t="s">
         <v>2058</v>
       </c>
-      <c r="B933" s="2" t="s">
+      <c r="C933" s="2" t="s">
         <v>2059</v>
-      </c>
-      <c r="C933" s="2" t="s">
-        <v>2060</v>
       </c>
     </row>
     <row r="934" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B934" s="2" t="s">
         <v>2061</v>
       </c>
-      <c r="B934" s="2" t="s">
+      <c r="C934" s="2" t="s">
         <v>2062</v>
-      </c>
-      <c r="C934" s="2" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="935" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B935" t="s">
         <v>2064</v>
       </c>
-      <c r="B935" t="s">
+      <c r="C935" t="s">
         <v>2065</v>
       </c>
-      <c r="C935" t="s">
+      <c r="D935" t="s">
         <v>2066</v>
-      </c>
-      <c r="D935" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B936" t="s">
         <v>2068</v>
       </c>
-      <c r="B936" t="s">
+      <c r="C936" t="s">
         <v>2069</v>
       </c>
-      <c r="C936" t="s">
+      <c r="D936" t="s">
         <v>2070</v>
-      </c>
-      <c r="D936" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="937" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B937" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C937" s="2" t="s">
         <v>2072</v>
-      </c>
-      <c r="C937" s="2" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="938" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B938" s="2" t="s">
         <v>2074</v>
       </c>
-      <c r="B938" s="2" t="s">
+      <c r="C938" s="2" t="s">
         <v>2075</v>
-      </c>
-      <c r="C938" s="2" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="939" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B939" t="s">
         <v>2077</v>
-      </c>
-      <c r="B939" t="s">
-        <v>2078</v>
       </c>
     </row>
     <row r="940" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B940" t="s">
         <v>2079</v>
-      </c>
-      <c r="B940" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="941" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B941" s="2" t="s">
         <v>2081</v>
       </c>
-      <c r="B941" s="2" t="s">
+      <c r="C941" s="2" t="s">
         <v>2082</v>
-      </c>
-      <c r="C941" s="2" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="942" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B942" s="2" t="s">
         <v>2084</v>
       </c>
-      <c r="B942" s="2" t="s">
+      <c r="C942" s="2" t="s">
         <v>2085</v>
-      </c>
-      <c r="C942" s="2" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="943" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B943" t="s">
         <v>2087</v>
-      </c>
-      <c r="B943" t="s">
-        <v>2088</v>
       </c>
     </row>
     <row r="944" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B944" t="s">
         <v>2089</v>
-      </c>
-      <c r="B944" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="945" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B945" s="2" t="s">
         <v>2091</v>
       </c>
-      <c r="B945" s="2" t="s">
+      <c r="C945" s="2" t="s">
         <v>2092</v>
-      </c>
-      <c r="C945" s="2" t="s">
-        <v>2093</v>
       </c>
     </row>
     <row r="946" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B946" s="2" t="s">
         <v>2094</v>
       </c>
-      <c r="B946" s="2" t="s">
+      <c r="C946" s="2" t="s">
         <v>2095</v>
-      </c>
-      <c r="C946" s="2" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="947" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B947" t="s">
         <v>2097</v>
-      </c>
-      <c r="B947" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="948" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B948" t="s">
         <v>2099</v>
-      </c>
-      <c r="B948" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="949" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B949" s="2" t="s">
         <v>2101</v>
       </c>
-      <c r="B949" s="2" t="s">
+      <c r="C949" s="2" t="s">
         <v>2102</v>
       </c>
-      <c r="C949" s="2" t="s">
+      <c r="D949" s="2" t="s">
         <v>2103</v>
-      </c>
-      <c r="D949" s="2" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="950" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B950" s="2" t="s">
         <v>2105</v>
       </c>
-      <c r="B950" s="2" t="s">
+      <c r="C950" s="2" t="s">
         <v>2106</v>
       </c>
-      <c r="C950" s="2" t="s">
+      <c r="D950" s="2" t="s">
         <v>2107</v>
-      </c>
-      <c r="D950" s="2" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="951" spans="1:4" x14ac:dyDescent="0.25">
@@ -19789,81 +19850,81 @@
         <v>7</v>
       </c>
       <c r="B951" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="952" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B952" t="s">
         <v>2110</v>
-      </c>
-      <c r="B952" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="953" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B953" s="2" t="s">
         <v>2112</v>
       </c>
-      <c r="B953" s="2" t="s">
+      <c r="C953" s="2" t="s">
         <v>2113</v>
-      </c>
-      <c r="C953" s="2" t="s">
-        <v>2114</v>
       </c>
     </row>
     <row r="954" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B954" s="2" t="s">
         <v>2115</v>
       </c>
-      <c r="B954" s="2" t="s">
+      <c r="C954" s="2" t="s">
         <v>2116</v>
-      </c>
-      <c r="C954" s="2" t="s">
-        <v>2117</v>
       </c>
     </row>
     <row r="955" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B955" t="s">
         <v>2118</v>
-      </c>
-      <c r="B955" t="s">
-        <v>2119</v>
       </c>
     </row>
     <row r="956" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B956" t="s">
         <v>2120</v>
-      </c>
-      <c r="B956" t="s">
-        <v>2121</v>
       </c>
     </row>
     <row r="957" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B957" s="2" t="s">
         <v>2122</v>
       </c>
-      <c r="B957" s="2" t="s">
+      <c r="C957" s="2" t="s">
         <v>2123</v>
       </c>
-      <c r="C957" s="2" t="s">
+      <c r="D957" s="2" t="s">
         <v>2124</v>
-      </c>
-      <c r="D957" s="2" t="s">
-        <v>2125</v>
       </c>
     </row>
     <row r="958" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B958" s="2" t="s">
         <v>2126</v>
       </c>
-      <c r="B958" s="2" t="s">
+      <c r="C958" s="2" t="s">
         <v>2127</v>
       </c>
-      <c r="C958" s="2" t="s">
+      <c r="D958" s="2" t="s">
         <v>2128</v>
-      </c>
-      <c r="D958" s="2" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="959" spans="1:4" x14ac:dyDescent="0.25">
@@ -19871,15 +19932,15 @@
         <v>7</v>
       </c>
       <c r="B959" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="960" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>3401</v>
+        <v>3398</v>
       </c>
       <c r="B960" t="s">
-        <v>3402</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="961" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19887,80 +19948,80 @@
         <v>7</v>
       </c>
       <c r="B961" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C961" s="2" t="s">
         <v>2131</v>
-      </c>
-      <c r="C961" s="2" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="962" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B962" s="2" t="s">
         <v>2133</v>
       </c>
-      <c r="B962" s="2" t="s">
+      <c r="C962" s="2" t="s">
         <v>2134</v>
-      </c>
-      <c r="C962" s="2" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="963" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B963" t="s">
         <v>2136</v>
-      </c>
-      <c r="B963" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="964" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B964" t="s">
         <v>2138</v>
-      </c>
-      <c r="B964" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="965" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B965" s="2" t="s">
         <v>2140</v>
       </c>
-      <c r="B965" s="2" t="s">
+      <c r="C965" s="2" t="s">
         <v>2141</v>
-      </c>
-      <c r="C965" s="2" t="s">
-        <v>2142</v>
       </c>
     </row>
     <row r="966" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B966" s="2" t="s">
         <v>2143</v>
       </c>
-      <c r="B966" s="2" t="s">
+      <c r="C966" s="2" t="s">
         <v>2144</v>
-      </c>
-      <c r="C966" s="2" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="967" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B967" t="s">
         <v>2146</v>
-      </c>
-      <c r="B967" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="968" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B968" t="s">
         <v>2148</v>
-      </c>
-      <c r="B968" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="969" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B969" s="3">
         <v>2785</v>
@@ -19968,64 +20029,64 @@
     </row>
     <row r="970" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B970" s="2" t="s">
         <v>2152</v>
-      </c>
-      <c r="B970" s="2" t="s">
-        <v>2153</v>
       </c>
     </row>
     <row r="971" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B971" t="s">
         <v>2154</v>
-      </c>
-      <c r="B971" t="s">
-        <v>2155</v>
       </c>
     </row>
     <row r="972" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B972" t="s">
         <v>2156</v>
-      </c>
-      <c r="B972" t="s">
-        <v>2157</v>
       </c>
     </row>
     <row r="973" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B973" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C973" s="2" t="s">
         <v>2158</v>
-      </c>
-      <c r="C973" s="2" t="s">
-        <v>2159</v>
       </c>
     </row>
     <row r="974" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B974" s="2" t="s">
         <v>2160</v>
       </c>
-      <c r="B974" s="2" t="s">
+      <c r="C974" s="2" t="s">
         <v>2161</v>
-      </c>
-      <c r="C974" s="2" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="975" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B975" t="s">
         <v>2163</v>
-      </c>
-      <c r="B975" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="976" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B976" t="s">
         <v>2165</v>
-      </c>
-      <c r="B976" t="s">
-        <v>2166</v>
       </c>
     </row>
     <row r="977" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20033,37 +20094,37 @@
         <v>7</v>
       </c>
       <c r="B977" s="2" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="978" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B978" s="2" t="s">
         <v>2168</v>
-      </c>
-      <c r="B978" s="2" t="s">
-        <v>2169</v>
       </c>
     </row>
     <row r="979" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B979" t="s">
         <v>2170</v>
       </c>
-      <c r="B979" t="s">
+      <c r="C979" t="s">
         <v>2171</v>
-      </c>
-      <c r="C979" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B980" t="s">
         <v>2174</v>
       </c>
-      <c r="B980" t="s">
+      <c r="C980" t="s">
         <v>2175</v>
-      </c>
-      <c r="C980" t="s">
-        <v>2176</v>
       </c>
     </row>
     <row r="981" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20071,15 +20132,15 @@
         <v>7</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="982" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B982" s="2" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="983" spans="1:3" x14ac:dyDescent="0.25">
@@ -20087,113 +20148,113 @@
         <v>7</v>
       </c>
       <c r="B983" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="984" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B984" t="s">
         <v>2180</v>
-      </c>
-      <c r="B984" t="s">
-        <v>2181</v>
       </c>
     </row>
     <row r="985" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B985" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C985" s="2" t="s">
         <v>2189</v>
-      </c>
-      <c r="C985" s="2" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="986" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B986" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C986" s="2" t="s">
         <v>2193</v>
-      </c>
-      <c r="C986" s="2" t="s">
-        <v>2194</v>
       </c>
     </row>
     <row r="987" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B987" t="s">
         <v>2184</v>
-      </c>
-      <c r="B987" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="988" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B988" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="989" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B989" s="2" t="s">
         <v>2187</v>
-      </c>
-      <c r="B989" s="2" t="s">
-        <v>2188</v>
       </c>
     </row>
     <row r="990" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B990" s="2" t="s">
         <v>2191</v>
-      </c>
-      <c r="B990" s="2" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B991" t="s">
         <v>2195</v>
-      </c>
-      <c r="B991" t="s">
-        <v>2196</v>
       </c>
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B992" t="s">
         <v>2197</v>
-      </c>
-      <c r="B992" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="993" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B993" s="2" t="s">
         <v>2199</v>
       </c>
-      <c r="B993" s="2" t="s">
+      <c r="C993" s="2" t="s">
         <v>2200</v>
       </c>
-      <c r="C993" s="2" t="s">
+      <c r="D993" s="2" t="s">
         <v>2201</v>
-      </c>
-      <c r="D993" s="2" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="994" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B994" s="2" t="s">
         <v>2204</v>
       </c>
-      <c r="B994" s="2" t="s">
+      <c r="C994" s="2" t="s">
         <v>2205</v>
       </c>
-      <c r="C994" s="2" t="s">
+      <c r="D994" s="2" t="s">
         <v>2206</v>
-      </c>
-      <c r="D994" s="2" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="995" spans="1:4" x14ac:dyDescent="0.25">
@@ -20201,31 +20262,31 @@
         <v>7</v>
       </c>
       <c r="B995" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="996" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B996" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="997" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B997" s="2" t="s">
         <v>2210</v>
-      </c>
-      <c r="B997" s="2" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="998" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B998" s="2" t="s">
         <v>2212</v>
-      </c>
-      <c r="B998" s="2" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="999" spans="1:4" x14ac:dyDescent="0.25">
@@ -20233,21 +20294,21 @@
         <v>7</v>
       </c>
       <c r="B999" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C999" t="s">
         <v>2214</v>
-      </c>
-      <c r="C999" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="1000" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1000" t="s">
         <v>2216</v>
       </c>
-      <c r="B1000" t="s">
+      <c r="C1000" t="s">
         <v>2217</v>
-      </c>
-      <c r="C1000" t="s">
-        <v>2218</v>
       </c>
     </row>
     <row r="1001" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20255,21 +20316,21 @@
         <v>199</v>
       </c>
       <c r="B1001" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C1001" s="2" t="s">
         <v>2219</v>
-      </c>
-      <c r="C1001" s="2" t="s">
-        <v>2220</v>
       </c>
     </row>
     <row r="1002" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1002" s="2" t="s">
         <v>2221</v>
       </c>
-      <c r="B1002" s="2" t="s">
+      <c r="C1002" s="2" t="s">
         <v>2222</v>
-      </c>
-      <c r="C1002" s="2" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="1003" spans="1:4" x14ac:dyDescent="0.25">
@@ -20277,119 +20338,119 @@
         <v>7</v>
       </c>
       <c r="B1003" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1004" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1004" t="s">
         <v>2225</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>2226</v>
       </c>
     </row>
     <row r="1005" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1005" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C1005" s="2" t="s">
         <v>2227</v>
-      </c>
-      <c r="C1005" s="2" t="s">
-        <v>2228</v>
       </c>
     </row>
     <row r="1006" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B1006" s="2" t="s">
         <v>2229</v>
       </c>
-      <c r="B1006" s="2" t="s">
+      <c r="C1006" s="2" t="s">
         <v>2230</v>
-      </c>
-      <c r="C1006" s="2" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="1007" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1007" t="s">
         <v>2232</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>2233</v>
       </c>
     </row>
     <row r="1008" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1008" t="s">
         <v>2234</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="1009" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1009" s="2" t="s">
         <v>2236</v>
       </c>
-      <c r="B1009" s="2" t="s">
+      <c r="C1009" s="2" t="s">
         <v>2237</v>
-      </c>
-      <c r="C1009" s="2" t="s">
-        <v>2238</v>
       </c>
     </row>
     <row r="1010" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1010" s="2" t="s">
         <v>2241</v>
       </c>
-      <c r="B1010" s="2" t="s">
+      <c r="C1010" s="2" t="s">
         <v>2242</v>
-      </c>
-      <c r="C1010" s="2" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="1011" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B1011" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C1011" t="s">
         <v>2239</v>
-      </c>
-      <c r="C1011" t="s">
-        <v>2240</v>
       </c>
     </row>
     <row r="1012" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="B1012" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C1012" t="s">
         <v>2244</v>
-      </c>
-      <c r="C1012" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="1013" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1013" s="2" t="s">
         <v>2248</v>
       </c>
-      <c r="B1013" s="2" t="s">
+      <c r="C1013" s="2" t="s">
         <v>2249</v>
-      </c>
-      <c r="C1013" s="2" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="1014" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1014" s="2" t="s">
         <v>2253</v>
       </c>
-      <c r="B1014" s="2" t="s">
-        <v>2254</v>
-      </c>
       <c r="C1014" s="2" t="s">
-        <v>2255</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="1015" spans="1:16" x14ac:dyDescent="0.25">
@@ -20397,181 +20458,181 @@
         <v>7</v>
       </c>
       <c r="B1015" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C1015" t="s">
         <v>2251</v>
-      </c>
-      <c r="C1015" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="1016" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="B1016" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C1016" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1017" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B1017" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C1017" s="2" t="s">
         <v>2259</v>
-      </c>
-      <c r="B1017" s="2" t="s">
-        <v>2260</v>
-      </c>
-      <c r="C1017" s="2" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="1018" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1018" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C1018" s="2" t="s">
         <v>2262</v>
-      </c>
-      <c r="B1018" s="2" t="s">
-        <v>2263</v>
-      </c>
-      <c r="C1018" s="2" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="1019" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="B1019" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1020" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="B1020" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1021" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1021" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C1021" s="2" t="s">
         <v>2269</v>
-      </c>
-      <c r="B1021" s="2" t="s">
-        <v>2270</v>
-      </c>
-      <c r="C1021" s="2" t="s">
-        <v>2271</v>
       </c>
     </row>
     <row r="1022" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1022" s="2" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1022" s="2" t="s">
         <v>2272</v>
-      </c>
-      <c r="B1022" s="2" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C1022" s="2" t="s">
-        <v>2274</v>
       </c>
     </row>
     <row r="1023" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C1023" t="s">
         <v>2275</v>
       </c>
-      <c r="B1023" t="s">
+      <c r="D1023" t="s">
         <v>2276</v>
       </c>
-      <c r="C1023" t="s">
+      <c r="E1023" t="s">
         <v>2277</v>
       </c>
-      <c r="D1023" t="s">
+      <c r="F1023" t="s">
         <v>2278</v>
       </c>
-      <c r="E1023" t="s">
+      <c r="G1023" t="s">
         <v>2279</v>
       </c>
-      <c r="F1023" t="s">
+      <c r="H1023" t="s">
         <v>2280</v>
       </c>
-      <c r="G1023" t="s">
+      <c r="I1023" t="s">
         <v>2281</v>
       </c>
-      <c r="H1023" t="s">
+      <c r="J1023" t="s">
         <v>2282</v>
       </c>
-      <c r="I1023" t="s">
+      <c r="K1023" t="s">
         <v>2283</v>
       </c>
-      <c r="J1023" t="s">
+      <c r="L1023" t="s">
         <v>2284</v>
       </c>
-      <c r="K1023" t="s">
+      <c r="M1023" t="s">
         <v>2285</v>
       </c>
-      <c r="L1023" t="s">
+      <c r="N1023" t="s">
         <v>2286</v>
       </c>
-      <c r="M1023" t="s">
+      <c r="O1023" t="s">
         <v>2287</v>
       </c>
-      <c r="N1023" t="s">
+      <c r="P1023" t="s">
         <v>2288</v>
-      </c>
-      <c r="O1023" t="s">
-        <v>2289</v>
-      </c>
-      <c r="P1023" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="1024" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>3354</v>
+      </c>
+      <c r="C1024" t="s">
         <v>3355</v>
       </c>
-      <c r="B1024" t="s">
+      <c r="D1024" t="s">
         <v>3356</v>
       </c>
-      <c r="C1024" t="s">
+      <c r="E1024" t="s">
         <v>3357</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="F1024" t="s">
         <v>3358</v>
       </c>
-      <c r="E1024" t="s">
+      <c r="G1024" t="s">
         <v>3359</v>
       </c>
-      <c r="F1024" t="s">
+      <c r="H1024" t="s">
         <v>3360</v>
       </c>
-      <c r="G1024" t="s">
+      <c r="I1024" t="s">
         <v>3361</v>
       </c>
-      <c r="H1024" t="s">
+      <c r="J1024" t="s">
+        <v>3361</v>
+      </c>
+      <c r="K1024" t="s">
         <v>3362</v>
       </c>
-      <c r="I1024" t="s">
+      <c r="L1024" t="s">
         <v>3363</v>
       </c>
-      <c r="J1024" t="s">
-        <v>3363</v>
-      </c>
-      <c r="K1024" t="s">
+      <c r="M1024" t="s">
         <v>3364</v>
       </c>
-      <c r="L1024" t="s">
+      <c r="N1024" t="s">
         <v>3365</v>
       </c>
-      <c r="M1024" t="s">
+      <c r="O1024" t="s">
         <v>3366</v>
       </c>
-      <c r="N1024" t="s">
+      <c r="P1024" t="s">
         <v>3367</v>
-      </c>
-      <c r="O1024" t="s">
-        <v>3368</v>
-      </c>
-      <c r="P1024" t="s">
-        <v>3369</v>
       </c>
     </row>
     <row r="1025" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20579,272 +20640,272 @@
         <v>199</v>
       </c>
       <c r="B1025" s="2" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1026" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1027" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C1027" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1028" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C1028" t="s">
         <v>2296</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>2297</v>
-      </c>
-      <c r="C1028" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="1029" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B1029" s="2" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="C1029" s="2" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1030" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B1030" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C1030" s="2" t="s">
         <v>2301</v>
-      </c>
-      <c r="B1030" s="2" t="s">
-        <v>2302</v>
-      </c>
-      <c r="C1030" s="2" t="s">
-        <v>2303</v>
       </c>
     </row>
     <row r="1031" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C1031" t="s">
         <v>2304</v>
       </c>
-      <c r="B1031" t="s">
+      <c r="D1031" t="s">
         <v>2305</v>
-      </c>
-      <c r="C1031" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D1031" t="s">
-        <v>2307</v>
       </c>
     </row>
     <row r="1032" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C1032" t="s">
         <v>2308</v>
       </c>
-      <c r="B1032" t="s">
+      <c r="D1032" t="s">
         <v>2309</v>
-      </c>
-      <c r="C1032" t="s">
-        <v>2310</v>
-      </c>
-      <c r="D1032" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="1033" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="2" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="B1033" s="2" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="1034" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="2" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="B1034" s="2" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="1035" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="B1035" s="10" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="C1035" s="10"/>
     </row>
     <row r="1036" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="B1036" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="1037" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="2" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1037" s="2" t="s">
         <v>2319</v>
-      </c>
-      <c r="B1037" s="2" t="s">
-        <v>2320</v>
-      </c>
-      <c r="C1037" s="2" t="s">
-        <v>2321</v>
       </c>
     </row>
     <row r="1038" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="2" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1038" s="2" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C1038" s="2" t="s">
         <v>2322</v>
-      </c>
-      <c r="B1038" s="2" t="s">
-        <v>2323</v>
-      </c>
-      <c r="C1038" s="2" t="s">
-        <v>2324</v>
       </c>
     </row>
     <row r="1039" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C1039" t="s">
         <v>2325</v>
       </c>
-      <c r="B1039" t="s">
+      <c r="D1039" t="s">
         <v>2326</v>
       </c>
-      <c r="C1039" t="s">
+      <c r="E1039" t="s">
         <v>2327</v>
-      </c>
-      <c r="D1039" t="s">
-        <v>2328</v>
-      </c>
-      <c r="E1039" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="1040" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C1040" t="s">
         <v>2330</v>
       </c>
-      <c r="B1040" t="s">
+      <c r="D1040" t="s">
         <v>2331</v>
       </c>
-      <c r="C1040" t="s">
+      <c r="E1040" t="s">
         <v>2332</v>
-      </c>
-      <c r="D1040" t="s">
-        <v>2333</v>
-      </c>
-      <c r="E1040" t="s">
-        <v>2334</v>
       </c>
     </row>
     <row r="1041" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="2" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1041" s="2" t="s">
         <v>2335</v>
       </c>
-      <c r="B1041" s="2" t="s">
+      <c r="D1041" s="2" t="s">
         <v>2336</v>
       </c>
-      <c r="C1041" s="2" t="s">
+      <c r="E1041" s="2" t="s">
         <v>2337</v>
       </c>
-      <c r="D1041" s="2" t="s">
+      <c r="F1041" s="2" t="s">
         <v>2338</v>
       </c>
-      <c r="E1041" s="2" t="s">
+      <c r="G1041" s="2" t="s">
         <v>2339</v>
       </c>
-      <c r="F1041" s="2" t="s">
+      <c r="H1041" s="2" t="s">
         <v>2340</v>
       </c>
-      <c r="G1041" s="2" t="s">
-        <v>2341</v>
-      </c>
-      <c r="H1041" s="2" t="s">
-        <v>2342</v>
-      </c>
       <c r="I1041" s="11" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="1042" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C1042" s="2" t="s">
         <v>2343</v>
       </c>
-      <c r="B1042" s="2" t="s">
+      <c r="D1042" s="2" t="s">
         <v>2344</v>
       </c>
-      <c r="C1042" s="2" t="s">
+      <c r="E1042" s="2" t="s">
         <v>2345</v>
       </c>
-      <c r="D1042" s="2" t="s">
+      <c r="F1042" s="2" t="s">
         <v>2346</v>
       </c>
-      <c r="E1042" s="2" t="s">
+      <c r="G1042" s="2" t="s">
         <v>2347</v>
       </c>
-      <c r="F1042" s="2" t="s">
+      <c r="H1042" s="2" t="s">
+        <v>3313</v>
+      </c>
+      <c r="I1042" s="2" t="s">
         <v>2348</v>
-      </c>
-      <c r="G1042" s="2" t="s">
-        <v>2349</v>
-      </c>
-      <c r="H1042" s="2" t="s">
-        <v>3315</v>
-      </c>
-      <c r="I1042" s="2" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="B1043" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="B1044" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1045" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C1045" s="2" t="s">
         <v>2355</v>
-      </c>
-      <c r="B1045" s="2" t="s">
-        <v>2356</v>
-      </c>
-      <c r="C1045" s="2" t="s">
-        <v>2357</v>
       </c>
     </row>
     <row r="1046" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C1046" s="2" t="s">
         <v>2358</v>
-      </c>
-      <c r="B1046" s="2" t="s">
-        <v>2359</v>
-      </c>
-      <c r="C1046" s="2" t="s">
-        <v>2360</v>
       </c>
     </row>
     <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
@@ -20852,21 +20913,21 @@
         <v>199</v>
       </c>
       <c r="B1047" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="C1047" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C1048" t="s">
         <v>2363</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>2364</v>
-      </c>
-      <c r="C1048" t="s">
-        <v>2365</v>
       </c>
     </row>
     <row r="1049" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20874,185 +20935,185 @@
         <v>199</v>
       </c>
       <c r="B1049" s="2" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="1050" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="B1050" s="2" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C1051" t="s">
         <v>2369</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>2370</v>
-      </c>
-      <c r="C1051" t="s">
-        <v>2371</v>
       </c>
     </row>
     <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C1052" t="s">
         <v>2372</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>2373</v>
-      </c>
-      <c r="C1052" t="s">
-        <v>2374</v>
       </c>
     </row>
     <row r="1053" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B1053" s="2" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1053" s="2" t="s">
         <v>2375</v>
-      </c>
-      <c r="B1053" s="2" t="s">
-        <v>2376</v>
-      </c>
-      <c r="C1053" s="2" t="s">
-        <v>2377</v>
       </c>
     </row>
     <row r="1054" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B1054" s="2" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C1054" s="2" t="s">
         <v>2378</v>
-      </c>
-      <c r="B1054" s="2" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C1054" s="2" t="s">
-        <v>2380</v>
       </c>
     </row>
     <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C1055" t="s">
         <v>2381</v>
       </c>
-      <c r="B1055" t="s">
+      <c r="D1055" t="s">
         <v>2382</v>
       </c>
-      <c r="C1055" t="s">
+      <c r="E1055" t="s">
         <v>2383</v>
-      </c>
-      <c r="D1055" t="s">
-        <v>2384</v>
-      </c>
-      <c r="E1055" t="s">
-        <v>2385</v>
       </c>
     </row>
     <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C1056" t="s">
         <v>2386</v>
       </c>
-      <c r="B1056" t="s">
+      <c r="D1056" t="s">
         <v>2387</v>
       </c>
-      <c r="C1056" t="s">
+      <c r="E1056" t="s">
         <v>2388</v>
-      </c>
-      <c r="D1056" t="s">
-        <v>2389</v>
-      </c>
-      <c r="E1056" t="s">
-        <v>2390</v>
       </c>
     </row>
     <row r="1057" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1057" s="2" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="C1057" s="2" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="1058" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="2" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B1058" s="2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C1058" s="2" t="s">
         <v>2393</v>
-      </c>
-      <c r="B1058" s="2" t="s">
-        <v>2394</v>
-      </c>
-      <c r="C1058" s="2" t="s">
-        <v>2395</v>
       </c>
     </row>
     <row r="1059" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="B1059" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="1060" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="B1060" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1061" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1061" s="2" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="B1061" s="2" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="1062" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1062" s="2" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="B1062" s="2" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="1063" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="B1063" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1064" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="B1064" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="1065" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="2" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="B1065" s="2" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="C1065" s="2" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1066" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="2" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="B1066" s="2" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="C1066" s="2" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="1067" spans="1:3" x14ac:dyDescent="0.25">
@@ -21060,43 +21121,43 @@
         <v>85</v>
       </c>
       <c r="B1067" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="C1067" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="1068" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C1068" t="s">
         <v>2410</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>2411</v>
-      </c>
-      <c r="C1068" t="s">
-        <v>2412</v>
       </c>
     </row>
     <row r="1069" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1069" s="2" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1069" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1069" s="2" t="s">
         <v>2413</v>
-      </c>
-      <c r="B1069" s="2" t="s">
-        <v>2414</v>
-      </c>
-      <c r="C1069" s="2" t="s">
-        <v>2415</v>
       </c>
     </row>
     <row r="1070" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1070" s="2" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B1070" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C1070" s="2" t="s">
         <v>2416</v>
-      </c>
-      <c r="B1070" s="2" t="s">
-        <v>2417</v>
-      </c>
-      <c r="C1070" s="2" t="s">
-        <v>2418</v>
       </c>
     </row>
     <row r="1071" spans="1:3" x14ac:dyDescent="0.25">
@@ -21104,43 +21165,43 @@
         <v>7</v>
       </c>
       <c r="B1071" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="1072" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="B1072" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="1073" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1073" s="2" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B1073" s="2" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C1073" s="2" t="s">
         <v>2422</v>
       </c>
-      <c r="B1073" s="2" t="s">
+      <c r="D1073" s="2" t="s">
         <v>2423</v>
-      </c>
-      <c r="C1073" s="2" t="s">
-        <v>2424</v>
-      </c>
-      <c r="D1073" s="2" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="1074" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1074" s="2" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B1074" s="2" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C1074" s="2" t="s">
         <v>2426</v>
       </c>
-      <c r="B1074" s="2" t="s">
+      <c r="D1074" s="2" t="s">
         <v>2427</v>
-      </c>
-      <c r="C1074" s="2" t="s">
-        <v>2428</v>
-      </c>
-      <c r="D1074" s="2" t="s">
-        <v>2429</v>
       </c>
     </row>
     <row r="1075" spans="1:4" x14ac:dyDescent="0.25">
@@ -21148,37 +21209,37 @@
         <v>199</v>
       </c>
       <c r="B1075" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="1076" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="B1076" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="1077" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1077" s="2" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B1077" s="2" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C1077" s="2" t="s">
         <v>2433</v>
-      </c>
-      <c r="B1077" s="2" t="s">
-        <v>2434</v>
-      </c>
-      <c r="C1077" s="2" t="s">
-        <v>2435</v>
       </c>
     </row>
     <row r="1078" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1078" s="2" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B1078" s="2" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C1078" s="2" t="s">
         <v>2436</v>
-      </c>
-      <c r="B1078" s="2" t="s">
-        <v>2437</v>
-      </c>
-      <c r="C1078" s="2" t="s">
-        <v>2438</v>
       </c>
     </row>
     <row r="1079" spans="1:4" x14ac:dyDescent="0.25">
@@ -21186,241 +21247,241 @@
         <v>7</v>
       </c>
       <c r="B1079" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="1080" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="B1080" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="1081" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="2" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="B1081" s="2" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="1082" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1082" s="2" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="B1082" s="2" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="1083" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="B1083" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="C1083" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="1084" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="B1084" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="C1084" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="1085" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B1085" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C1085" s="2" t="s">
         <v>2452</v>
-      </c>
-      <c r="B1085" s="2" t="s">
-        <v>2453</v>
-      </c>
-      <c r="C1085" s="2" t="s">
-        <v>2454</v>
       </c>
     </row>
     <row r="1086" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1086" s="2" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B1086" s="2" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C1086" s="2" t="s">
         <v>2455</v>
-      </c>
-      <c r="B1086" s="2" t="s">
-        <v>2456</v>
-      </c>
-      <c r="C1086" s="2" t="s">
-        <v>2457</v>
       </c>
     </row>
     <row r="1087" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B1087" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="1088" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="B1088" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="1089" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1089" s="2" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="B1089" s="2" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="1090" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1090" s="2" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="B1090" s="2" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="B1091" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="1092" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="B1092" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="1093" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1093" s="2" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="B1093" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="1094" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1094" s="2" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="B1094" s="2" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="1095" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="B1095" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="1096" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="B1096" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="1097" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1097" s="2" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="B1097" s="2" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="1098" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1098" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="B1098" s="2" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="1099" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="B1099" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="1100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="B1100" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="1101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1101" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B1101" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C1101" s="2" t="s">
         <v>2486</v>
-      </c>
-      <c r="B1101" s="2" t="s">
-        <v>2487</v>
-      </c>
-      <c r="C1101" s="2" t="s">
-        <v>2488</v>
       </c>
     </row>
     <row r="1102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1102" s="2" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B1102" s="2" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C1102" s="2" t="s">
         <v>2489</v>
-      </c>
-      <c r="B1102" s="2" t="s">
-        <v>2490</v>
-      </c>
-      <c r="C1102" s="2" t="s">
-        <v>2491</v>
       </c>
     </row>
     <row r="1103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B1103" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="1104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="B1104" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="1105" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1105" s="2" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="B1105" s="2" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="1106" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1106" s="2" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="B1106" s="2" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="1107" spans="1:4" x14ac:dyDescent="0.25">
@@ -21428,145 +21489,145 @@
         <v>7</v>
       </c>
       <c r="B1107" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="1108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B1108" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="1109" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1109" s="2" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B1109" s="2" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C1109" s="2" t="s">
         <v>2507</v>
       </c>
-      <c r="B1109" s="2" t="s">
+      <c r="D1109" s="2" t="s">
         <v>2508</v>
-      </c>
-      <c r="C1109" s="2" t="s">
-        <v>2509</v>
-      </c>
-      <c r="D1109" s="2" t="s">
-        <v>2510</v>
       </c>
     </row>
     <row r="1110" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1110" s="2" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B1110" s="2" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C1110" s="2" t="s">
         <v>2511</v>
       </c>
-      <c r="B1110" s="2" t="s">
+      <c r="D1110" s="2" t="s">
         <v>2512</v>
-      </c>
-      <c r="C1110" s="2" t="s">
-        <v>2513</v>
-      </c>
-      <c r="D1110" s="2" t="s">
-        <v>2514</v>
       </c>
     </row>
     <row r="1111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="B1111" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="1112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="B1112" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="1113" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1113" s="2" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B1113" s="2" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="1114" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1114" s="2" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="B1114" s="2" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="1115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="B1115" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="1116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="B1116" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="1117" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1117" s="2" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B1117" s="2" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="1118" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1118" s="2" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="B1118" s="2" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="1119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C1119" t="s">
         <v>2531</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>2532</v>
-      </c>
-      <c r="C1119" t="s">
-        <v>2533</v>
       </c>
     </row>
     <row r="1120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C1120" t="s">
         <v>2534</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C1120" t="s">
-        <v>2536</v>
       </c>
     </row>
     <row r="1121" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1121" s="2" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="B1121" s="2" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="1122" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="2" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="B1122" s="2" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="1123" spans="1:3" x14ac:dyDescent="0.25">
@@ -21574,37 +21635,37 @@
         <v>7</v>
       </c>
       <c r="B1123" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="B1124" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="1125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1125" s="2" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="C1125" s="2" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="1126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1126" s="2" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B1126" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C1126" s="2" t="s">
         <v>2547</v>
-      </c>
-      <c r="B1126" s="2" t="s">
-        <v>2548</v>
-      </c>
-      <c r="C1126" s="2" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="1127" spans="1:3" x14ac:dyDescent="0.25">
@@ -21612,15 +21673,15 @@
         <v>199</v>
       </c>
       <c r="B1127" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="1128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="B1128" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="1129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -21628,65 +21689,65 @@
         <v>85</v>
       </c>
       <c r="B1129" s="2" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="C1129" s="2" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="1130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1130" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B1130" s="2" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C1130" s="2" t="s">
         <v>2554</v>
-      </c>
-      <c r="B1130" s="2" t="s">
-        <v>2555</v>
-      </c>
-      <c r="C1130" s="2" t="s">
-        <v>2556</v>
       </c>
     </row>
     <row r="1131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C1131" t="s">
         <v>2557</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2558</v>
-      </c>
-      <c r="C1131" t="s">
-        <v>2559</v>
       </c>
     </row>
     <row r="1132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C1132" t="s">
         <v>2560</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2561</v>
-      </c>
-      <c r="C1132" t="s">
-        <v>2562</v>
       </c>
     </row>
     <row r="1133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1133" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B1133" s="2" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C1133" s="2" t="s">
         <v>2563</v>
-      </c>
-      <c r="B1133" s="2" t="s">
-        <v>2564</v>
-      </c>
-      <c r="C1133" s="2" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="1134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1134" s="2" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B1134" s="2" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C1134" s="2" t="s">
         <v>2566</v>
-      </c>
-      <c r="B1134" s="2" t="s">
-        <v>2567</v>
-      </c>
-      <c r="C1134" s="2" t="s">
-        <v>2568</v>
       </c>
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.25">
@@ -21694,37 +21755,37 @@
         <v>7</v>
       </c>
       <c r="B1135" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="1136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="B1136" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="1137" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B1137" s="2" t="s">
+        <v>2571</v>
+      </c>
+      <c r="C1137" s="2" t="s">
         <v>2572</v>
-      </c>
-      <c r="B1137" s="2" t="s">
-        <v>2573</v>
-      </c>
-      <c r="C1137" s="2" t="s">
-        <v>2574</v>
       </c>
     </row>
     <row r="1138" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1138" s="2" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B1138" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C1138" s="2" t="s">
         <v>2575</v>
-      </c>
-      <c r="B1138" s="2" t="s">
-        <v>2576</v>
-      </c>
-      <c r="C1138" s="2" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="1139" spans="1:3" x14ac:dyDescent="0.25">
@@ -21732,63 +21793,63 @@
         <v>85</v>
       </c>
       <c r="B1139" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="1140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="B1140" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="1141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1141" s="2" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="B1141" s="2" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="1142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1142" s="2" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="B1142" s="2" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="1143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="B1143" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="1144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="B1144" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="1145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="2" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="B1145" s="2" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="1146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1146" s="2" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="B1146" s="2" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="1147" spans="1:3" x14ac:dyDescent="0.25">
@@ -21796,15 +21857,15 @@
         <v>7</v>
       </c>
       <c r="B1147" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="1148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="B1148" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="1149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -21812,15 +21873,15 @@
         <v>7</v>
       </c>
       <c r="B1149" s="2" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="1150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1150" s="2" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="B1150" s="2" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="1151" spans="1:3" x14ac:dyDescent="0.25">
@@ -21833,7 +21894,7 @@
     </row>
     <row r="1152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="B1152" t="s">
         <v>709</v>
@@ -21844,37 +21905,37 @@
         <v>7</v>
       </c>
       <c r="B1153" s="2" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="1154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1154" s="2" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="B1154" s="2" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="1155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="B1155" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="C1155" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="1156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="B1156" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="C1156" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="1157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -21882,31 +21943,31 @@
         <v>7</v>
       </c>
       <c r="B1157" s="2" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="1158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1158" s="2" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="B1158" s="2" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="1159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="B1159" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="1160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="B1160" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="1161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -21914,21 +21975,21 @@
         <v>7</v>
       </c>
       <c r="B1161" s="2" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="C1161" s="2" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="1162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1162" s="2" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="B1162" s="2" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C1162" s="2" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="1163" spans="1:3" x14ac:dyDescent="0.25">
@@ -21936,107 +21997,107 @@
         <v>7</v>
       </c>
       <c r="B1163" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="1164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="B1164" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="1165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1165" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B1165" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C1165" s="2" t="s">
         <v>2620</v>
-      </c>
-      <c r="B1165" s="2" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C1165" s="2" t="s">
-        <v>2622</v>
       </c>
     </row>
     <row r="1166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1166" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B1166" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C1166" s="2" t="s">
         <v>2626</v>
-      </c>
-      <c r="B1166" s="2" t="s">
-        <v>2627</v>
-      </c>
-      <c r="C1166" s="2" t="s">
-        <v>2628</v>
       </c>
     </row>
     <row r="1167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="B1167" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="C1167" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="B1168" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="C1168" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="1169" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="2" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="B1169" s="2" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="1170" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1170" s="2" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="B1170" s="2" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="1171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="B1171" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="1172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="B1172" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="1173" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="2" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="B1173" s="2" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="1174" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1174" s="2" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="B1174" s="2" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="1175" spans="1:4" x14ac:dyDescent="0.25">
@@ -22044,15 +22105,15 @@
         <v>85</v>
       </c>
       <c r="B1175" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="1176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="B1176" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="1177" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22060,147 +22121,147 @@
         <v>199</v>
       </c>
       <c r="B1177" s="2" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="C1177" s="2" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="1178" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1178" s="2" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="B1178" s="2" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C1178" s="2" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C1179" t="s">
         <v>2654</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C1179" t="s">
-        <v>2656</v>
       </c>
     </row>
     <row r="1180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C1180" t="s">
         <v>2657</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C1180" t="s">
-        <v>2659</v>
       </c>
     </row>
     <row r="1181" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B1181" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C1181" s="2" t="s">
         <v>2660</v>
       </c>
-      <c r="B1181" s="2" t="s">
+      <c r="D1181" s="2" t="s">
         <v>2661</v>
-      </c>
-      <c r="C1181" s="2" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1181" s="2" t="s">
-        <v>2663</v>
       </c>
     </row>
     <row r="1182" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="2" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B1182" s="2" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1182" s="2" t="s">
         <v>3370</v>
       </c>
-      <c r="B1182" s="2" t="s">
+      <c r="D1182" s="2" t="s">
         <v>3371</v>
-      </c>
-      <c r="C1182" s="2" t="s">
-        <v>3372</v>
-      </c>
-      <c r="D1182" s="2" t="s">
-        <v>3373</v>
       </c>
     </row>
     <row r="1183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C1183" t="s">
         <v>2664</v>
-      </c>
-      <c r="B1183" t="s">
-        <v>2665</v>
-      </c>
-      <c r="C1183" t="s">
-        <v>2666</v>
       </c>
     </row>
     <row r="1184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
+        <v>2665</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2666</v>
+      </c>
+      <c r="C1184" t="s">
         <v>2667</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>2668</v>
-      </c>
-      <c r="C1184" t="s">
-        <v>2669</v>
       </c>
     </row>
     <row r="1185" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1185" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B1185" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C1185" s="2" t="s">
         <v>2670</v>
-      </c>
-      <c r="B1185" s="2" t="s">
-        <v>2671</v>
-      </c>
-      <c r="C1185" s="2" t="s">
-        <v>2672</v>
       </c>
     </row>
     <row r="1186" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1186" s="2" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B1186" s="2" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C1186" s="2" t="s">
         <v>2673</v>
-      </c>
-      <c r="B1186" s="2" t="s">
-        <v>2674</v>
-      </c>
-      <c r="C1186" s="2" t="s">
-        <v>2675</v>
       </c>
     </row>
     <row r="1187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="B1187" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="B1188" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="1189" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1189" s="2" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="B1189" s="2" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="1190" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1190" s="2" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="B1190" s="2" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.25">
@@ -22208,15 +22269,15 @@
         <v>85</v>
       </c>
       <c r="B1191" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="B1192" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="1193" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22224,315 +22285,315 @@
         <v>199</v>
       </c>
       <c r="B1193" s="2" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="1194" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="2" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="B1194" s="2" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B1195" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B1196" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="1197" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1197" s="2" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="B1197" s="2" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C1197" s="2" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D1197" s="2" t="s">
         <v>2698</v>
       </c>
-      <c r="C1197" s="2" t="s">
+      <c r="E1197" s="2" t="s">
         <v>2699</v>
       </c>
-      <c r="D1197" s="2" t="s">
+      <c r="F1197" s="2" t="s">
         <v>2700</v>
       </c>
-      <c r="E1197" s="2" t="s">
+      <c r="G1197" s="2" t="s">
         <v>2701</v>
-      </c>
-      <c r="F1197" s="2" t="s">
-        <v>2702</v>
-      </c>
-      <c r="G1197" s="2" t="s">
-        <v>2703</v>
       </c>
     </row>
     <row r="1198" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1198" s="2" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B1198" s="2" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C1198" s="2" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D1198" s="2" t="s">
         <v>2708</v>
       </c>
-      <c r="C1198" s="2" t="s">
+      <c r="E1198" s="2" t="s">
         <v>2709</v>
       </c>
-      <c r="D1198" s="2" t="s">
+      <c r="F1198" s="2" t="s">
         <v>2710</v>
       </c>
-      <c r="E1198" s="2" t="s">
+      <c r="G1198" s="2" t="s">
         <v>2711</v>
-      </c>
-      <c r="F1198" s="2" t="s">
-        <v>2712</v>
-      </c>
-      <c r="G1198" s="2" t="s">
-        <v>2713</v>
       </c>
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="B1199" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="1200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="B1200" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="1201" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1201" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B1201" s="2" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="C1201" s="2" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="1202" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1202" s="2" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="B1202" s="2" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="C1202" s="2" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="B1203" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="B1204" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="1205" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1205" s="2" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B1205" s="2" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1205" s="2" t="s">
         <v>2721</v>
-      </c>
-      <c r="B1205" s="2" t="s">
-        <v>2722</v>
-      </c>
-      <c r="C1205" s="2" t="s">
-        <v>2723</v>
       </c>
     </row>
     <row r="1206" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1206" s="2" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B1206" s="2" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C1206" s="2" t="s">
         <v>2725</v>
-      </c>
-      <c r="B1206" s="2" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C1206" s="2" t="s">
-        <v>2727</v>
       </c>
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="B1207" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="1208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="B1208" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1209" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1209" s="2" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="B1209" s="2" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="1210" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="2" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="B1210" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="B1211" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D1211" t="s">
         <v>2738</v>
       </c>
-      <c r="C1211" t="s">
+      <c r="E1211" t="s">
         <v>2739</v>
-      </c>
-      <c r="D1211" t="s">
-        <v>2740</v>
-      </c>
-      <c r="E1211" t="s">
-        <v>2741</v>
       </c>
     </row>
     <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="B1212" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D1212" t="s">
         <v>2750</v>
       </c>
-      <c r="C1212" t="s">
+      <c r="E1212" t="s">
         <v>2751</v>
-      </c>
-      <c r="D1212" t="s">
-        <v>2752</v>
-      </c>
-      <c r="E1212" t="s">
-        <v>2753</v>
       </c>
     </row>
     <row r="1213" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1213" s="2" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="B1213" s="2" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C1213" s="2" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D1213" s="2" t="s">
         <v>2742</v>
       </c>
-      <c r="C1213" s="2" t="s">
+      <c r="E1213" s="2" t="s">
         <v>2743</v>
       </c>
-      <c r="D1213" s="2" t="s">
+      <c r="F1213" s="2" t="s">
         <v>2744</v>
       </c>
-      <c r="E1213" s="2" t="s">
+      <c r="G1213" s="2" t="s">
         <v>2745</v>
       </c>
-      <c r="F1213" s="2" t="s">
+      <c r="H1213" s="2" t="s">
         <v>2746</v>
-      </c>
-      <c r="G1213" s="2" t="s">
-        <v>2747</v>
-      </c>
-      <c r="H1213" s="2" t="s">
-        <v>2748</v>
       </c>
     </row>
     <row r="1214" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1214" s="2" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="B1214" s="2" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C1214" s="2" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D1214" s="2" t="s">
         <v>2754</v>
       </c>
-      <c r="C1214" s="2" t="s">
+      <c r="E1214" s="2" t="s">
         <v>2755</v>
       </c>
-      <c r="D1214" s="2" t="s">
+      <c r="F1214" s="2" t="s">
         <v>2756</v>
       </c>
-      <c r="E1214" s="2" t="s">
+      <c r="G1214" s="2" t="s">
         <v>2757</v>
       </c>
-      <c r="F1214" s="2" t="s">
+      <c r="H1214" s="2" t="s">
         <v>2758</v>
-      </c>
-      <c r="G1214" s="2" t="s">
-        <v>2759</v>
-      </c>
-      <c r="H1214" s="2" t="s">
-        <v>2760</v>
       </c>
     </row>
     <row r="1215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C1215" t="s">
         <v>2761</v>
       </c>
-      <c r="B1215" t="s">
+      <c r="D1215" t="s">
         <v>2762</v>
-      </c>
-      <c r="C1215" t="s">
-        <v>2763</v>
-      </c>
-      <c r="D1215" t="s">
-        <v>2764</v>
       </c>
     </row>
     <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C1216" t="s">
         <v>2765</v>
       </c>
-      <c r="B1216" t="s">
+      <c r="D1216" t="s">
         <v>2766</v>
-      </c>
-      <c r="C1216" t="s">
-        <v>2767</v>
-      </c>
-      <c r="D1216" t="s">
-        <v>2768</v>
       </c>
     </row>
     <row r="1217" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1217" s="2" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="B1217" s="2" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="1218" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1218" s="2" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
       <c r="B1218" s="2" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="1219" spans="1:4" x14ac:dyDescent="0.25">
@@ -22540,27 +22601,27 @@
         <v>7</v>
       </c>
       <c r="B1219" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D1219" t="s">
         <v>2773</v>
-      </c>
-      <c r="C1219" t="s">
-        <v>2774</v>
-      </c>
-      <c r="D1219" t="s">
-        <v>2775</v>
       </c>
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C1220" t="s">
         <v>2776</v>
       </c>
-      <c r="B1220" t="s">
+      <c r="D1220" t="s">
         <v>2777</v>
-      </c>
-      <c r="C1220" t="s">
-        <v>2778</v>
-      </c>
-      <c r="D1220" t="s">
-        <v>2779</v>
       </c>
     </row>
     <row r="1221" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22568,31 +22629,31 @@
         <v>199</v>
       </c>
       <c r="B1221" s="2" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="1222" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1222" s="2" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="B1222" s="2" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="B1223" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="B1224" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="1225" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22600,79 +22661,79 @@
         <v>7</v>
       </c>
       <c r="B1225" s="2" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="1226" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1226" s="2" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="B1226" s="2" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="1227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="B1227" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="B1228" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="1229" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1229" s="2" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="B1229" s="2" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="1230" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1230" s="2" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="B1230" s="2" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
       <c r="B1231" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
       <c r="B1232" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="1233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1233" s="2" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="B1233" s="2" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1234" s="2" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="1235" spans="1:3" x14ac:dyDescent="0.25">
@@ -22680,21 +22741,21 @@
         <v>199</v>
       </c>
       <c r="B1235" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="C1235" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="1236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="B1236" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
       <c r="C1236" t="s">
-        <v>2810</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="1237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22702,53 +22763,53 @@
         <v>7</v>
       </c>
       <c r="B1237" s="2" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="1238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1238" s="2" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
       <c r="B1238" s="2" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="1239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C1239" t="s">
         <v>2815</v>
-      </c>
-      <c r="B1239" t="s">
-        <v>2816</v>
-      </c>
-      <c r="C1239" t="s">
-        <v>2817</v>
       </c>
     </row>
     <row r="1240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C1240" t="s">
         <v>2818</v>
-      </c>
-      <c r="B1240" t="s">
-        <v>2819</v>
-      </c>
-      <c r="C1240" t="s">
-        <v>2820</v>
       </c>
     </row>
     <row r="1241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="2" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
       <c r="B1241" s="2" t="s">
-        <v>2822</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="2" t="s">
-        <v>2823</v>
+        <v>2821</v>
       </c>
       <c r="B1242" s="2" t="s">
-        <v>2824</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.25">
@@ -22756,15 +22817,15 @@
         <v>85</v>
       </c>
       <c r="B1243" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>2826</v>
+        <v>2824</v>
       </c>
       <c r="B1244" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="1245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22772,15 +22833,15 @@
         <v>199</v>
       </c>
       <c r="B1245" s="2" t="s">
-        <v>2828</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="1246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1246" s="2" t="s">
-        <v>2829</v>
+        <v>2827</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>2830</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1247" spans="1:3" x14ac:dyDescent="0.25">
@@ -22788,95 +22849,95 @@
         <v>7</v>
       </c>
       <c r="B1247" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="1248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>2832</v>
+        <v>2830</v>
       </c>
       <c r="B1248" t="s">
-        <v>2833</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="1249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="2" t="s">
-        <v>2834</v>
+        <v>2832</v>
       </c>
       <c r="B1249" s="2" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="2" t="s">
-        <v>2837</v>
+        <v>2835</v>
       </c>
       <c r="B1250" s="2" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="B1251" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="B1252" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1253" s="2" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="B1253" s="2" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1254" s="2" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="B1254" s="2" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="B1255" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="B1256" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="1257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1257" s="2" t="s">
-        <v>2847</v>
+        <v>2845</v>
       </c>
       <c r="B1257" s="2" t="s">
-        <v>2848</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="1258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1258" s="2" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
       <c r="B1258" s="2" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="1259" spans="1:3" x14ac:dyDescent="0.25">
@@ -22884,113 +22945,113 @@
         <v>7</v>
       </c>
       <c r="B1259" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="C1259" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="1260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C1260" t="s">
         <v>2853</v>
-      </c>
-      <c r="B1260" t="s">
-        <v>2854</v>
-      </c>
-      <c r="C1260" t="s">
-        <v>2855</v>
       </c>
     </row>
     <row r="1261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1261" s="2" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="B1261" s="2" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="C1261" s="2" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="1262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1262" s="2" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="B1262" s="2" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="C1262" s="2" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="1263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
       <c r="B1263" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="1264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="B1264" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="1265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1265" s="2" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
       <c r="B1265" s="2" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="1266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1266" s="2" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="B1266" s="2" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="B1267" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="1268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="B1268" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="1269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1269" s="2" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="B1269" s="2" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="C1269" s="2" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="1270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1270" s="2" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="B1270" s="2" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="C1270" s="2" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="1271" spans="1:3" x14ac:dyDescent="0.25">
@@ -22998,53 +23059,53 @@
         <v>7</v>
       </c>
       <c r="B1271" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="1272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="B1272" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="1273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1273" s="2" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B1273" s="2" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C1273" s="2" t="s">
         <v>2879</v>
-      </c>
-      <c r="B1273" s="2" t="s">
-        <v>2880</v>
-      </c>
-      <c r="C1273" s="2" t="s">
-        <v>2881</v>
       </c>
     </row>
     <row r="1274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1274" s="2" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B1274" s="2" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C1274" s="2" t="s">
         <v>2882</v>
-      </c>
-      <c r="B1274" s="2" t="s">
-        <v>2883</v>
-      </c>
-      <c r="C1274" s="2" t="s">
-        <v>2884</v>
       </c>
     </row>
     <row r="1275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
       <c r="B1275" t="s">
-        <v>2886</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="B1276" t="s">
-        <v>2888</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="1277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23052,15 +23113,15 @@
         <v>7</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>2889</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="1278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1278" s="2" t="s">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="B1278" s="2" t="s">
-        <v>2891</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="1279" spans="1:3" x14ac:dyDescent="0.25">
@@ -23068,31 +23129,31 @@
         <v>7</v>
       </c>
       <c r="B1279" t="s">
-        <v>2892</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="1280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="B1280" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="1281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1281" s="2" t="s">
-        <v>199</v>
+        <v>3440</v>
       </c>
       <c r="B1281" s="2" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="1282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1282" s="2" t="s">
-        <v>2896</v>
+        <v>2894</v>
       </c>
       <c r="B1282" s="2" t="s">
-        <v>2897</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="1283" spans="1:3" x14ac:dyDescent="0.25">
@@ -23100,119 +23161,119 @@
         <v>7</v>
       </c>
       <c r="B1283" t="s">
-        <v>2898</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="1284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="B1284" t="s">
-        <v>2900</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="1285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1285" s="2" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="1286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1286" s="2" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="B1286" s="2" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B1287" t="s">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="C1287" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>2906</v>
+      </c>
+      <c r="C1288" t="s">
         <v>2907</v>
-      </c>
-      <c r="B1288" t="s">
-        <v>2908</v>
-      </c>
-      <c r="C1288" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="1289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1289" s="2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B1289" s="2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C1289" s="2" t="s">
         <v>2910</v>
-      </c>
-      <c r="B1289" s="2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="C1289" s="2" t="s">
-        <v>2912</v>
       </c>
     </row>
     <row r="1290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1290" s="2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="B1290" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="C1290" s="2" t="s">
         <v>2913</v>
-      </c>
-      <c r="B1290" s="2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="C1290" s="2" t="s">
-        <v>2915</v>
       </c>
     </row>
     <row r="1291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C1291" t="s">
         <v>2916</v>
-      </c>
-      <c r="B1291" t="s">
-        <v>2917</v>
-      </c>
-      <c r="C1291" t="s">
-        <v>2918</v>
       </c>
     </row>
     <row r="1292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C1292" t="s">
         <v>2919</v>
-      </c>
-      <c r="B1292" t="s">
-        <v>2920</v>
-      </c>
-      <c r="C1292" t="s">
-        <v>2921</v>
       </c>
     </row>
     <row r="1293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1293" s="2" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1293" s="2" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="1294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1294" s="2" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B1294" s="2" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C1294" s="2" t="s">
         <v>2924</v>
-      </c>
-      <c r="B1294" s="2" t="s">
-        <v>2925</v>
-      </c>
-      <c r="C1294" s="2" t="s">
-        <v>2926</v>
       </c>
     </row>
     <row r="1295" spans="1:3" x14ac:dyDescent="0.25">
@@ -23220,59 +23281,59 @@
         <v>7</v>
       </c>
       <c r="B1295" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="1296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="B1296" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="1297" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1297" s="2" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="C1297" s="2" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="1298" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1298" s="2" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B1298" s="2" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C1298" s="2" t="s">
         <v>2936</v>
-      </c>
-      <c r="B1298" s="2" t="s">
-        <v>2937</v>
-      </c>
-      <c r="C1298" s="2" t="s">
-        <v>2938</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C1299" t="s">
         <v>2939</v>
-      </c>
-      <c r="B1299" t="s">
-        <v>2940</v>
-      </c>
-      <c r="C1299" t="s">
-        <v>2941</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C1300" t="s">
         <v>2942</v>
-      </c>
-      <c r="B1300" t="s">
-        <v>2943</v>
-      </c>
-      <c r="C1300" t="s">
-        <v>2944</v>
       </c>
     </row>
     <row r="1301" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23280,513 +23341,513 @@
         <v>199</v>
       </c>
       <c r="B1301" s="2" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="1302" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1302" s="2" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="B1302" s="2" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1303" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="C1303" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>2952</v>
+      </c>
+      <c r="C1304" t="s">
         <v>2953</v>
-      </c>
-      <c r="B1304" t="s">
-        <v>2954</v>
-      </c>
-      <c r="C1304" t="s">
-        <v>2955</v>
       </c>
     </row>
     <row r="1305" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1305" s="2" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="B1305" s="2" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="1306" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1306" s="2" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="B1306" s="2" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="B1307" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="B1308" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="1309" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="2" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="1310" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1310" s="2" t="s">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>3344</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C1311" t="s">
         <v>2969</v>
       </c>
-      <c r="B1311" t="s">
+      <c r="D1311" t="s">
         <v>2970</v>
-      </c>
-      <c r="C1311" t="s">
-        <v>2971</v>
-      </c>
-      <c r="D1311" t="s">
-        <v>2972</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
+        <v>2971</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>2972</v>
+      </c>
+      <c r="C1312" t="s">
         <v>2973</v>
       </c>
-      <c r="B1312" t="s">
+      <c r="D1312" t="s">
         <v>2974</v>
-      </c>
-      <c r="C1312" t="s">
-        <v>2975</v>
-      </c>
-      <c r="D1312" t="s">
-        <v>2976</v>
       </c>
     </row>
     <row r="1313" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="2" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="B1313" s="2" t="s">
+        <v>2948</v>
+      </c>
+      <c r="C1313" s="2" t="s">
+        <v>2949</v>
+      </c>
+      <c r="D1313" s="2" t="s">
         <v>2950</v>
-      </c>
-      <c r="C1313" s="2" t="s">
-        <v>2951</v>
-      </c>
-      <c r="D1313" s="2" t="s">
-        <v>2952</v>
       </c>
     </row>
     <row r="1314" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="2" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="B1314" s="2" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C1314" s="2" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D1314" s="2" t="s">
         <v>2956</v>
-      </c>
-      <c r="C1314" s="2" t="s">
-        <v>2957</v>
-      </c>
-      <c r="D1314" s="2" t="s">
-        <v>2958</v>
       </c>
     </row>
     <row r="1315" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="2" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B1315" s="2" t="s">
         <v>2979</v>
       </c>
-      <c r="B1315" s="2" t="s">
+      <c r="C1315" s="2" t="s">
+        <v>2980</v>
+      </c>
+      <c r="D1315" s="2" t="s">
         <v>2981</v>
-      </c>
-      <c r="C1315" s="2" t="s">
-        <v>2982</v>
-      </c>
-      <c r="D1315" s="2" t="s">
-        <v>2983</v>
       </c>
     </row>
     <row r="1316" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="2" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="B1316" s="2" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C1316" s="2" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D1316" s="2" t="s">
         <v>2984</v>
-      </c>
-      <c r="C1316" s="2" t="s">
-        <v>2985</v>
-      </c>
-      <c r="D1316" s="2" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C1317" t="s">
         <v>2987</v>
       </c>
-      <c r="B1317" t="s">
+      <c r="D1317" t="s">
         <v>2988</v>
-      </c>
-      <c r="C1317" t="s">
-        <v>2989</v>
-      </c>
-      <c r="D1317" t="s">
-        <v>2990</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
+        <v>2989</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C1318" t="s">
         <v>2991</v>
       </c>
-      <c r="B1318" t="s">
+      <c r="D1318" t="s">
         <v>2992</v>
-      </c>
-      <c r="C1318" t="s">
-        <v>2993</v>
-      </c>
-      <c r="D1318" t="s">
-        <v>2994</v>
       </c>
     </row>
     <row r="1319" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1319" s="2" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="1320" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1320" s="2" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B1321" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="B1322" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="1323" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1323" s="2" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="B1323" s="2" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C1323" s="2" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D1323" s="2" t="s">
         <v>3000</v>
-      </c>
-      <c r="C1323" s="2" t="s">
-        <v>3001</v>
-      </c>
-      <c r="D1323" s="2" t="s">
-        <v>3002</v>
       </c>
     </row>
     <row r="1324" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1324" s="2" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="B1324" s="2" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C1324" s="2" t="s">
+        <v>3004</v>
+      </c>
+      <c r="D1324" s="2" t="s">
         <v>3005</v>
-      </c>
-      <c r="C1324" s="2" t="s">
-        <v>3006</v>
-      </c>
-      <c r="D1324" s="2" t="s">
-        <v>3007</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="B1325" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="B1326" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="1327" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1327" s="2" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B1327" s="2" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1327" s="2" t="s">
         <v>3014</v>
       </c>
-      <c r="B1327" s="2" t="s">
+      <c r="D1327" s="2" t="s">
         <v>3015</v>
-      </c>
-      <c r="C1327" s="2" t="s">
-        <v>3016</v>
-      </c>
-      <c r="D1327" s="2" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="1328" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1328" s="2" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B1328" s="2" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C1328" s="2" t="s">
         <v>3018</v>
       </c>
-      <c r="B1328" s="2" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C1328" s="2" t="s">
-        <v>3020</v>
-      </c>
       <c r="D1328" s="2" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="B1329" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="B1330" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1331" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1331" s="2" t="s">
+        <v>3025</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C1331" s="2" t="s">
         <v>3027</v>
       </c>
-      <c r="B1331" s="2" t="s">
+      <c r="D1331" s="2" t="s">
         <v>3028</v>
-      </c>
-      <c r="C1331" s="2" t="s">
-        <v>3029</v>
-      </c>
-      <c r="D1331" s="2" t="s">
-        <v>3030</v>
       </c>
     </row>
     <row r="1332" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1332" s="2" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B1332" s="2" t="s">
+        <v>3030</v>
+      </c>
+      <c r="C1332" s="2" t="s">
         <v>3031</v>
       </c>
-      <c r="B1332" s="2" t="s">
+      <c r="D1332" s="2" t="s">
         <v>3032</v>
-      </c>
-      <c r="C1332" s="2" t="s">
-        <v>3033</v>
-      </c>
-      <c r="D1332" s="2" t="s">
-        <v>3034</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C1333" t="s">
         <v>3035</v>
-      </c>
-      <c r="B1333" t="s">
-        <v>3036</v>
-      </c>
-      <c r="C1333" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C1334" t="s">
         <v>3038</v>
-      </c>
-      <c r="B1334" t="s">
-        <v>3039</v>
-      </c>
-      <c r="C1334" t="s">
-        <v>3040</v>
       </c>
     </row>
     <row r="1335" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1335" s="2" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1336" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1336" s="2" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="B1337" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="B1338" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="1339" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1339" s="2" t="s">
+        <v>3045</v>
+      </c>
+      <c r="B1339" s="2" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C1339" s="2" t="s">
         <v>3047</v>
-      </c>
-      <c r="B1339" s="2" t="s">
-        <v>3048</v>
-      </c>
-      <c r="C1339" s="2" t="s">
-        <v>3049</v>
       </c>
     </row>
     <row r="1340" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1340" s="2" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B1340" s="2" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C1340" s="2" t="s">
         <v>3050</v>
-      </c>
-      <c r="B1340" s="2" t="s">
-        <v>3051</v>
-      </c>
-      <c r="C1340" s="2" t="s">
-        <v>3052</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="B1341" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="B1342" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="1343" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1343" s="2" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="1344" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1344" s="2" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C1345" t="s">
         <v>3059</v>
-      </c>
-      <c r="B1345" t="s">
-        <v>3060</v>
-      </c>
-      <c r="C1345" t="s">
-        <v>3061</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>3062</v>
+      </c>
+      <c r="C1346" t="s">
         <v>3063</v>
-      </c>
-      <c r="B1346" t="s">
-        <v>3064</v>
-      </c>
-      <c r="C1346" t="s">
-        <v>3065</v>
       </c>
     </row>
     <row r="1347" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1347" s="2" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1348" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1348" s="2" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C1349" t="s">
         <v>3069</v>
       </c>
-      <c r="B1349" t="s">
+      <c r="D1349" t="s">
         <v>3070</v>
-      </c>
-      <c r="C1349" t="s">
-        <v>3071</v>
-      </c>
-      <c r="D1349" t="s">
-        <v>3072</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C1350" t="s">
         <v>3073</v>
       </c>
-      <c r="B1350" t="s">
+      <c r="D1350" t="s">
         <v>3074</v>
-      </c>
-      <c r="C1350" t="s">
-        <v>3075</v>
-      </c>
-      <c r="D1350" t="s">
-        <v>3076</v>
       </c>
     </row>
     <row r="1351" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23794,343 +23855,343 @@
         <v>7</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="C1351" s="2" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="1352" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1352" s="2" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B1352" s="2" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C1352" s="2" t="s">
         <v>3079</v>
-      </c>
-      <c r="B1352" s="2" t="s">
-        <v>3080</v>
-      </c>
-      <c r="C1352" s="2" t="s">
-        <v>3081</v>
       </c>
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="B1353" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B1354" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="1355" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1355" s="2" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1355" s="2" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C1355" s="2" t="s">
         <v>3086</v>
-      </c>
-      <c r="B1355" s="2" t="s">
-        <v>3087</v>
-      </c>
-      <c r="C1355" s="2" t="s">
-        <v>3088</v>
       </c>
     </row>
     <row r="1356" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1356" s="2" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B1356" s="2" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C1356" s="2" t="s">
         <v>3089</v>
-      </c>
-      <c r="B1356" s="2" t="s">
-        <v>3090</v>
-      </c>
-      <c r="C1356" s="2" t="s">
-        <v>3091</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>3091</v>
+      </c>
+      <c r="C1357" t="s">
         <v>3092</v>
       </c>
-      <c r="B1357" t="s">
+      <c r="D1357" t="s">
         <v>3093</v>
-      </c>
-      <c r="C1357" t="s">
-        <v>3094</v>
-      </c>
-      <c r="D1357" t="s">
-        <v>3095</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C1358" t="s">
         <v>3096</v>
       </c>
-      <c r="B1358" t="s">
+      <c r="D1358" t="s">
         <v>3097</v>
-      </c>
-      <c r="C1358" t="s">
-        <v>3098</v>
-      </c>
-      <c r="D1358" t="s">
-        <v>3099</v>
       </c>
     </row>
     <row r="1359" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="2" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1359" s="2" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C1359" s="2" t="s">
         <v>3100</v>
       </c>
-      <c r="B1359" s="2" t="s">
+      <c r="D1359" s="2" t="s">
         <v>3101</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="E1359" s="2" t="s">
         <v>3102</v>
       </c>
-      <c r="D1359" s="2" t="s">
+      <c r="F1359" s="2" t="s">
         <v>3103</v>
       </c>
-      <c r="E1359" s="2" t="s">
+      <c r="G1359" s="2" t="s">
         <v>3104</v>
-      </c>
-      <c r="F1359" s="2" t="s">
-        <v>3105</v>
-      </c>
-      <c r="G1359" s="2" t="s">
-        <v>3106</v>
       </c>
     </row>
     <row r="1360" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="2" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B1360" s="2" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C1360" s="2" t="s">
         <v>3107</v>
       </c>
-      <c r="B1360" s="2" t="s">
+      <c r="D1360" s="2" t="s">
         <v>3108</v>
       </c>
-      <c r="C1360" s="2" t="s">
+      <c r="E1360" s="2" t="s">
+        <v>3106</v>
+      </c>
+      <c r="F1360" s="2" t="s">
         <v>3109</v>
       </c>
-      <c r="D1360" s="2" t="s">
+      <c r="G1360" s="2" t="s">
         <v>3110</v>
-      </c>
-      <c r="E1360" s="2" t="s">
-        <v>3108</v>
-      </c>
-      <c r="F1360" s="2" t="s">
-        <v>3111</v>
-      </c>
-      <c r="G1360" s="2" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="1361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
+        <v>3111</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>3112</v>
+      </c>
+      <c r="C1361" t="s">
         <v>3113</v>
       </c>
-      <c r="B1361" t="s">
+      <c r="D1361" t="s">
         <v>3114</v>
       </c>
-      <c r="C1361" t="s">
+      <c r="E1361" t="s">
         <v>3115</v>
-      </c>
-      <c r="D1361" t="s">
-        <v>3116</v>
-      </c>
-      <c r="E1361" t="s">
-        <v>3117</v>
       </c>
     </row>
     <row r="1362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1362" t="s">
         <v>3118</v>
       </c>
-      <c r="B1362" t="s">
+      <c r="D1362" t="s">
         <v>3119</v>
       </c>
-      <c r="C1362" t="s">
+      <c r="E1362" t="s">
         <v>3120</v>
-      </c>
-      <c r="D1362" t="s">
-        <v>3121</v>
-      </c>
-      <c r="E1362" t="s">
-        <v>3122</v>
       </c>
     </row>
     <row r="1363" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1363" s="2" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="B1363" s="2" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="1364" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1364" s="2" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="B1364" s="2" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="1365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
+        <v>3125</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C1365" t="s">
         <v>3127</v>
       </c>
-      <c r="B1365" t="s">
+      <c r="D1365" t="s">
         <v>3128</v>
       </c>
-      <c r="C1365" t="s">
+      <c r="E1365" t="s">
         <v>3129</v>
-      </c>
-      <c r="D1365" t="s">
-        <v>3130</v>
-      </c>
-      <c r="E1365" t="s">
-        <v>3131</v>
       </c>
     </row>
     <row r="1366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C1366" t="s">
         <v>3132</v>
       </c>
-      <c r="B1366" t="s">
+      <c r="D1366" t="s">
         <v>3133</v>
       </c>
-      <c r="C1366" t="s">
+      <c r="E1366" t="s">
         <v>3134</v>
-      </c>
-      <c r="D1366" t="s">
-        <v>3135</v>
-      </c>
-      <c r="E1366" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="1367" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1367" s="2" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="B1367" s="2" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="1368" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1368" s="2" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="B1368" s="2" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="1369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="B1369" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="1370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B1370" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="1371" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="2" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B1371" s="2" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="C1371" s="2" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="1372" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1372" s="2" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="C1372" s="2" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="1373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1373" t="s">
         <v>3151</v>
-      </c>
-      <c r="B1373" t="s">
-        <v>3152</v>
-      </c>
-      <c r="C1373" t="s">
-        <v>3153</v>
       </c>
     </row>
     <row r="1374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1374" t="s">
         <v>3154</v>
-      </c>
-      <c r="B1374" t="s">
-        <v>3155</v>
-      </c>
-      <c r="C1374" t="s">
-        <v>3156</v>
       </c>
     </row>
     <row r="1375" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="2" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B1375" s="2" t="s">
+        <v>3156</v>
+      </c>
+      <c r="C1375" s="2" t="s">
         <v>3157</v>
       </c>
-      <c r="B1375" s="2" t="s">
+      <c r="D1375" s="2" t="s">
         <v>3158</v>
-      </c>
-      <c r="C1375" s="2" t="s">
-        <v>3159</v>
-      </c>
-      <c r="D1375" s="2" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="1376" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1376" s="2" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B1376" s="2" t="s">
+        <v>3162</v>
+      </c>
+      <c r="C1376" s="2" t="s">
         <v>3163</v>
       </c>
-      <c r="B1376" s="2" t="s">
+      <c r="D1376" s="2" t="s">
         <v>3164</v>
-      </c>
-      <c r="C1376" s="2" t="s">
-        <v>3165</v>
-      </c>
-      <c r="D1376" s="2" t="s">
-        <v>3166</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1377" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="B1377" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="C1377" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="B1378" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="C1378" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="1379" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24138,165 +24199,165 @@
         <v>7</v>
       </c>
       <c r="B1379" s="8" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="1380" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="4" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="B1380" s="4" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1381" s="6" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="B1381" s="9" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="C1381" s="9" t="s">
-        <v>3294</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
+        <v>3195</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>3196</v>
+      </c>
+      <c r="C1382" t="s">
         <v>3197</v>
-      </c>
-      <c r="B1382" t="s">
-        <v>3198</v>
-      </c>
-      <c r="C1382" t="s">
-        <v>3199</v>
       </c>
     </row>
     <row r="1383" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1383" s="4" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="B1383" s="8" t="s">
+        <v>3293</v>
+      </c>
+      <c r="C1383" s="8" t="s">
+        <v>3294</v>
+      </c>
+      <c r="D1383" s="8" t="s">
         <v>3295</v>
-      </c>
-      <c r="C1383" s="8" t="s">
-        <v>3296</v>
-      </c>
-      <c r="D1383" s="8" t="s">
-        <v>3297</v>
       </c>
     </row>
     <row r="1384" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1384" s="4" t="s">
+        <v>3199</v>
+      </c>
+      <c r="B1384" s="4" t="s">
+        <v>3200</v>
+      </c>
+      <c r="C1384" s="4" t="s">
         <v>3201</v>
       </c>
-      <c r="B1384" s="4" t="s">
+      <c r="D1384" s="4" t="s">
         <v>3202</v>
-      </c>
-      <c r="C1384" s="4" t="s">
-        <v>3203</v>
-      </c>
-      <c r="D1384" s="4" t="s">
-        <v>3204</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="B1385" s="9" t="s">
+        <v>3296</v>
+      </c>
+      <c r="C1385" s="9" t="s">
+        <v>3297</v>
+      </c>
+      <c r="D1385" s="9" t="s">
         <v>3298</v>
-      </c>
-      <c r="C1385" s="9" t="s">
-        <v>3299</v>
-      </c>
-      <c r="D1385" s="9" t="s">
-        <v>3300</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C1386" t="s">
         <v>3206</v>
       </c>
-      <c r="B1386" t="s">
+      <c r="D1386" t="s">
         <v>3207</v>
-      </c>
-      <c r="C1386" t="s">
-        <v>3208</v>
-      </c>
-      <c r="D1386" t="s">
-        <v>3209</v>
       </c>
     </row>
     <row r="1387" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1387" s="4" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="B1387" s="8" t="s">
+        <v>3299</v>
+      </c>
+      <c r="C1387" s="8" t="s">
+        <v>3300</v>
+      </c>
+      <c r="D1387" s="8" t="s">
         <v>3301</v>
-      </c>
-      <c r="C1387" s="8" t="s">
-        <v>3302</v>
-      </c>
-      <c r="D1387" s="8" t="s">
-        <v>3303</v>
       </c>
     </row>
     <row r="1388" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1388" s="4" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B1388" s="4" t="s">
+        <v>3210</v>
+      </c>
+      <c r="C1388" s="4" t="s">
         <v>3211</v>
       </c>
-      <c r="B1388" s="4" t="s">
+      <c r="D1388" s="4" t="s">
         <v>3212</v>
-      </c>
-      <c r="C1388" s="4" t="s">
-        <v>3213</v>
-      </c>
-      <c r="D1388" s="4" t="s">
-        <v>3214</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="B1389" s="9" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="B1390" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="1391" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1391" s="4" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B1391" s="8" t="s">
+        <v>3303</v>
+      </c>
+      <c r="C1391" s="8" t="s">
+        <v>3304</v>
+      </c>
+      <c r="D1391" s="8" t="s">
         <v>3305</v>
-      </c>
-      <c r="C1391" s="8" t="s">
-        <v>3306</v>
-      </c>
-      <c r="D1391" s="8" t="s">
-        <v>3307</v>
       </c>
     </row>
     <row r="1392" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1392" s="4" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B1392" s="4" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C1392" s="4" t="s">
         <v>3218</v>
       </c>
-      <c r="B1392" s="4" t="s">
+      <c r="D1392" s="4" t="s">
         <v>3219</v>
-      </c>
-      <c r="C1392" s="4" t="s">
-        <v>3220</v>
-      </c>
-      <c r="D1392" s="4" t="s">
-        <v>3221</v>
       </c>
     </row>
     <row r="1393" spans="1:3" x14ac:dyDescent="0.25">
@@ -24304,60 +24365,60 @@
         <v>199</v>
       </c>
       <c r="B1393" s="9" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="1394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="B1394" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="1395" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1395" s="4" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>3309</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="1396" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1396" s="4" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="B1396" s="4" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="B1397" s="9" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="B1398" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="1399" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1399" s="4" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="B1399" s="8" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="1400" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1400" s="7" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="B1400" s="4" t="s">
         <v>547</v>
@@ -24365,79 +24426,79 @@
     </row>
     <row r="1401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="B1401" s="9" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="C1401" s="9" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="1402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>3232</v>
+      </c>
+      <c r="C1402" t="s">
         <v>3233</v>
-      </c>
-      <c r="B1402" t="s">
-        <v>3234</v>
-      </c>
-      <c r="C1402" t="s">
-        <v>3235</v>
       </c>
     </row>
     <row r="1403" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1403" s="4" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="B1403" s="8" t="s">
-        <v>3288</v>
+        <v>3286</v>
       </c>
       <c r="C1403" s="8" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="1404" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1404" s="4" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="B1404" s="4" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="C1404" s="4" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="1405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="B1405" s="10" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="1406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="B1406" s="5" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="C1406" s="5"/>
     </row>
     <row r="1407" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1407" s="4" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B1407" s="8" t="s">
         <v>3244</v>
       </c>
-      <c r="B1407" s="8" t="s">
-        <v>3246</v>
-      </c>
       <c r="C1407" s="8" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="1408" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1408" s="4" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B1408" s="4" t="s">
         <v>1117</v>
@@ -24448,230 +24509,230 @@
     </row>
     <row r="1409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B1409" s="10" t="s">
         <v>3249</v>
-      </c>
-      <c r="B1409" s="10" t="s">
-        <v>3251</v>
       </c>
     </row>
     <row r="1410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1410" t="s">
         <v>3250</v>
-      </c>
-      <c r="B1410" t="s">
-        <v>3252</v>
       </c>
     </row>
     <row r="1411" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1411" s="4" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="B1411" s="8" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
       <c r="C1411" s="8" t="s">
-        <v>3290</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="1412" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1412" s="4" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="B1412" s="4" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="C1412" s="4" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="1413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B1413" s="10" t="s">
         <v>3257</v>
       </c>
-      <c r="B1413" s="10" t="s">
+      <c r="C1413" s="10" t="s">
+        <v>3258</v>
+      </c>
+      <c r="D1413" s="10" t="s">
         <v>3259</v>
-      </c>
-      <c r="C1413" s="10" t="s">
-        <v>3260</v>
-      </c>
-      <c r="D1413" s="10" t="s">
-        <v>3261</v>
       </c>
     </row>
     <row r="1414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="B1414" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>3261</v>
+      </c>
+      <c r="D1414" t="s">
         <v>3262</v>
-      </c>
-      <c r="C1414" t="s">
-        <v>3263</v>
-      </c>
-      <c r="D1414" t="s">
-        <v>3264</v>
       </c>
     </row>
     <row r="1415" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1415" s="4" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B1415" s="8" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C1415" s="8" t="s">
         <v>3265</v>
       </c>
-      <c r="B1415" s="8" t="s">
+      <c r="D1415" s="4" t="s">
         <v>3266</v>
       </c>
-      <c r="C1415" s="8" t="s">
-        <v>3267</v>
-      </c>
-      <c r="D1415" s="4" t="s">
-        <v>3268</v>
-      </c>
       <c r="E1415" s="12" t="s">
-        <v>3348</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="1416" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1416" s="4" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="B1416" s="4" t="s">
+        <v>3343</v>
+      </c>
+      <c r="C1416" s="4" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D1416" s="4" t="s">
         <v>3345</v>
       </c>
-      <c r="C1416" s="4" t="s">
-        <v>3346</v>
-      </c>
-      <c r="D1416" s="4" t="s">
+      <c r="E1416" s="4" t="s">
         <v>3347</v>
-      </c>
-      <c r="E1416" s="4" t="s">
-        <v>3349</v>
       </c>
     </row>
     <row r="1417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1417" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B1417" s="10" t="s">
-        <v>3329</v>
+        <v>3327</v>
       </c>
     </row>
     <row r="1418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
-        <v>3406</v>
+        <v>3403</v>
       </c>
       <c r="B1418" t="s">
-        <v>3407</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="1419" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1419" s="4" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="B1419" s="8" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="C1419" s="8"/>
     </row>
     <row r="1420" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1420" s="4" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="1421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
       <c r="B1421" s="10" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="C1421" s="10" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="1422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="B1422" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="C1422" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="1423" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1423" s="4" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
       <c r="B1423" s="8" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="C1423" s="8"/>
     </row>
     <row r="1424" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1424" s="4" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B1424" s="4" t="s">
         <v>3323</v>
-      </c>
-      <c r="B1424" s="4" t="s">
-        <v>3325</v>
       </c>
     </row>
     <row r="1425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="B1425" s="10" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="1426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="B1426" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="1427" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1427" s="4" t="s">
-        <v>3342</v>
+        <v>3340</v>
       </c>
       <c r="B1427" s="8" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="C1427" s="8" t="s">
-        <v>3287</v>
+        <v>3285</v>
       </c>
       <c r="D1427" s="4" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="E1427" s="4" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="F1427" s="4" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="1428" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1428" s="4" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B1428" s="4" t="s">
+        <v>3335</v>
+      </c>
+      <c r="C1428" s="4" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D1428" s="4" t="s">
+        <v>3339</v>
+      </c>
+      <c r="E1428" s="4" t="s">
         <v>3336</v>
       </c>
-      <c r="B1428" s="4" t="s">
-        <v>3337</v>
-      </c>
-      <c r="C1428" s="4" t="s">
-        <v>3339</v>
-      </c>
-      <c r="D1428" s="4" t="s">
-        <v>3341</v>
-      </c>
-      <c r="E1428" s="4" t="s">
+      <c r="F1428" s="4" t="s">
         <v>3338</v>
-      </c>
-      <c r="F1428" s="4" t="s">
-        <v>3340</v>
       </c>
     </row>
     <row r="1429" spans="1:6" x14ac:dyDescent="0.25">
@@ -24679,32 +24740,32 @@
         <v>7</v>
       </c>
       <c r="B1429" s="10" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="1430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
       <c r="B1430" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
     </row>
     <row r="1431" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1431" s="4" t="s">
-        <v>3415</v>
+        <v>3410</v>
       </c>
       <c r="B1431" s="8" t="s">
-        <v>3376</v>
+        <v>3374</v>
       </c>
       <c r="C1431" s="8"/>
     </row>
     <row r="1432" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1432" s="4" t="s">
-        <v>3414</v>
+        <v>3409</v>
       </c>
       <c r="B1432" s="4" t="s">
-        <v>3377</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="1433" spans="1:6" x14ac:dyDescent="0.25">
@@ -24712,21 +24773,21 @@
         <v>7</v>
       </c>
       <c r="B1433" s="10" t="s">
-        <v>3380</v>
+        <v>3378</v>
       </c>
       <c r="C1433" s="10" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="1434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>3379</v>
+        <v>3377</v>
       </c>
       <c r="B1434" t="s">
-        <v>3382</v>
+        <v>3380</v>
       </c>
       <c r="C1434" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="1435" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24734,16 +24795,16 @@
         <v>7</v>
       </c>
       <c r="B1435" s="8" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="C1435" s="8"/>
     </row>
     <row r="1436" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1436" s="4" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B1436" s="4" t="s">
         <v>3384</v>
-      </c>
-      <c r="B1436" s="4" t="s">
-        <v>3386</v>
       </c>
     </row>
     <row r="1437" spans="1:6" x14ac:dyDescent="0.25">
@@ -24751,15 +24812,15 @@
         <v>199</v>
       </c>
       <c r="B1437" s="10" t="s">
-        <v>3390</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="1438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>3388</v>
+        <v>3385</v>
       </c>
       <c r="B1438" t="s">
-        <v>3389</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="1439" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24767,27 +24828,27 @@
         <v>199</v>
       </c>
       <c r="B1439" s="12" t="s">
-        <v>3396</v>
+        <v>3393</v>
       </c>
       <c r="C1439" s="12" t="s">
-        <v>3397</v>
+        <v>3394</v>
       </c>
       <c r="D1439" s="12" t="s">
-        <v>3398</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="1440" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1440" s="4" t="s">
+        <v>3388</v>
+      </c>
+      <c r="B1440" s="4" t="s">
+        <v>3390</v>
+      </c>
+      <c r="C1440" s="4" t="s">
         <v>3391</v>
       </c>
-      <c r="B1440" s="4" t="s">
-        <v>3393</v>
-      </c>
-      <c r="C1440" s="4" t="s">
-        <v>3394</v>
-      </c>
       <c r="D1440" s="4" t="s">
-        <v>3395</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
@@ -24795,15 +24856,15 @@
         <v>199</v>
       </c>
       <c r="B1441" s="10" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
-        <v>3399</v>
+        <v>3396</v>
       </c>
       <c r="B1442" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="1443" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24811,15 +24872,15 @@
         <v>7</v>
       </c>
       <c r="B1443" s="12" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="1444" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1444" s="4" t="s">
-        <v>3403</v>
+        <v>3400</v>
       </c>
       <c r="B1444" s="4" t="s">
-        <v>3404</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
@@ -24827,15 +24888,15 @@
         <v>7</v>
       </c>
       <c r="B1445" s="10" t="s">
-        <v>3418</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
-        <v>3416</v>
+        <v>3411</v>
       </c>
       <c r="B1446" t="s">
-        <v>3417</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="1447" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24843,15 +24904,15 @@
         <v>7</v>
       </c>
       <c r="B1447" s="12" t="s">
-        <v>3421</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="1448" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1448" s="4" t="s">
-        <v>3419</v>
+        <v>3414</v>
       </c>
       <c r="B1448" s="4" t="s">
-        <v>3420</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
@@ -24859,15 +24920,15 @@
         <v>7</v>
       </c>
       <c r="B1449" s="10" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
-        <v>3422</v>
+        <v>3417</v>
       </c>
       <c r="B1450" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="1451" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24875,15 +24936,15 @@
         <v>7</v>
       </c>
       <c r="B1451" s="12" t="s">
-        <v>3421</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="1452" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1452" s="4" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="B1452" s="4" t="s">
-        <v>3426</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
@@ -24891,47 +24952,76 @@
         <v>7</v>
       </c>
       <c r="B1453" s="10" t="s">
-        <v>3428</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>3427</v>
+        <v>3422</v>
       </c>
       <c r="B1454" t="s">
-        <v>3429</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="1455" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1455" s="4" t="s">
-        <v>3436</v>
+        <v>3431</v>
       </c>
       <c r="B1455" s="12" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="1456" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1456" s="4" t="s">
-        <v>3437</v>
+        <v>3432</v>
       </c>
       <c r="B1456" s="4" t="s">
-        <v>3438</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>3440</v>
+        <v>3435</v>
       </c>
       <c r="B1457" s="10" t="s">
-        <v>3443</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>3437</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1459" s="13" t="s">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1460" s="13" t="s">
         <v>3441</v>
       </c>
-      <c r="B1458" t="s">
+      <c r="B1460" s="13" t="s">
         <v>3442</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1461" t="s">
+        <v>3452</v>
+      </c>
+      <c r="B1461" s="10" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1462" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>3454</v>
       </c>
     </row>
   </sheetData>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC297FFD-2BA1-47DE-B3C6-D72E5476F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BC3D44-69BF-4907-A779-FE0AE52F89D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="3456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="3457">
   <si>
     <t>2706</t>
   </si>
@@ -10404,6 +10404,9 @@
   </si>
   <si>
     <t>5000</t>
+  </si>
+  <si>
+    <t>2786</t>
   </si>
 </sst>
 </file>
@@ -19492,8 +19495,8 @@
       </c>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A915" t="s">
-        <v>7</v>
+      <c r="A915" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B915" t="s">
         <v>2018</v>
@@ -24936,7 +24939,7 @@
         <v>7</v>
       </c>
       <c r="B1451" s="12" t="s">
-        <v>3416</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="1452" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BC3D44-69BF-4907-A779-FE0AE52F89D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708A429F-C025-48E9-AE42-AC9D1F2CBE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8381,9 +8381,6 @@
     <t>Venango Trails|Pool</t>
   </si>
   <si>
-    <t>C-VE20</t>
-  </si>
-  <si>
     <t>2546</t>
   </si>
   <si>
@@ -10407,6 +10404,9 @@
   </si>
   <si>
     <t>2786</t>
+  </si>
+  <si>
+    <t>C-VE120</t>
   </si>
 </sst>
 </file>
@@ -10817,7 +10817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1462"/>
+  <dimension ref="A1:P1463"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -10840,18 +10840,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10950,7 +10950,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11042,7 +11042,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>44</v>
@@ -11086,7 +11086,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>55</v>
@@ -11156,7 +11156,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>71</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>93</v>
@@ -11288,7 +11288,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>155</v>
@@ -11556,7 +11556,7 @@
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>164</v>
@@ -11778,7 +11778,7 @@
         <v>218</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11789,7 +11789,7 @@
         <v>220</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -11870,7 +11870,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B111" t="s">
         <v>241</v>
@@ -11958,7 +11958,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B119" t="s">
         <v>262</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="121" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>267</v>
@@ -12110,7 +12110,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="B135" t="s">
         <v>295</v>
@@ -12188,10 +12188,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B144" t="s">
         <v>3270</v>
-      </c>
-      <c r="B144" t="s">
-        <v>3271</v>
       </c>
     </row>
     <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12234,7 +12234,7 @@
     </row>
     <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>322</v>
@@ -12492,7 +12492,7 @@
     </row>
     <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>389</v>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B199" t="s">
         <v>456</v>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B239" t="s">
         <v>536</v>
@@ -13154,7 +13154,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="B243" t="s">
         <v>568</v>
@@ -13192,7 +13192,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B247" t="s">
         <v>548</v>
@@ -13278,7 +13278,7 @@
     </row>
     <row r="257" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>576</v>
@@ -13289,7 +13289,7 @@
         <v>573</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -13305,7 +13305,7 @@
         <v>577</v>
       </c>
       <c r="B260" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="261" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13338,7 +13338,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="B263" t="s">
         <v>581</v>
@@ -13672,10 +13672,10 @@
     </row>
     <row r="298" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>3272</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>3273</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -13908,7 +13908,7 @@
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>715</v>
@@ -13916,7 +13916,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B327" t="s">
         <v>716</v>
@@ -14372,7 +14372,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B375" t="s">
         <v>825</v>
@@ -14410,7 +14410,7 @@
         <v>833</v>
       </c>
       <c r="C379" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -14512,7 +14512,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="B391" t="s">
         <v>849</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="401" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>873</v>
@@ -14654,15 +14654,15 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B408" t="s">
         <v>3274</v>
-      </c>
-      <c r="B408" t="s">
-        <v>3275</v>
       </c>
     </row>
     <row r="409" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>885</v>
@@ -14802,7 +14802,7 @@
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>913</v>
@@ -15289,7 +15289,7 @@
         <v>1034</v>
       </c>
       <c r="B475" s="10" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -15318,7 +15318,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="B479" t="s">
         <v>1041</v>
@@ -15398,7 +15398,7 @@
     </row>
     <row r="489" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>1062</v>
@@ -15470,7 +15470,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B495" t="s">
         <v>1075</v>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>1080</v>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B579" t="s">
         <v>1251</v>
@@ -16464,7 +16464,7 @@
     </row>
     <row r="605" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>1299</v>
@@ -16828,7 +16828,7 @@
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>1384</v>
@@ -16974,7 +16974,7 @@
     </row>
     <row r="665" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>1419</v>
@@ -17050,7 +17050,7 @@
     </row>
     <row r="673" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>1439</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="693" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>1489</v>
@@ -17297,13 +17297,13 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B696" t="s">
         <v>3427</v>
       </c>
-      <c r="B696" t="s">
+      <c r="C696" t="s">
         <v>3428</v>
-      </c>
-      <c r="C696" t="s">
-        <v>3429</v>
       </c>
     </row>
     <row r="697" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17368,7 +17368,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="B703" t="s">
         <v>1513</v>
@@ -17768,7 +17768,7 @@
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>1612</v>
@@ -17912,7 +17912,7 @@
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B756" t="s">
         <v>1640</v>
@@ -18036,7 +18036,7 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B767" t="s">
         <v>1674</v>
@@ -18088,7 +18088,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B772" t="s">
         <v>1686</v>
@@ -18198,7 +18198,7 @@
     </row>
     <row r="785" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>1713</v>
@@ -18220,7 +18220,7 @@
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B787" t="s">
         <v>1718</v>
@@ -18254,7 +18254,7 @@
     </row>
     <row r="789" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>1722</v>
@@ -18503,13 +18503,13 @@
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B816" t="s">
         <v>3350</v>
       </c>
-      <c r="B816" t="s">
+      <c r="C816" t="s">
         <v>3351</v>
-      </c>
-      <c r="C816" t="s">
-        <v>3352</v>
       </c>
     </row>
     <row r="817" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18624,7 +18624,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B827" t="s">
         <v>1818</v>
@@ -18806,15 +18806,15 @@
     </row>
     <row r="846" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B846" s="2" t="s">
         <v>3276</v>
-      </c>
-      <c r="B846" s="2" t="s">
-        <v>3277</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B847" t="s">
         <v>1864</v>
@@ -18838,10 +18838,10 @@
     </row>
     <row r="850" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B850" s="2" t="s">
         <v>3278</v>
-      </c>
-      <c r="B850" s="2" t="s">
-        <v>3279</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.25">
@@ -19132,7 +19132,7 @@
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B883" t="s">
         <v>1934</v>
@@ -19170,7 +19170,7 @@
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B887" t="s">
         <v>1943</v>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="889" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>1948</v>
@@ -19286,7 +19286,7 @@
     </row>
     <row r="897" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>1973</v>
@@ -19414,10 +19414,10 @@
         <v>2002</v>
       </c>
       <c r="C907" s="10" t="s">
+        <v>3446</v>
+      </c>
+      <c r="D907" s="10" t="s">
         <v>3447</v>
-      </c>
-      <c r="D907" s="10" t="s">
-        <v>3448</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
@@ -19425,13 +19425,13 @@
         <v>2003</v>
       </c>
       <c r="B908" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C908" t="s">
         <v>3449</v>
       </c>
-      <c r="C908" t="s">
+      <c r="D908" t="s">
         <v>3450</v>
-      </c>
-      <c r="D908" t="s">
-        <v>3451</v>
       </c>
     </row>
     <row r="909" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19480,7 +19480,7 @@
     </row>
     <row r="913" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>2015</v>
@@ -19636,7 +19636,7 @@
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B931" t="s">
         <v>2052</v>
@@ -19708,7 +19708,7 @@
     </row>
     <row r="937" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>2071</v>
@@ -19940,10 +19940,10 @@
     </row>
     <row r="960" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
+        <v>3397</v>
+      </c>
+      <c r="B960" t="s">
         <v>3398</v>
-      </c>
-      <c r="B960" t="s">
-        <v>3399</v>
       </c>
     </row>
     <row r="961" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20056,7 +20056,7 @@
     </row>
     <row r="973" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B973" s="2" t="s">
         <v>2157</v>
@@ -20354,7 +20354,7 @@
     </row>
     <row r="1005" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1005" s="2" t="s">
         <v>2226</v>
@@ -20453,7 +20453,7 @@
         <v>2253</v>
       </c>
       <c r="C1014" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="1015" spans="1:16" x14ac:dyDescent="0.25">
@@ -20590,52 +20590,52 @@
     </row>
     <row r="1024" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B1024" t="s">
         <v>3353</v>
       </c>
-      <c r="B1024" t="s">
+      <c r="C1024" t="s">
         <v>3354</v>
       </c>
-      <c r="C1024" t="s">
+      <c r="D1024" t="s">
         <v>3355</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="E1024" t="s">
         <v>3356</v>
       </c>
-      <c r="E1024" t="s">
+      <c r="F1024" t="s">
         <v>3357</v>
       </c>
-      <c r="F1024" t="s">
+      <c r="G1024" t="s">
         <v>3358</v>
       </c>
-      <c r="G1024" t="s">
+      <c r="H1024" t="s">
         <v>3359</v>
       </c>
-      <c r="H1024" t="s">
+      <c r="I1024" t="s">
         <v>3360</v>
       </c>
-      <c r="I1024" t="s">
+      <c r="J1024" t="s">
+        <v>3360</v>
+      </c>
+      <c r="K1024" t="s">
         <v>3361</v>
       </c>
-      <c r="J1024" t="s">
-        <v>3361</v>
-      </c>
-      <c r="K1024" t="s">
+      <c r="L1024" t="s">
         <v>3362</v>
       </c>
-      <c r="L1024" t="s">
+      <c r="M1024" t="s">
         <v>3363</v>
       </c>
-      <c r="M1024" t="s">
+      <c r="N1024" t="s">
         <v>3364</v>
       </c>
-      <c r="N1024" t="s">
+      <c r="O1024" t="s">
         <v>3365</v>
       </c>
-      <c r="O1024" t="s">
+      <c r="P1024" t="s">
         <v>3366</v>
-      </c>
-      <c r="P1024" t="s">
-        <v>3367</v>
       </c>
     </row>
     <row r="1025" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20656,7 +20656,7 @@
     </row>
     <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1027" t="s">
         <v>2292</v>
@@ -20678,7 +20678,7 @@
     </row>
     <row r="1029" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B1029" s="2" t="s">
         <v>2297</v>
@@ -20747,7 +20747,7 @@
         <v>2314</v>
       </c>
       <c r="B1035" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="C1035" s="10"/>
     </row>
@@ -20841,7 +20841,7 @@
         <v>2340</v>
       </c>
       <c r="I1041" s="11" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="1042" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20867,7 +20867,7 @@
         <v>2347</v>
       </c>
       <c r="H1042" s="2" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="I1042" s="2" t="s">
         <v>2348</v>
@@ -21029,7 +21029,7 @@
     </row>
     <row r="1057" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1057" s="2" t="s">
         <v>2389</v>
@@ -21651,7 +21651,7 @@
     </row>
     <row r="1125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1125" s="2" t="s">
         <v>2542</v>
@@ -22179,16 +22179,16 @@
     </row>
     <row r="1182" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="2" t="s">
+        <v>3367</v>
+      </c>
+      <c r="B1182" s="2" t="s">
         <v>3368</v>
       </c>
-      <c r="B1182" s="2" t="s">
+      <c r="C1182" s="2" t="s">
         <v>3369</v>
       </c>
-      <c r="C1182" s="2" t="s">
+      <c r="D1182" s="2" t="s">
         <v>3370</v>
-      </c>
-      <c r="D1182" s="2" t="s">
-        <v>3371</v>
       </c>
     </row>
     <row r="1183" spans="1:4" x14ac:dyDescent="0.25">
@@ -22379,7 +22379,7 @@
     </row>
     <row r="1201" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1201" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B1201" s="2" t="s">
         <v>2702</v>
@@ -22645,18 +22645,18 @@
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B1223" t="s">
         <v>2781</v>
-      </c>
-      <c r="B1223" t="s">
-        <v>2782</v>
       </c>
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B1224" t="s">
         <v>2783</v>
-      </c>
-      <c r="B1224" t="s">
-        <v>2784</v>
       </c>
     </row>
     <row r="1225" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22664,79 +22664,79 @@
         <v>7</v>
       </c>
       <c r="B1225" s="2" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="1226" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1226" s="2" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B1226" s="2" t="s">
         <v>2786</v>
-      </c>
-      <c r="B1226" s="2" t="s">
-        <v>2787</v>
       </c>
     </row>
     <row r="1227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B1227" t="s">
         <v>2788</v>
-      </c>
-      <c r="B1227" t="s">
-        <v>2789</v>
       </c>
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B1228" t="s">
         <v>2790</v>
-      </c>
-      <c r="B1228" t="s">
-        <v>2791</v>
       </c>
     </row>
     <row r="1229" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1229" s="2" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B1229" s="2" t="s">
         <v>2792</v>
-      </c>
-      <c r="B1229" s="2" t="s">
-        <v>2793</v>
       </c>
     </row>
     <row r="1230" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1230" s="2" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B1230" s="2" t="s">
         <v>2794</v>
-      </c>
-      <c r="B1230" s="2" t="s">
-        <v>2795</v>
       </c>
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B1231" t="s">
         <v>2796</v>
-      </c>
-      <c r="B1231" t="s">
-        <v>2797</v>
       </c>
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="B1232" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="1233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1233" s="2" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B1233" s="2" t="s">
         <v>2799</v>
-      </c>
-      <c r="B1233" s="2" t="s">
-        <v>2800</v>
       </c>
     </row>
     <row r="1234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1234" s="2" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B1234" s="2" t="s">
         <v>2804</v>
-      </c>
-      <c r="B1234" s="2" t="s">
-        <v>2805</v>
       </c>
     </row>
     <row r="1235" spans="1:3" x14ac:dyDescent="0.25">
@@ -22744,21 +22744,21 @@
         <v>199</v>
       </c>
       <c r="B1235" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C1235" t="s">
         <v>2802</v>
-      </c>
-      <c r="C1235" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="B1236" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C1236" t="s">
         <v>2807</v>
-      </c>
-      <c r="C1236" t="s">
-        <v>2808</v>
       </c>
     </row>
     <row r="1237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22766,53 +22766,53 @@
         <v>7</v>
       </c>
       <c r="B1237" s="2" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="1238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1238" s="2" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1238" s="2" t="s">
         <v>2811</v>
-      </c>
-      <c r="B1238" s="2" t="s">
-        <v>2812</v>
       </c>
     </row>
     <row r="1239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B1239" t="s">
         <v>2813</v>
       </c>
-      <c r="B1239" t="s">
+      <c r="C1239" t="s">
         <v>2814</v>
-      </c>
-      <c r="C1239" t="s">
-        <v>2815</v>
       </c>
     </row>
     <row r="1240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B1240" t="s">
         <v>2816</v>
       </c>
-      <c r="B1240" t="s">
+      <c r="C1240" t="s">
         <v>2817</v>
-      </c>
-      <c r="C1240" t="s">
-        <v>2818</v>
       </c>
     </row>
     <row r="1241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="2" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B1241" s="2" t="s">
         <v>2819</v>
-      </c>
-      <c r="B1241" s="2" t="s">
-        <v>2820</v>
       </c>
     </row>
     <row r="1242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="2" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B1242" s="2" t="s">
         <v>2821</v>
-      </c>
-      <c r="B1242" s="2" t="s">
-        <v>2822</v>
       </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.25">
@@ -22820,15 +22820,15 @@
         <v>85</v>
       </c>
       <c r="B1243" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B1244" t="s">
         <v>2824</v>
-      </c>
-      <c r="B1244" t="s">
-        <v>2825</v>
       </c>
     </row>
     <row r="1245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -22836,15 +22836,15 @@
         <v>199</v>
       </c>
       <c r="B1245" s="2" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="1246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1246" s="2" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B1246" s="2" t="s">
         <v>2827</v>
-      </c>
-      <c r="B1246" s="2" t="s">
-        <v>2828</v>
       </c>
     </row>
     <row r="1247" spans="1:3" x14ac:dyDescent="0.25">
@@ -22852,95 +22852,95 @@
         <v>7</v>
       </c>
       <c r="B1247" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B1248" t="s">
         <v>2830</v>
-      </c>
-      <c r="B1248" t="s">
-        <v>2831</v>
       </c>
     </row>
     <row r="1249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="2" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B1249" s="2" t="s">
         <v>2832</v>
-      </c>
-      <c r="B1249" s="2" t="s">
-        <v>2833</v>
       </c>
     </row>
     <row r="1250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="2" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B1250" s="2" t="s">
         <v>2835</v>
-      </c>
-      <c r="B1250" s="2" t="s">
-        <v>2836</v>
       </c>
     </row>
     <row r="1251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="B1251" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B1252" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1253" s="2" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B1253" s="2" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1254" s="2" t="s">
+        <v>2840</v>
+      </c>
+      <c r="B1254" s="2" t="s">
         <v>2841</v>
-      </c>
-      <c r="B1254" s="2" t="s">
-        <v>2842</v>
       </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="B1255" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="B1256" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="1257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1257" s="2" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B1257" s="2" t="s">
         <v>2845</v>
-      </c>
-      <c r="B1257" s="2" t="s">
-        <v>2846</v>
       </c>
     </row>
     <row r="1258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1258" s="2" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B1258" s="2" t="s">
         <v>2847</v>
-      </c>
-      <c r="B1258" s="2" t="s">
-        <v>2848</v>
       </c>
     </row>
     <row r="1259" spans="1:3" x14ac:dyDescent="0.25">
@@ -22948,113 +22948,113 @@
         <v>7</v>
       </c>
       <c r="B1259" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1259" t="s">
         <v>2849</v>
-      </c>
-      <c r="C1259" t="s">
-        <v>2850</v>
       </c>
     </row>
     <row r="1260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B1260" t="s">
         <v>2851</v>
       </c>
-      <c r="B1260" t="s">
+      <c r="C1260" t="s">
         <v>2852</v>
-      </c>
-      <c r="C1260" t="s">
-        <v>2853</v>
       </c>
     </row>
     <row r="1261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1261" s="2" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B1261" s="2" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C1261" s="2" t="s">
         <v>2926</v>
-      </c>
-      <c r="C1261" s="2" t="s">
-        <v>2927</v>
       </c>
     </row>
     <row r="1262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1262" s="2" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="B1262" s="2" t="s">
+        <v>2929</v>
+      </c>
+      <c r="C1262" s="2" t="s">
         <v>2930</v>
-      </c>
-      <c r="C1262" s="2" t="s">
-        <v>2931</v>
       </c>
     </row>
     <row r="1263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B1263" t="s">
         <v>2856</v>
-      </c>
-      <c r="B1263" t="s">
-        <v>2857</v>
       </c>
     </row>
     <row r="1264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B1264" t="s">
         <v>2858</v>
-      </c>
-      <c r="B1264" t="s">
-        <v>2859</v>
       </c>
     </row>
     <row r="1265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1265" s="2" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B1265" s="2" t="s">
         <v>2860</v>
-      </c>
-      <c r="B1265" s="2" t="s">
-        <v>2861</v>
       </c>
     </row>
     <row r="1266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1266" s="2" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B1266" s="2" t="s">
         <v>2862</v>
-      </c>
-      <c r="B1266" s="2" t="s">
-        <v>2863</v>
       </c>
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B1267" t="s">
         <v>2864</v>
-      </c>
-      <c r="B1267" t="s">
-        <v>2865</v>
       </c>
     </row>
     <row r="1268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B1268" t="s">
         <v>2868</v>
-      </c>
-      <c r="B1268" t="s">
-        <v>2869</v>
       </c>
     </row>
     <row r="1269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1269" s="2" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="B1269" s="2" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C1269" s="2" t="s">
         <v>2866</v>
-      </c>
-      <c r="C1269" s="2" t="s">
-        <v>2867</v>
       </c>
     </row>
     <row r="1270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1270" s="2" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B1270" s="2" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C1270" s="2" t="s">
         <v>2870</v>
-      </c>
-      <c r="C1270" s="2" t="s">
-        <v>2871</v>
       </c>
     </row>
     <row r="1271" spans="1:3" x14ac:dyDescent="0.25">
@@ -23062,53 +23062,53 @@
         <v>7</v>
       </c>
       <c r="B1271" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="1272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B1272" t="s">
         <v>2875</v>
-      </c>
-      <c r="B1272" t="s">
-        <v>2876</v>
       </c>
     </row>
     <row r="1273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1273" s="2" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B1273" s="2" t="s">
         <v>2877</v>
       </c>
-      <c r="B1273" s="2" t="s">
+      <c r="C1273" s="2" t="s">
         <v>2878</v>
-      </c>
-      <c r="C1273" s="2" t="s">
-        <v>2879</v>
       </c>
     </row>
     <row r="1274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1274" s="2" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B1274" s="2" t="s">
         <v>2880</v>
       </c>
-      <c r="B1274" s="2" t="s">
+      <c r="C1274" s="2" t="s">
         <v>2881</v>
-      </c>
-      <c r="C1274" s="2" t="s">
-        <v>2882</v>
       </c>
     </row>
     <row r="1275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B1275" t="s">
         <v>2883</v>
-      </c>
-      <c r="B1275" t="s">
-        <v>2884</v>
       </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B1276" t="s">
         <v>2885</v>
-      </c>
-      <c r="B1276" t="s">
-        <v>2886</v>
       </c>
     </row>
     <row r="1277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23116,15 +23116,15 @@
         <v>7</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="1278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1278" s="2" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B1278" s="2" t="s">
         <v>2888</v>
-      </c>
-      <c r="B1278" s="2" t="s">
-        <v>2889</v>
       </c>
     </row>
     <row r="1279" spans="1:3" x14ac:dyDescent="0.25">
@@ -23132,31 +23132,31 @@
         <v>7</v>
       </c>
       <c r="B1279" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="1280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B1280" t="s">
         <v>2891</v>
-      </c>
-      <c r="B1280" t="s">
-        <v>2892</v>
       </c>
     </row>
     <row r="1281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1281" s="2" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B1281" s="2" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="1282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1282" s="2" t="s">
+        <v>2893</v>
+      </c>
+      <c r="B1282" s="2" t="s">
         <v>2894</v>
-      </c>
-      <c r="B1282" s="2" t="s">
-        <v>2895</v>
       </c>
     </row>
     <row r="1283" spans="1:3" x14ac:dyDescent="0.25">
@@ -23164,119 +23164,119 @@
         <v>7</v>
       </c>
       <c r="B1283" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="1284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B1284" t="s">
         <v>2897</v>
-      </c>
-      <c r="B1284" t="s">
-        <v>2898</v>
       </c>
     </row>
     <row r="1285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1285" s="2" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B1285" s="2" t="s">
         <v>2899</v>
-      </c>
-      <c r="B1285" s="2" t="s">
-        <v>2900</v>
       </c>
     </row>
     <row r="1286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1286" s="2" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B1286" s="2" t="s">
         <v>2901</v>
-      </c>
-      <c r="B1286" s="2" t="s">
-        <v>2902</v>
       </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B1287" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C1287" t="s">
         <v>2903</v>
-      </c>
-      <c r="C1287" t="s">
-        <v>2904</v>
       </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B1288" t="s">
         <v>2905</v>
       </c>
-      <c r="B1288" t="s">
+      <c r="C1288" t="s">
         <v>2906</v>
-      </c>
-      <c r="C1288" t="s">
-        <v>2907</v>
       </c>
     </row>
     <row r="1289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1289" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B1289" s="2" t="s">
         <v>2908</v>
       </c>
-      <c r="B1289" s="2" t="s">
+      <c r="C1289" s="2" t="s">
         <v>2909</v>
-      </c>
-      <c r="C1289" s="2" t="s">
-        <v>2910</v>
       </c>
     </row>
     <row r="1290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1290" s="2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1290" s="2" t="s">
         <v>2911</v>
       </c>
-      <c r="B1290" s="2" t="s">
+      <c r="C1290" s="2" t="s">
         <v>2912</v>
-      </c>
-      <c r="C1290" s="2" t="s">
-        <v>2913</v>
       </c>
     </row>
     <row r="1291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B1291" t="s">
         <v>2914</v>
       </c>
-      <c r="B1291" t="s">
+      <c r="C1291" t="s">
         <v>2915</v>
-      </c>
-      <c r="C1291" t="s">
-        <v>2916</v>
       </c>
     </row>
     <row r="1292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B1292" t="s">
         <v>2917</v>
       </c>
-      <c r="B1292" t="s">
+      <c r="C1292" t="s">
         <v>2918</v>
-      </c>
-      <c r="C1292" t="s">
-        <v>2919</v>
       </c>
     </row>
     <row r="1293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1293" s="2" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1293" s="2" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1293" s="2" t="s">
         <v>2920</v>
-      </c>
-      <c r="C1293" s="2" t="s">
-        <v>2921</v>
       </c>
     </row>
     <row r="1294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1294" s="2" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B1294" s="2" t="s">
         <v>2922</v>
       </c>
-      <c r="B1294" s="2" t="s">
+      <c r="C1294" s="2" t="s">
         <v>2923</v>
-      </c>
-      <c r="C1294" s="2" t="s">
-        <v>2924</v>
       </c>
     </row>
     <row r="1295" spans="1:3" x14ac:dyDescent="0.25">
@@ -23284,59 +23284,59 @@
         <v>7</v>
       </c>
       <c r="B1295" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="1296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B1296" t="s">
         <v>2928</v>
-      </c>
-      <c r="B1296" t="s">
-        <v>2929</v>
       </c>
     </row>
     <row r="1297" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1297" s="2" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B1297" s="2" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C1297" s="2" t="s">
         <v>2932</v>
-      </c>
-      <c r="C1297" s="2" t="s">
-        <v>2933</v>
       </c>
     </row>
     <row r="1298" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1298" s="2" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B1298" s="2" t="s">
         <v>2934</v>
       </c>
-      <c r="B1298" s="2" t="s">
+      <c r="C1298" s="2" t="s">
         <v>2935</v>
-      </c>
-      <c r="C1298" s="2" t="s">
-        <v>2936</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B1299" t="s">
         <v>2937</v>
       </c>
-      <c r="B1299" t="s">
+      <c r="C1299" t="s">
         <v>2938</v>
-      </c>
-      <c r="C1299" t="s">
-        <v>2939</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B1300" t="s">
         <v>2940</v>
       </c>
-      <c r="B1300" t="s">
+      <c r="C1300" t="s">
         <v>2941</v>
-      </c>
-      <c r="C1300" t="s">
-        <v>2942</v>
       </c>
     </row>
     <row r="1301" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23344,513 +23344,513 @@
         <v>199</v>
       </c>
       <c r="B1301" s="2" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="1302" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1302" s="2" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B1302" s="2" t="s">
         <v>2944</v>
-      </c>
-      <c r="B1302" s="2" t="s">
-        <v>2945</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1303" t="s">
+        <v>2945</v>
+      </c>
+      <c r="C1303" t="s">
         <v>2946</v>
-      </c>
-      <c r="C1303" t="s">
-        <v>2947</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1304" t="s">
         <v>2951</v>
       </c>
-      <c r="B1304" t="s">
+      <c r="C1304" t="s">
         <v>2952</v>
-      </c>
-      <c r="C1304" t="s">
-        <v>2953</v>
       </c>
     </row>
     <row r="1305" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1305" s="2" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B1305" s="2" t="s">
         <v>2957</v>
-      </c>
-      <c r="B1305" s="2" t="s">
-        <v>2958</v>
       </c>
     </row>
     <row r="1306" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1306" s="2" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B1306" s="2" t="s">
         <v>2959</v>
-      </c>
-      <c r="B1306" s="2" t="s">
-        <v>2960</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B1307" t="s">
         <v>2961</v>
-      </c>
-      <c r="B1307" t="s">
-        <v>2962</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B1308" t="s">
         <v>2963</v>
-      </c>
-      <c r="B1308" t="s">
-        <v>2964</v>
       </c>
     </row>
     <row r="1309" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="2" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B1309" s="2" t="s">
         <v>2965</v>
-      </c>
-      <c r="B1309" s="2" t="s">
-        <v>2966</v>
       </c>
     </row>
     <row r="1310" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1310" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B1310" s="2" t="s">
         <v>3341</v>
-      </c>
-      <c r="B1310" s="2" t="s">
-        <v>3342</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B1311" t="s">
         <v>2967</v>
       </c>
-      <c r="B1311" t="s">
+      <c r="C1311" t="s">
         <v>2968</v>
       </c>
-      <c r="C1311" t="s">
+      <c r="D1311" t="s">
         <v>2969</v>
-      </c>
-      <c r="D1311" t="s">
-        <v>2970</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1312" t="s">
         <v>2971</v>
       </c>
-      <c r="B1312" t="s">
+      <c r="C1312" t="s">
         <v>2972</v>
       </c>
-      <c r="C1312" t="s">
+      <c r="D1312" t="s">
         <v>2973</v>
-      </c>
-      <c r="D1312" t="s">
-        <v>2974</v>
       </c>
     </row>
     <row r="1313" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="2" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="B1313" s="2" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C1313" s="2" t="s">
         <v>2948</v>
       </c>
-      <c r="C1313" s="2" t="s">
+      <c r="D1313" s="2" t="s">
         <v>2949</v>
-      </c>
-      <c r="D1313" s="2" t="s">
-        <v>2950</v>
       </c>
     </row>
     <row r="1314" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="2" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B1314" s="2" t="s">
+        <v>2953</v>
+      </c>
+      <c r="C1314" s="2" t="s">
         <v>2954</v>
       </c>
-      <c r="C1314" s="2" t="s">
+      <c r="D1314" s="2" t="s">
         <v>2955</v>
-      </c>
-      <c r="D1314" s="2" t="s">
-        <v>2956</v>
       </c>
     </row>
     <row r="1315" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="2" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B1315" s="2" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C1315" s="2" t="s">
         <v>2979</v>
       </c>
-      <c r="C1315" s="2" t="s">
+      <c r="D1315" s="2" t="s">
         <v>2980</v>
-      </c>
-      <c r="D1315" s="2" t="s">
-        <v>2981</v>
       </c>
     </row>
     <row r="1316" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="2" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B1316" s="2" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C1316" s="2" t="s">
         <v>2982</v>
       </c>
-      <c r="C1316" s="2" t="s">
+      <c r="D1316" s="2" t="s">
         <v>2983</v>
-      </c>
-      <c r="D1316" s="2" t="s">
-        <v>2984</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B1317" t="s">
         <v>2985</v>
       </c>
-      <c r="B1317" t="s">
+      <c r="C1317" t="s">
         <v>2986</v>
       </c>
-      <c r="C1317" t="s">
+      <c r="D1317" t="s">
         <v>2987</v>
-      </c>
-      <c r="D1317" t="s">
-        <v>2988</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B1318" t="s">
         <v>2989</v>
       </c>
-      <c r="B1318" t="s">
+      <c r="C1318" t="s">
         <v>2990</v>
       </c>
-      <c r="C1318" t="s">
+      <c r="D1318" t="s">
         <v>2991</v>
-      </c>
-      <c r="D1318" t="s">
-        <v>2992</v>
       </c>
     </row>
     <row r="1319" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1319" s="2" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B1319" s="2" t="s">
         <v>2993</v>
-      </c>
-      <c r="B1319" s="2" t="s">
-        <v>2994</v>
       </c>
     </row>
     <row r="1320" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1320" s="2" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B1320" s="2" t="s">
         <v>2995</v>
-      </c>
-      <c r="B1320" s="2" t="s">
-        <v>2996</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B1321" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B1322" t="s">
         <v>3001</v>
-      </c>
-      <c r="B1322" t="s">
-        <v>3002</v>
       </c>
     </row>
     <row r="1323" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1323" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B1323" s="2" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C1323" s="2" t="s">
         <v>2998</v>
       </c>
-      <c r="C1323" s="2" t="s">
+      <c r="D1323" s="2" t="s">
         <v>2999</v>
-      </c>
-      <c r="D1323" s="2" t="s">
-        <v>3000</v>
       </c>
     </row>
     <row r="1324" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1324" s="2" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B1324" s="2" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C1324" s="2" t="s">
         <v>3003</v>
       </c>
-      <c r="C1324" s="2" t="s">
+      <c r="D1324" s="2" t="s">
         <v>3004</v>
-      </c>
-      <c r="D1324" s="2" t="s">
-        <v>3005</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B1325" t="s">
         <v>3008</v>
-      </c>
-      <c r="B1325" t="s">
-        <v>3009</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
+        <v>3009</v>
+      </c>
+      <c r="B1326" t="s">
         <v>3010</v>
-      </c>
-      <c r="B1326" t="s">
-        <v>3011</v>
       </c>
     </row>
     <row r="1327" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1327" s="2" t="s">
+        <v>3011</v>
+      </c>
+      <c r="B1327" s="2" t="s">
         <v>3012</v>
       </c>
-      <c r="B1327" s="2" t="s">
+      <c r="C1327" s="2" t="s">
         <v>3013</v>
       </c>
-      <c r="C1327" s="2" t="s">
+      <c r="D1327" s="2" t="s">
         <v>3014</v>
-      </c>
-      <c r="D1327" s="2" t="s">
-        <v>3015</v>
       </c>
     </row>
     <row r="1328" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1328" s="2" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B1328" s="2" t="s">
         <v>3016</v>
       </c>
-      <c r="B1328" s="2" t="s">
+      <c r="C1328" s="2" t="s">
         <v>3017</v>
       </c>
-      <c r="C1328" s="2" t="s">
-        <v>3018</v>
-      </c>
       <c r="D1328" s="2" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B1329" t="s">
         <v>3019</v>
-      </c>
-      <c r="B1329" t="s">
-        <v>3020</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
+        <v>3021</v>
+      </c>
+      <c r="B1330" t="s">
         <v>3022</v>
-      </c>
-      <c r="B1330" t="s">
-        <v>3023</v>
       </c>
     </row>
     <row r="1331" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1331" s="2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B1331" s="2" t="s">
         <v>3025</v>
       </c>
-      <c r="B1331" s="2" t="s">
+      <c r="C1331" s="2" t="s">
         <v>3026</v>
       </c>
-      <c r="C1331" s="2" t="s">
+      <c r="D1331" s="2" t="s">
         <v>3027</v>
-      </c>
-      <c r="D1331" s="2" t="s">
-        <v>3028</v>
       </c>
     </row>
     <row r="1332" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1332" s="2" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B1332" s="2" t="s">
         <v>3029</v>
       </c>
-      <c r="B1332" s="2" t="s">
+      <c r="C1332" s="2" t="s">
         <v>3030</v>
       </c>
-      <c r="C1332" s="2" t="s">
+      <c r="D1332" s="2" t="s">
         <v>3031</v>
-      </c>
-      <c r="D1332" s="2" t="s">
-        <v>3032</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B1333" t="s">
         <v>3033</v>
       </c>
-      <c r="B1333" t="s">
+      <c r="C1333" t="s">
         <v>3034</v>
-      </c>
-      <c r="C1333" t="s">
-        <v>3035</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B1334" t="s">
         <v>3036</v>
       </c>
-      <c r="B1334" t="s">
+      <c r="C1334" t="s">
         <v>3037</v>
-      </c>
-      <c r="C1334" t="s">
-        <v>3038</v>
       </c>
     </row>
     <row r="1335" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1335" s="2" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1336" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1336" s="2" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B1337" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B1338" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="1339" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1339" s="2" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1339" s="2" t="s">
         <v>3045</v>
       </c>
-      <c r="B1339" s="2" t="s">
+      <c r="C1339" s="2" t="s">
         <v>3046</v>
-      </c>
-      <c r="C1339" s="2" t="s">
-        <v>3047</v>
       </c>
     </row>
     <row r="1340" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1340" s="2" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B1340" s="2" t="s">
         <v>3048</v>
       </c>
-      <c r="B1340" s="2" t="s">
+      <c r="C1340" s="2" t="s">
         <v>3049</v>
-      </c>
-      <c r="C1340" s="2" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B1341" t="s">
         <v>3051</v>
-      </c>
-      <c r="B1341" t="s">
-        <v>3052</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B1342" t="s">
         <v>3053</v>
-      </c>
-      <c r="B1342" t="s">
-        <v>3054</v>
       </c>
     </row>
     <row r="1343" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1343" s="2" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="1344" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1344" s="2" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1345" t="s">
         <v>3057</v>
       </c>
-      <c r="B1345" t="s">
+      <c r="C1345" t="s">
         <v>3058</v>
-      </c>
-      <c r="C1345" t="s">
-        <v>3059</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1346" t="s">
         <v>3061</v>
       </c>
-      <c r="B1346" t="s">
+      <c r="C1346" t="s">
         <v>3062</v>
-      </c>
-      <c r="C1346" t="s">
-        <v>3063</v>
       </c>
     </row>
     <row r="1347" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1347" s="2" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="1348" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1348" s="2" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1349" t="s">
         <v>3067</v>
       </c>
-      <c r="B1349" t="s">
+      <c r="C1349" t="s">
         <v>3068</v>
       </c>
-      <c r="C1349" t="s">
+      <c r="D1349" t="s">
         <v>3069</v>
-      </c>
-      <c r="D1349" t="s">
-        <v>3070</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B1350" t="s">
         <v>3071</v>
       </c>
-      <c r="B1350" t="s">
+      <c r="C1350" t="s">
         <v>3072</v>
       </c>
-      <c r="C1350" t="s">
+      <c r="D1350" t="s">
         <v>3073</v>
-      </c>
-      <c r="D1350" t="s">
-        <v>3074</v>
       </c>
     </row>
     <row r="1351" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23858,343 +23858,343 @@
         <v>7</v>
       </c>
       <c r="B1351" s="2" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C1351" s="2" t="s">
         <v>3075</v>
-      </c>
-      <c r="C1351" s="2" t="s">
-        <v>3076</v>
       </c>
     </row>
     <row r="1352" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1352" s="2" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B1352" s="2" t="s">
         <v>3077</v>
       </c>
-      <c r="B1352" s="2" t="s">
+      <c r="C1352" s="2" t="s">
         <v>3078</v>
-      </c>
-      <c r="C1352" s="2" t="s">
-        <v>3079</v>
       </c>
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
+        <v>3079</v>
+      </c>
+      <c r="B1353" t="s">
         <v>3080</v>
-      </c>
-      <c r="B1353" t="s">
-        <v>3081</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1354" t="s">
         <v>3082</v>
-      </c>
-      <c r="B1354" t="s">
-        <v>3083</v>
       </c>
     </row>
     <row r="1355" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1355" s="2" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B1355" s="2" t="s">
         <v>3084</v>
       </c>
-      <c r="B1355" s="2" t="s">
+      <c r="C1355" s="2" t="s">
         <v>3085</v>
-      </c>
-      <c r="C1355" s="2" t="s">
-        <v>3086</v>
       </c>
     </row>
     <row r="1356" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1356" s="2" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B1356" s="2" t="s">
         <v>3087</v>
       </c>
-      <c r="B1356" s="2" t="s">
+      <c r="C1356" s="2" t="s">
         <v>3088</v>
-      </c>
-      <c r="C1356" s="2" t="s">
-        <v>3089</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B1357" t="s">
         <v>3090</v>
       </c>
-      <c r="B1357" t="s">
+      <c r="C1357" t="s">
         <v>3091</v>
       </c>
-      <c r="C1357" t="s">
+      <c r="D1357" t="s">
         <v>3092</v>
-      </c>
-      <c r="D1357" t="s">
-        <v>3093</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B1358" t="s">
         <v>3094</v>
       </c>
-      <c r="B1358" t="s">
+      <c r="C1358" t="s">
         <v>3095</v>
       </c>
-      <c r="C1358" t="s">
+      <c r="D1358" t="s">
         <v>3096</v>
-      </c>
-      <c r="D1358" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="1359" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="2" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B1359" s="2" t="s">
         <v>3098</v>
       </c>
-      <c r="B1359" s="2" t="s">
+      <c r="C1359" s="2" t="s">
         <v>3099</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="D1359" s="2" t="s">
         <v>3100</v>
       </c>
-      <c r="D1359" s="2" t="s">
+      <c r="E1359" s="2" t="s">
         <v>3101</v>
       </c>
-      <c r="E1359" s="2" t="s">
+      <c r="F1359" s="2" t="s">
         <v>3102</v>
       </c>
-      <c r="F1359" s="2" t="s">
+      <c r="G1359" s="2" t="s">
         <v>3103</v>
-      </c>
-      <c r="G1359" s="2" t="s">
-        <v>3104</v>
       </c>
     </row>
     <row r="1360" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="2" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B1360" s="2" t="s">
         <v>3105</v>
       </c>
-      <c r="B1360" s="2" t="s">
+      <c r="C1360" s="2" t="s">
         <v>3106</v>
       </c>
-      <c r="C1360" s="2" t="s">
+      <c r="D1360" s="2" t="s">
         <v>3107</v>
       </c>
-      <c r="D1360" s="2" t="s">
+      <c r="E1360" s="2" t="s">
+        <v>3105</v>
+      </c>
+      <c r="F1360" s="2" t="s">
         <v>3108</v>
       </c>
-      <c r="E1360" s="2" t="s">
-        <v>3106</v>
-      </c>
-      <c r="F1360" s="2" t="s">
+      <c r="G1360" s="2" t="s">
         <v>3109</v>
-      </c>
-      <c r="G1360" s="2" t="s">
-        <v>3110</v>
       </c>
     </row>
     <row r="1361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B1361" t="s">
         <v>3111</v>
       </c>
-      <c r="B1361" t="s">
+      <c r="C1361" t="s">
         <v>3112</v>
       </c>
-      <c r="C1361" t="s">
+      <c r="D1361" t="s">
         <v>3113</v>
       </c>
-      <c r="D1361" t="s">
+      <c r="E1361" t="s">
         <v>3114</v>
-      </c>
-      <c r="E1361" t="s">
-        <v>3115</v>
       </c>
     </row>
     <row r="1362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
+        <v>3115</v>
+      </c>
+      <c r="B1362" t="s">
         <v>3116</v>
       </c>
-      <c r="B1362" t="s">
+      <c r="C1362" t="s">
         <v>3117</v>
       </c>
-      <c r="C1362" t="s">
+      <c r="D1362" t="s">
         <v>3118</v>
       </c>
-      <c r="D1362" t="s">
+      <c r="E1362" t="s">
         <v>3119</v>
-      </c>
-      <c r="E1362" t="s">
-        <v>3120</v>
       </c>
     </row>
     <row r="1363" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1363" s="2" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1363" s="2" t="s">
         <v>3121</v>
-      </c>
-      <c r="B1363" s="2" t="s">
-        <v>3122</v>
       </c>
     </row>
     <row r="1364" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1364" s="2" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B1364" s="2" t="s">
         <v>3123</v>
-      </c>
-      <c r="B1364" s="2" t="s">
-        <v>3124</v>
       </c>
     </row>
     <row r="1365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1365" t="s">
         <v>3125</v>
       </c>
-      <c r="B1365" t="s">
+      <c r="C1365" t="s">
         <v>3126</v>
       </c>
-      <c r="C1365" t="s">
+      <c r="D1365" t="s">
         <v>3127</v>
       </c>
-      <c r="D1365" t="s">
+      <c r="E1365" t="s">
         <v>3128</v>
-      </c>
-      <c r="E1365" t="s">
-        <v>3129</v>
       </c>
     </row>
     <row r="1366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B1366" t="s">
         <v>3130</v>
       </c>
-      <c r="B1366" t="s">
+      <c r="C1366" t="s">
         <v>3131</v>
       </c>
-      <c r="C1366" t="s">
+      <c r="D1366" t="s">
         <v>3132</v>
       </c>
-      <c r="D1366" t="s">
+      <c r="E1366" t="s">
         <v>3133</v>
-      </c>
-      <c r="E1366" t="s">
-        <v>3134</v>
       </c>
     </row>
     <row r="1367" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1367" s="2" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B1367" s="2" t="s">
         <v>3135</v>
-      </c>
-      <c r="B1367" s="2" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="1368" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1368" s="2" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B1368" s="2" t="s">
         <v>3137</v>
-      </c>
-      <c r="B1368" s="2" t="s">
-        <v>3138</v>
       </c>
     </row>
     <row r="1369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B1369" t="s">
         <v>3139</v>
-      </c>
-      <c r="B1369" t="s">
-        <v>3140</v>
       </c>
     </row>
     <row r="1370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B1370" t="s">
         <v>3143</v>
-      </c>
-      <c r="B1370" t="s">
-        <v>3144</v>
       </c>
     </row>
     <row r="1371" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="2" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B1371" s="2" t="s">
+        <v>3140</v>
+      </c>
+      <c r="C1371" s="2" t="s">
         <v>3141</v>
-      </c>
-      <c r="C1371" s="2" t="s">
-        <v>3142</v>
       </c>
     </row>
     <row r="1372" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1372" s="2" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="B1372" s="2" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1372" s="2" t="s">
         <v>3145</v>
-      </c>
-      <c r="C1372" s="2" t="s">
-        <v>3146</v>
       </c>
     </row>
     <row r="1373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B1373" t="s">
         <v>3149</v>
       </c>
-      <c r="B1373" t="s">
+      <c r="C1373" t="s">
         <v>3150</v>
-      </c>
-      <c r="C1373" t="s">
-        <v>3151</v>
       </c>
     </row>
     <row r="1374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B1374" t="s">
         <v>3152</v>
       </c>
-      <c r="B1374" t="s">
+      <c r="C1374" t="s">
         <v>3153</v>
-      </c>
-      <c r="C1374" t="s">
-        <v>3154</v>
       </c>
     </row>
     <row r="1375" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="2" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1375" s="2" t="s">
         <v>3155</v>
       </c>
-      <c r="B1375" s="2" t="s">
+      <c r="C1375" s="2" t="s">
         <v>3156</v>
       </c>
-      <c r="C1375" s="2" t="s">
+      <c r="D1375" s="2" t="s">
         <v>3157</v>
-      </c>
-      <c r="D1375" s="2" t="s">
-        <v>3158</v>
       </c>
     </row>
     <row r="1376" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1376" s="2" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1376" s="2" t="s">
         <v>3161</v>
       </c>
-      <c r="B1376" s="2" t="s">
+      <c r="C1376" s="2" t="s">
         <v>3162</v>
       </c>
-      <c r="C1376" s="2" t="s">
+      <c r="D1376" s="2" t="s">
         <v>3163</v>
-      </c>
-      <c r="D1376" s="2" t="s">
-        <v>3164</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1377" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="B1377" t="s">
+        <v>3158</v>
+      </c>
+      <c r="C1377" t="s">
         <v>3159</v>
-      </c>
-      <c r="C1377" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B1378" t="s">
+        <v>3164</v>
+      </c>
+      <c r="C1378" t="s">
         <v>3165</v>
-      </c>
-      <c r="C1378" t="s">
-        <v>3166</v>
       </c>
     </row>
     <row r="1379" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24202,165 +24202,165 @@
         <v>7</v>
       </c>
       <c r="B1379" s="8" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="1380" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="4" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B1380" s="4" t="s">
         <v>3192</v>
-      </c>
-      <c r="B1380" s="4" t="s">
-        <v>3193</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1381" s="6" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B1381" s="9" t="s">
+        <v>3290</v>
+      </c>
+      <c r="C1381" s="9" t="s">
         <v>3291</v>
-      </c>
-      <c r="C1381" s="9" t="s">
-        <v>3292</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B1382" t="s">
         <v>3195</v>
       </c>
-      <c r="B1382" t="s">
+      <c r="C1382" t="s">
         <v>3196</v>
-      </c>
-      <c r="C1382" t="s">
-        <v>3197</v>
       </c>
     </row>
     <row r="1383" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1383" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B1383" s="8" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C1383" s="8" t="s">
         <v>3293</v>
       </c>
-      <c r="C1383" s="8" t="s">
+      <c r="D1383" s="8" t="s">
         <v>3294</v>
-      </c>
-      <c r="D1383" s="8" t="s">
-        <v>3295</v>
       </c>
     </row>
     <row r="1384" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1384" s="4" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1384" s="4" t="s">
         <v>3199</v>
       </c>
-      <c r="B1384" s="4" t="s">
+      <c r="C1384" s="4" t="s">
         <v>3200</v>
       </c>
-      <c r="C1384" s="4" t="s">
+      <c r="D1384" s="4" t="s">
         <v>3201</v>
-      </c>
-      <c r="D1384" s="4" t="s">
-        <v>3202</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B1385" s="9" t="s">
+        <v>3295</v>
+      </c>
+      <c r="C1385" s="9" t="s">
         <v>3296</v>
       </c>
-      <c r="C1385" s="9" t="s">
+      <c r="D1385" s="9" t="s">
         <v>3297</v>
-      </c>
-      <c r="D1385" s="9" t="s">
-        <v>3298</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B1386" t="s">
         <v>3204</v>
       </c>
-      <c r="B1386" t="s">
+      <c r="C1386" t="s">
         <v>3205</v>
       </c>
-      <c r="C1386" t="s">
+      <c r="D1386" t="s">
         <v>3206</v>
-      </c>
-      <c r="D1386" t="s">
-        <v>3207</v>
       </c>
     </row>
     <row r="1387" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1387" s="4" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B1387" s="8" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C1387" s="8" t="s">
         <v>3299</v>
       </c>
-      <c r="C1387" s="8" t="s">
+      <c r="D1387" s="8" t="s">
         <v>3300</v>
-      </c>
-      <c r="D1387" s="8" t="s">
-        <v>3301</v>
       </c>
     </row>
     <row r="1388" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1388" s="4" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B1388" s="4" t="s">
         <v>3209</v>
       </c>
-      <c r="B1388" s="4" t="s">
+      <c r="C1388" s="4" t="s">
         <v>3210</v>
       </c>
-      <c r="C1388" s="4" t="s">
+      <c r="D1388" s="4" t="s">
         <v>3211</v>
-      </c>
-      <c r="D1388" s="4" t="s">
-        <v>3212</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="B1389" s="9" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B1390" t="s">
         <v>3213</v>
-      </c>
-      <c r="B1390" t="s">
-        <v>3214</v>
       </c>
     </row>
     <row r="1391" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1391" s="4" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B1391" s="8" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1391" s="8" t="s">
         <v>3303</v>
       </c>
-      <c r="C1391" s="8" t="s">
+      <c r="D1391" s="8" t="s">
         <v>3304</v>
-      </c>
-      <c r="D1391" s="8" t="s">
-        <v>3305</v>
       </c>
     </row>
     <row r="1392" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1392" s="4" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B1392" s="4" t="s">
         <v>3216</v>
       </c>
-      <c r="B1392" s="4" t="s">
+      <c r="C1392" s="4" t="s">
         <v>3217</v>
       </c>
-      <c r="C1392" s="4" t="s">
+      <c r="D1392" s="4" t="s">
         <v>3218</v>
-      </c>
-      <c r="D1392" s="4" t="s">
-        <v>3219</v>
       </c>
     </row>
     <row r="1393" spans="1:3" x14ac:dyDescent="0.25">
@@ -24368,60 +24368,60 @@
         <v>199</v>
       </c>
       <c r="B1393" s="9" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="1394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B1394" t="s">
         <v>3220</v>
-      </c>
-      <c r="B1394" t="s">
-        <v>3221</v>
       </c>
     </row>
     <row r="1395" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1395" s="4" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="1396" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1396" s="4" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B1396" s="4" t="s">
         <v>3223</v>
-      </c>
-      <c r="B1396" s="4" t="s">
-        <v>3224</v>
       </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="B1397" s="9" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B1398" t="s">
         <v>3225</v>
-      </c>
-      <c r="B1398" t="s">
-        <v>3226</v>
       </c>
     </row>
     <row r="1399" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1399" s="4" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="B1399" s="8" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="1400" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1400" s="7" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="B1400" s="4" t="s">
         <v>547</v>
@@ -24429,79 +24429,79 @@
     </row>
     <row r="1401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="B1401" s="9" t="s">
+        <v>3309</v>
+      </c>
+      <c r="C1401" s="9" t="s">
         <v>3310</v>
-      </c>
-      <c r="C1401" s="9" t="s">
-        <v>3311</v>
       </c>
     </row>
     <row r="1402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B1402" t="s">
         <v>3231</v>
       </c>
-      <c r="B1402" t="s">
+      <c r="C1402" t="s">
         <v>3232</v>
-      </c>
-      <c r="C1402" t="s">
-        <v>3233</v>
       </c>
     </row>
     <row r="1403" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1403" s="4" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="B1403" s="8" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C1403" s="8" t="s">
         <v>3286</v>
-      </c>
-      <c r="C1403" s="8" t="s">
-        <v>3287</v>
       </c>
     </row>
     <row r="1404" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1404" s="4" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="B1404" s="4" t="s">
+        <v>3231</v>
+      </c>
+      <c r="C1404" s="4" t="s">
         <v>3232</v>
-      </c>
-      <c r="C1404" s="4" t="s">
-        <v>3233</v>
       </c>
     </row>
     <row r="1405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B1405" s="10" t="s">
         <v>3236</v>
-      </c>
-      <c r="B1405" s="10" t="s">
-        <v>3237</v>
       </c>
     </row>
     <row r="1406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="B1406" s="5" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="C1406" s="5"/>
     </row>
     <row r="1407" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1407" s="4" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="B1407" s="8" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C1407" s="8" t="s">
         <v>3244</v>
-      </c>
-      <c r="C1407" s="8" t="s">
-        <v>3245</v>
       </c>
     </row>
     <row r="1408" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1408" s="4" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B1408" s="4" t="s">
         <v>1117</v>
@@ -24512,230 +24512,230 @@
     </row>
     <row r="1409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="B1409" s="10" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="1410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B1410" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="1411" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1411" s="4" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="B1411" s="8" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="C1411" s="8" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="1412" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1412" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="B1412" s="4" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C1412" s="4" t="s">
         <v>3252</v>
-      </c>
-      <c r="C1412" s="4" t="s">
-        <v>3253</v>
       </c>
     </row>
     <row r="1413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="B1413" s="10" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C1413" s="10" t="s">
         <v>3257</v>
       </c>
-      <c r="C1413" s="10" t="s">
+      <c r="D1413" s="10" t="s">
         <v>3258</v>
-      </c>
-      <c r="D1413" s="10" t="s">
-        <v>3259</v>
       </c>
     </row>
     <row r="1414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="B1414" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C1414" t="s">
         <v>3260</v>
       </c>
-      <c r="C1414" t="s">
+      <c r="D1414" t="s">
         <v>3261</v>
-      </c>
-      <c r="D1414" t="s">
-        <v>3262</v>
       </c>
     </row>
     <row r="1415" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1415" s="4" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B1415" s="8" t="s">
         <v>3263</v>
       </c>
-      <c r="B1415" s="8" t="s">
+      <c r="C1415" s="8" t="s">
         <v>3264</v>
       </c>
-      <c r="C1415" s="8" t="s">
+      <c r="D1415" s="4" t="s">
         <v>3265</v>
       </c>
-      <c r="D1415" s="4" t="s">
-        <v>3266</v>
-      </c>
       <c r="E1415" s="12" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="1416" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1416" s="4" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="B1416" s="4" t="s">
+        <v>3342</v>
+      </c>
+      <c r="C1416" s="4" t="s">
         <v>3343</v>
       </c>
-      <c r="C1416" s="4" t="s">
+      <c r="D1416" s="4" t="s">
         <v>3344</v>
       </c>
-      <c r="D1416" s="4" t="s">
-        <v>3345</v>
-      </c>
       <c r="E1416" s="4" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="1417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1417" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="B1417" s="10" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="1418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
+        <v>3402</v>
+      </c>
+      <c r="B1418" t="s">
         <v>3403</v>
-      </c>
-      <c r="B1418" t="s">
-        <v>3404</v>
       </c>
     </row>
     <row r="1419" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1419" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="B1419" s="8" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="C1419" s="8"/>
     </row>
     <row r="1420" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1420" s="4" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1420" s="4" t="s">
         <v>3283</v>
-      </c>
-      <c r="B1420" s="4" t="s">
-        <v>3284</v>
       </c>
     </row>
     <row r="1421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="B1421" s="10" t="s">
+        <v>3330</v>
+      </c>
+      <c r="C1421" s="10" t="s">
         <v>3331</v>
-      </c>
-      <c r="C1421" s="10" t="s">
-        <v>3332</v>
       </c>
     </row>
     <row r="1422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B1422" t="s">
+        <v>3328</v>
+      </c>
+      <c r="C1422" t="s">
         <v>3329</v>
-      </c>
-      <c r="C1422" t="s">
-        <v>3330</v>
       </c>
     </row>
     <row r="1423" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1423" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B1423" s="8" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="C1423" s="8"/>
     </row>
     <row r="1424" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1424" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B1424" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="1425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="B1425" s="10" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="1426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B1426" t="s">
         <v>3325</v>
-      </c>
-      <c r="B1426" t="s">
-        <v>3326</v>
       </c>
     </row>
     <row r="1427" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1427" s="4" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="B1427" s="8" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="C1427" s="8" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="D1427" s="4" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E1427" s="4" t="s">
         <v>3318</v>
       </c>
-      <c r="E1427" s="4" t="s">
-        <v>3319</v>
-      </c>
       <c r="F1427" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="1428" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1428" s="4" t="s">
+        <v>3333</v>
+      </c>
+      <c r="B1428" s="4" t="s">
         <v>3334</v>
       </c>
-      <c r="B1428" s="4" t="s">
+      <c r="C1428" s="4" t="s">
+        <v>3336</v>
+      </c>
+      <c r="D1428" s="4" t="s">
+        <v>3338</v>
+      </c>
+      <c r="E1428" s="4" t="s">
         <v>3335</v>
       </c>
-      <c r="C1428" s="4" t="s">
+      <c r="F1428" s="4" t="s">
         <v>3337</v>
-      </c>
-      <c r="D1428" s="4" t="s">
-        <v>3339</v>
-      </c>
-      <c r="E1428" s="4" t="s">
-        <v>3336</v>
-      </c>
-      <c r="F1428" s="4" t="s">
-        <v>3338</v>
       </c>
     </row>
     <row r="1429" spans="1:6" x14ac:dyDescent="0.25">
@@ -24743,32 +24743,32 @@
         <v>7</v>
       </c>
       <c r="B1429" s="10" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="1430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="B1430" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="1431" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1431" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B1431" s="8" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="C1431" s="8"/>
     </row>
     <row r="1432" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1432" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B1432" s="4" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="1433" spans="1:6" x14ac:dyDescent="0.25">
@@ -24776,21 +24776,21 @@
         <v>7</v>
       </c>
       <c r="B1433" s="10" t="s">
+        <v>3377</v>
+      </c>
+      <c r="C1433" s="10" t="s">
         <v>3378</v>
-      </c>
-      <c r="C1433" s="10" t="s">
-        <v>3379</v>
       </c>
     </row>
     <row r="1434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="B1434" t="s">
+        <v>3379</v>
+      </c>
+      <c r="C1434" t="s">
         <v>3380</v>
-      </c>
-      <c r="C1434" t="s">
-        <v>3381</v>
       </c>
     </row>
     <row r="1435" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24798,16 +24798,16 @@
         <v>7</v>
       </c>
       <c r="B1435" s="8" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="C1435" s="8"/>
     </row>
     <row r="1436" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1436" s="4" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="B1436" s="4" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="1437" spans="1:6" x14ac:dyDescent="0.25">
@@ -24815,15 +24815,15 @@
         <v>199</v>
       </c>
       <c r="B1437" s="10" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="1438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
+        <v>3384</v>
+      </c>
+      <c r="B1438" t="s">
         <v>3385</v>
-      </c>
-      <c r="B1438" t="s">
-        <v>3386</v>
       </c>
     </row>
     <row r="1439" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24831,27 +24831,27 @@
         <v>199</v>
       </c>
       <c r="B1439" s="12" t="s">
+        <v>3392</v>
+      </c>
+      <c r="C1439" s="12" t="s">
         <v>3393</v>
       </c>
-      <c r="C1439" s="12" t="s">
+      <c r="D1439" s="12" t="s">
         <v>3394</v>
-      </c>
-      <c r="D1439" s="12" t="s">
-        <v>3395</v>
       </c>
     </row>
     <row r="1440" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1440" s="4" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="B1440" s="4" t="s">
+        <v>3389</v>
+      </c>
+      <c r="C1440" s="4" t="s">
         <v>3390</v>
       </c>
-      <c r="C1440" s="4" t="s">
+      <c r="D1440" s="4" t="s">
         <v>3391</v>
-      </c>
-      <c r="D1440" s="4" t="s">
-        <v>3392</v>
       </c>
     </row>
     <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
@@ -24859,15 +24859,15 @@
         <v>199</v>
       </c>
       <c r="B1441" s="10" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
+        <v>3395</v>
+      </c>
+      <c r="B1442" t="s">
         <v>3396</v>
-      </c>
-      <c r="B1442" t="s">
-        <v>3397</v>
       </c>
     </row>
     <row r="1443" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24875,15 +24875,15 @@
         <v>7</v>
       </c>
       <c r="B1443" s="12" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="1444" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1444" s="4" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B1444" s="4" t="s">
         <v>3400</v>
-      </c>
-      <c r="B1444" s="4" t="s">
-        <v>3401</v>
       </c>
     </row>
     <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
@@ -24891,15 +24891,15 @@
         <v>7</v>
       </c>
       <c r="B1445" s="10" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B1446" t="s">
         <v>3411</v>
-      </c>
-      <c r="B1446" t="s">
-        <v>3412</v>
       </c>
     </row>
     <row r="1447" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24907,15 +24907,15 @@
         <v>7</v>
       </c>
       <c r="B1447" s="12" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="1448" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1448" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B1448" s="4" t="s">
         <v>3414</v>
-      </c>
-      <c r="B1448" s="4" t="s">
-        <v>3415</v>
       </c>
     </row>
     <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
@@ -24923,15 +24923,15 @@
         <v>7</v>
       </c>
       <c r="B1449" s="10" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B1450" t="s">
         <v>3417</v>
-      </c>
-      <c r="B1450" t="s">
-        <v>3418</v>
       </c>
     </row>
     <row r="1451" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24939,15 +24939,15 @@
         <v>7</v>
       </c>
       <c r="B1451" s="12" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="1452" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1452" s="4" t="s">
+        <v>3419</v>
+      </c>
+      <c r="B1452" s="4" t="s">
         <v>3420</v>
-      </c>
-      <c r="B1452" s="4" t="s">
-        <v>3421</v>
       </c>
     </row>
     <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
@@ -24955,77 +24955,80 @@
         <v>7</v>
       </c>
       <c r="B1453" s="10" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="B1454" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="1455" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1455" s="4" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="B1455" s="12" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="1456" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1456" s="4" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B1456" s="4" t="s">
         <v>3432</v>
-      </c>
-      <c r="B1456" s="4" t="s">
-        <v>3433</v>
       </c>
     </row>
     <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B1457" s="10" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B1458" t="s">
         <v>3436</v>
-      </c>
-      <c r="B1458" t="s">
-        <v>3437</v>
       </c>
     </row>
     <row r="1459" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1459" s="13" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="1460" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1460" s="13" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1460" s="13" t="s">
         <v>3441</v>
-      </c>
-      <c r="B1460" s="13" t="s">
-        <v>3442</v>
       </c>
     </row>
     <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1461" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="B1461" s="10" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1462" t="s">
+        <v>3452</v>
+      </c>
+      <c r="B1462" t="s">
         <v>3453</v>
       </c>
-      <c r="B1462" t="s">
-        <v>3454</v>
-      </c>
+    </row>
+    <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1463" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708A429F-C025-48E9-AE42-AC9D1F2CBE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9D7AAB-9634-4E8D-ACC1-321EE536251D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="3457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3760" uniqueCount="3463">
   <si>
     <t>2706</t>
   </si>
@@ -10407,6 +10407,24 @@
   </si>
   <si>
     <t>C-VE120</t>
+  </si>
+  <si>
+    <t>C-RO120</t>
+  </si>
+  <si>
+    <t>2815</t>
+  </si>
+  <si>
+    <t>Ross Mountain Club</t>
+  </si>
+  <si>
+    <t>Ross Mountain Club|Pool</t>
+  </si>
+  <si>
+    <t>2769</t>
+  </si>
+  <si>
+    <t>C-CA345</t>
   </si>
 </sst>
 </file>
@@ -10817,7 +10835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1463"/>
+  <dimension ref="A1:P1466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -25027,8 +25045,37 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1463" s="10"/>
+    <row r="1463" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1463" s="4" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B1463" s="12" t="s">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1464" s="4" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B1464" s="4" t="s">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1465" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B1465" s="10" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1466" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>352</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
